--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{002D0D09-FC53-4BB3-94C4-5A1BEF06E3AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D62FFCEB-D282-4513-9E68-611296CCA33F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6873" uniqueCount="715">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6873" uniqueCount="720">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2236,13 +2236,28 @@
   </si>
   <si>
     <t>Código.ABNT</t>
+  </si>
+  <si>
+    <t>1S.40.80.17</t>
+  </si>
+  <si>
+    <t>1S.20.40.03.00</t>
+  </si>
+  <si>
+    <t>1S.20.30.01.00</t>
+  </si>
+  <si>
+    <t>1S.20.30.02.00</t>
+  </si>
+  <si>
+    <t>1S.70.45.07.00</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -2316,6 +2331,12 @@
       <b/>
       <sz val="5"/>
       <color rgb="FF000000"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FFFF0000"/>
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
@@ -2543,7 +2564,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -2697,12 +2718,15 @@
     <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="15">
     <dxf>
       <font>
         <b val="0"/>
@@ -2790,6 +2814,16 @@
         <strike val="0"/>
         <color theme="0"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3354,7 +3388,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46139.333336574076</v>
+        <v>46146.299021874998</v>
       </c>
       <c r="C18" s="47" t="s">
         <v>702</v>
@@ -3658,7 +3692,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="AA1:AA2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3808,7 +3842,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3853,7 +3887,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7012,8 +7046,8 @@
       <c r="A45" s="9">
         <v>45</v>
       </c>
-      <c r="B45" s="13" t="s">
-        <v>367</v>
+      <c r="B45" s="53" t="s">
+        <v>717</v>
       </c>
       <c r="C45" s="12" t="s">
         <v>714</v>
@@ -7154,8 +7188,8 @@
       <c r="A47" s="9">
         <v>47</v>
       </c>
-      <c r="B47" s="13" t="s">
-        <v>368</v>
+      <c r="B47" s="53" t="s">
+        <v>718</v>
       </c>
       <c r="C47" s="12" t="s">
         <v>714</v>
@@ -7580,8 +7614,8 @@
       <c r="A53" s="9">
         <v>53</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>373</v>
+      <c r="B53" s="53" t="s">
+        <v>716</v>
       </c>
       <c r="C53" s="12" t="s">
         <v>714</v>
@@ -12337,7 +12371,7 @@
       <c r="A120" s="9">
         <v>120</v>
       </c>
-      <c r="B120" s="13" t="s">
+      <c r="B120" s="53" t="s">
         <v>440</v>
       </c>
       <c r="C120" s="12" t="s">
@@ -12408,8 +12442,8 @@
       <c r="A121" s="9">
         <v>121</v>
       </c>
-      <c r="B121" s="13" t="s">
-        <v>440</v>
+      <c r="B121" s="53" t="s">
+        <v>715</v>
       </c>
       <c r="C121" s="12" t="s">
         <v>714</v>
@@ -20715,8 +20749,8 @@
       <c r="A238" s="9">
         <v>238</v>
       </c>
-      <c r="B238" s="13" t="s">
-        <v>556</v>
+      <c r="B238" s="53" t="s">
+        <v>719</v>
       </c>
       <c r="C238" s="12" t="s">
         <v>714</v>
@@ -25540,58 +25574,61 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="11" priority="1"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="10" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="7" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC91E386-056A-42B3-9A01-375FDCAC5EB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A61A1CA-30EC-4C4F-8EE5-4E532B555684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -2205,9 +2205,6 @@
     <t>"-"</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção"</t>
-  </si>
-  <si>
     <t>"Norma Brasileira para a classificação de objetos da construção"</t>
   </si>
   <si>
@@ -2478,7 +2475,10 @@
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
   </si>
   <si>
-    <t>"Classificação de objetos da construção - 1S"</t>
+    <t>"Normas"</t>
+  </si>
+  <si>
+    <t>"Classificação de Projeto e Construção"</t>
   </si>
 </sst>
 </file>
@@ -2951,15 +2951,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="21">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <b val="0"/>
@@ -3669,7 +3661,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.381228356484</v>
+        <v>46148.571151851851</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>698</v>
@@ -3677,7 +3669,7 @@
     </row>
     <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="B19" s="5" t="s">
         <v>702</v>
@@ -3700,7 +3692,7 @@
     </row>
     <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="38" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="B21" s="5" t="str">
         <f>_xlfn.TRANSLATE(B20,"pt","en")</f>
@@ -3889,19 +3881,19 @@
         <v>2</v>
       </c>
       <c r="B2" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="C2" s="50" t="s">
         <v>715</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="D2" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="D2" s="49" t="s">
+      <c r="E2" s="49" t="s">
         <v>717</v>
       </c>
-      <c r="E2" s="49" t="s">
+      <c r="F2" s="50" t="s">
         <v>718</v>
-      </c>
-      <c r="F2" s="50" t="s">
-        <v>719</v>
       </c>
       <c r="G2" s="51" t="s">
         <v>321</v>
@@ -3935,10 +3927,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="37" t="s">
+        <v>719</v>
+      </c>
+      <c r="Q2" s="37" t="s">
         <v>720</v>
-      </c>
-      <c r="Q2" s="37" t="s">
-        <v>721</v>
       </c>
       <c r="R2" s="53" t="s">
         <v>321</v>
@@ -3956,7 +3948,7 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="W2" s="55" t="str">
         <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
@@ -3972,7 +3964,7 @@
         <v>321</v>
       </c>
       <c r="AA2" s="37" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -3980,19 +3972,19 @@
         <v>3</v>
       </c>
       <c r="B3" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="C3" s="50" t="s">
         <v>715</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="D3" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="D3" s="49" t="s">
-        <v>717</v>
-      </c>
       <c r="E3" s="49" t="s">
+        <v>723</v>
+      </c>
+      <c r="F3" s="50" t="s">
         <v>724</v>
-      </c>
-      <c r="F3" s="50" t="s">
-        <v>725</v>
       </c>
       <c r="G3" s="51" t="s">
         <v>321</v>
@@ -4026,10 +4018,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="Q3" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="R3" s="53" t="s">
         <v>321</v>
@@ -4047,7 +4039,7 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="W3" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4063,7 +4055,7 @@
         <v>321</v>
       </c>
       <c r="AA3" s="37" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
     <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4071,19 +4063,19 @@
         <v>4</v>
       </c>
       <c r="B4" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="C4" s="50" t="s">
         <v>715</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="D4" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="D4" s="49" t="s">
-        <v>717</v>
-      </c>
       <c r="E4" s="49" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F4" s="50" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="G4" s="51" t="s">
         <v>321</v>
@@ -4117,10 +4109,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="R4" s="53" t="s">
         <v>321</v>
@@ -4138,7 +4130,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="W4" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4154,7 +4146,7 @@
         <v>321</v>
       </c>
       <c r="AA4" s="37" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
     </row>
     <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4162,19 +4154,19 @@
         <v>5</v>
       </c>
       <c r="B5" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="C5" s="50" t="s">
         <v>715</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="D5" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="D5" s="49" t="s">
-        <v>717</v>
-      </c>
       <c r="E5" s="49" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="G5" s="51" t="s">
         <v>321</v>
@@ -4208,10 +4200,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="R5" s="53" t="s">
         <v>321</v>
@@ -4229,7 +4221,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="W5" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4245,7 +4237,7 @@
         <v>321</v>
       </c>
       <c r="AA5" s="37" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4253,19 +4245,19 @@
         <v>6</v>
       </c>
       <c r="B6" s="49" t="s">
+        <v>714</v>
+      </c>
+      <c r="C6" s="50" t="s">
         <v>715</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="D6" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="D6" s="49" t="s">
-        <v>717</v>
-      </c>
       <c r="E6" s="49" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="F6" s="50" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="G6" s="51" t="s">
         <v>321</v>
@@ -4299,10 +4291,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="Q6" s="37" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="R6" s="53" t="s">
         <v>321</v>
@@ -4320,7 +4312,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="W6" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4336,7 +4328,7 @@
         <v>321</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4356,7 +4348,7 @@
         <v>679</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>321</v>
@@ -4390,10 +4382,10 @@
         <v>ABNT.0M</v>
       </c>
       <c r="P7" s="52" t="s">
+        <v>737</v>
+      </c>
+      <c r="Q7" s="52" t="s">
         <v>738</v>
-      </c>
-      <c r="Q7" s="52" t="s">
-        <v>739</v>
       </c>
       <c r="R7" s="53" t="s">
         <v>321</v>
@@ -4424,10 +4416,10 @@
         <v>321</v>
       </c>
       <c r="Z7" s="37" t="s">
+        <v>739</v>
+      </c>
+      <c r="AA7" s="56" t="s">
         <v>740</v>
-      </c>
-      <c r="AA7" s="56" t="s">
-        <v>741</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4447,7 +4439,7 @@
         <v>679</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="G8" s="31" t="s">
         <v>321</v>
@@ -4481,10 +4473,10 @@
         <v>ABNT.0P</v>
       </c>
       <c r="P8" s="52" t="s">
+        <v>742</v>
+      </c>
+      <c r="Q8" s="52" t="s">
         <v>743</v>
-      </c>
-      <c r="Q8" s="52" t="s">
-        <v>744</v>
       </c>
       <c r="R8" s="53" t="s">
         <v>321</v>
@@ -4515,10 +4507,10 @@
         <v>321</v>
       </c>
       <c r="Z8" s="37" t="s">
+        <v>744</v>
+      </c>
+      <c r="AA8" s="56" t="s">
         <v>745</v>
-      </c>
-      <c r="AA8" s="56" t="s">
-        <v>746</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4538,7 +4530,7 @@
         <v>679</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>321</v>
@@ -4572,10 +4564,10 @@
         <v>ABNT.1D</v>
       </c>
       <c r="P9" s="52" t="s">
+        <v>747</v>
+      </c>
+      <c r="Q9" s="52" t="s">
         <v>748</v>
-      </c>
-      <c r="Q9" s="52" t="s">
-        <v>749</v>
       </c>
       <c r="R9" s="53" t="s">
         <v>321</v>
@@ -4606,10 +4598,10 @@
         <v>321</v>
       </c>
       <c r="Z9" s="37" t="s">
+        <v>749</v>
+      </c>
+      <c r="AA9" s="56" t="s">
         <v>750</v>
-      </c>
-      <c r="AA9" s="56" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4629,7 +4621,7 @@
         <v>679</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G10" s="31" t="s">
         <v>321</v>
@@ -4663,10 +4655,10 @@
         <v>ABNT.1F</v>
       </c>
       <c r="P10" s="52" t="s">
+        <v>752</v>
+      </c>
+      <c r="Q10" s="52" t="s">
         <v>753</v>
-      </c>
-      <c r="Q10" s="52" t="s">
-        <v>754</v>
       </c>
       <c r="R10" s="53" t="s">
         <v>321</v>
@@ -4697,10 +4689,10 @@
         <v>321</v>
       </c>
       <c r="Z10" s="37" t="s">
+        <v>754</v>
+      </c>
+      <c r="AA10" s="56" t="s">
         <v>755</v>
-      </c>
-      <c r="AA10" s="56" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4720,7 +4712,7 @@
         <v>679</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G11" s="31" t="s">
         <v>321</v>
@@ -4754,10 +4746,10 @@
         <v>ABNT.1S</v>
       </c>
       <c r="P11" s="52" t="s">
+        <v>757</v>
+      </c>
+      <c r="Q11" s="52" t="s">
         <v>758</v>
-      </c>
-      <c r="Q11" s="52" t="s">
-        <v>759</v>
       </c>
       <c r="R11" s="53" t="s">
         <v>321</v>
@@ -4791,7 +4783,7 @@
         <v>624</v>
       </c>
       <c r="AA11" s="56" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4811,7 +4803,7 @@
         <v>679</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G12" s="31" t="s">
         <v>321</v>
@@ -4845,10 +4837,10 @@
         <v>ABNT.2C</v>
       </c>
       <c r="P12" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q12" s="52" t="s">
         <v>762</v>
-      </c>
-      <c r="Q12" s="52" t="s">
-        <v>763</v>
       </c>
       <c r="R12" s="53" t="s">
         <v>321</v>
@@ -4879,10 +4871,10 @@
         <v>321</v>
       </c>
       <c r="Z12" s="37" t="s">
+        <v>763</v>
+      </c>
+      <c r="AA12" s="56" t="s">
         <v>764</v>
-      </c>
-      <c r="AA12" s="56" t="s">
-        <v>765</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4902,7 +4894,7 @@
         <v>679</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="G13" s="31" t="s">
         <v>321</v>
@@ -4936,10 +4928,10 @@
         <v>ABNT.2N</v>
       </c>
       <c r="P13" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q13" s="52" t="s">
         <v>762</v>
-      </c>
-      <c r="Q13" s="52" t="s">
-        <v>763</v>
       </c>
       <c r="R13" s="53" t="s">
         <v>321</v>
@@ -4970,10 +4962,10 @@
         <v>321</v>
       </c>
       <c r="Z13" s="37" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="AA13" s="56" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -4993,7 +4985,7 @@
         <v>679</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="G14" s="31" t="s">
         <v>321</v>
@@ -5027,10 +5019,10 @@
         <v>ABNT.2Q</v>
       </c>
       <c r="P14" s="52" t="s">
+        <v>761</v>
+      </c>
+      <c r="Q14" s="52" t="s">
         <v>762</v>
-      </c>
-      <c r="Q14" s="52" t="s">
-        <v>763</v>
       </c>
       <c r="R14" s="53" t="s">
         <v>321</v>
@@ -5061,10 +5053,10 @@
         <v>321</v>
       </c>
       <c r="Z14" s="37" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AA14" s="56" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5084,7 +5076,7 @@
         <v>679</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G15" s="31" t="s">
         <v>321</v>
@@ -5118,10 +5110,10 @@
         <v>ABNT.3E</v>
       </c>
       <c r="P15" s="52" t="s">
+        <v>770</v>
+      </c>
+      <c r="Q15" s="52" t="s">
         <v>771</v>
-      </c>
-      <c r="Q15" s="52" t="s">
-        <v>772</v>
       </c>
       <c r="R15" s="53" t="s">
         <v>321</v>
@@ -5152,10 +5144,10 @@
         <v>321</v>
       </c>
       <c r="Z15" s="37" t="s">
+        <v>772</v>
+      </c>
+      <c r="AA15" s="56" t="s">
         <v>773</v>
-      </c>
-      <c r="AA15" s="56" t="s">
-        <v>774</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5175,7 +5167,7 @@
         <v>679</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>321</v>
@@ -5209,10 +5201,10 @@
         <v>ABNT.3R</v>
       </c>
       <c r="P16" s="52" t="s">
+        <v>775</v>
+      </c>
+      <c r="Q16" s="52" t="s">
         <v>776</v>
-      </c>
-      <c r="Q16" s="52" t="s">
-        <v>777</v>
       </c>
       <c r="R16" s="53" t="s">
         <v>321</v>
@@ -5243,10 +5235,10 @@
         <v>321</v>
       </c>
       <c r="Z16" s="37" t="s">
+        <v>777</v>
+      </c>
+      <c r="AA16" s="56" t="s">
         <v>778</v>
-      </c>
-      <c r="AA16" s="56" t="s">
-        <v>779</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5266,7 +5258,7 @@
         <v>679</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="G17" s="31" t="s">
         <v>321</v>
@@ -5300,10 +5292,10 @@
         <v>ABNT.4A</v>
       </c>
       <c r="P17" s="52" t="s">
+        <v>780</v>
+      </c>
+      <c r="Q17" s="52" t="s">
         <v>781</v>
-      </c>
-      <c r="Q17" s="52" t="s">
-        <v>782</v>
       </c>
       <c r="R17" s="53" t="s">
         <v>321</v>
@@ -5334,10 +5326,10 @@
         <v>321</v>
       </c>
       <c r="Z17" s="37" t="s">
+        <v>782</v>
+      </c>
+      <c r="AA17" s="56" t="s">
         <v>783</v>
-      </c>
-      <c r="AA17" s="56" t="s">
-        <v>784</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5357,7 +5349,7 @@
         <v>679</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>321</v>
@@ -5391,10 +5383,10 @@
         <v>ABNT.4U</v>
       </c>
       <c r="P18" s="52" t="s">
+        <v>785</v>
+      </c>
+      <c r="Q18" s="52" t="s">
         <v>786</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>787</v>
       </c>
       <c r="R18" s="53" t="s">
         <v>321</v>
@@ -5425,10 +5417,10 @@
         <v>321</v>
       </c>
       <c r="Z18" s="37" t="s">
+        <v>787</v>
+      </c>
+      <c r="AA18" s="56" t="s">
         <v>788</v>
-      </c>
-      <c r="AA18" s="56" t="s">
-        <v>789</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -5448,7 +5440,7 @@
         <v>679</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="G19" s="31" t="s">
         <v>321</v>
@@ -5482,10 +5474,10 @@
         <v>ABNT.5I</v>
       </c>
       <c r="P19" s="52" t="s">
+        <v>790</v>
+      </c>
+      <c r="Q19" s="52" t="s">
         <v>791</v>
-      </c>
-      <c r="Q19" s="52" t="s">
-        <v>792</v>
       </c>
       <c r="R19" s="53" t="s">
         <v>321</v>
@@ -5516,26 +5508,26 @@
         <v>321</v>
       </c>
       <c r="Z19" s="37" t="s">
+        <v>792</v>
+      </c>
+      <c r="AA19" s="56" t="s">
         <v>793</v>
-      </c>
-      <c r="AA19" s="56" t="s">
-        <v>794</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A2:A19">
-    <cfRule type="cellIs" dxfId="20" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="19" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA19">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5685,7 +5677,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5730,7 +5722,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5849,16 +5841,16 @@
         <v>632</v>
       </c>
       <c r="F2" s="43" t="s">
-        <v>626</v>
+        <v>321</v>
       </c>
       <c r="G2" s="35" t="s">
-        <v>703</v>
+        <v>321</v>
       </c>
       <c r="H2" s="43" t="s">
         <v>628</v>
       </c>
       <c r="I2" s="35" t="s">
-        <v>704</v>
+        <v>794</v>
       </c>
       <c r="J2" s="43" t="s">
         <v>685</v>
@@ -5870,16 +5862,16 @@
         <v>1</v>
       </c>
       <c r="M2" s="44" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="N2" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O2" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P2" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q2" s="35" t="s">
         <v>703</v>
@@ -5925,13 +5917,13 @@
       <c r="G3" s="33" t="s">
         <v>627</v>
       </c>
-      <c r="H3" s="32" t="s">
+      <c r="H3" s="43" t="s">
         <v>628</v>
       </c>
       <c r="I3" s="35" t="s">
-        <v>704</v>
-      </c>
-      <c r="J3" s="32" t="s">
+        <v>794</v>
+      </c>
+      <c r="J3" s="43" t="s">
         <v>685</v>
       </c>
       <c r="K3" s="35" t="s">
@@ -5944,13 +5936,13 @@
         <v>14</v>
       </c>
       <c r="N3" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O3" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P3" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q3" s="35" t="s">
         <v>703</v>
@@ -5982,7 +5974,7 @@
         <v>624</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D4" s="32" t="s">
         <v>630</v>
@@ -5996,13 +5988,13 @@
       <c r="G4" s="33" t="s">
         <v>627</v>
       </c>
-      <c r="H4" s="32" t="s">
+      <c r="H4" s="43" t="s">
         <v>628</v>
       </c>
       <c r="I4" s="35" t="s">
-        <v>704</v>
-      </c>
-      <c r="J4" s="32" t="s">
+        <v>794</v>
+      </c>
+      <c r="J4" s="43" t="s">
         <v>685</v>
       </c>
       <c r="K4" s="35" t="s">
@@ -6015,13 +6007,13 @@
         <v>629</v>
       </c>
       <c r="N4" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O4" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P4" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q4" s="35" t="s">
         <v>703</v>
@@ -6053,7 +6045,7 @@
         <v>328</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D5" s="32" t="s">
         <v>630</v>
@@ -6086,13 +6078,13 @@
         <v>18</v>
       </c>
       <c r="N5" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O5" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P5" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q5" s="35" t="s">
         <v>703</v>
@@ -6124,7 +6116,7 @@
         <v>329</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D6" s="32" t="s">
         <v>630</v>
@@ -6157,13 +6149,13 @@
         <v>19</v>
       </c>
       <c r="N6" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O6" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P6" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>703</v>
@@ -6195,7 +6187,7 @@
         <v>330</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D7" s="32" t="s">
         <v>630</v>
@@ -6228,13 +6220,13 @@
         <v>20</v>
       </c>
       <c r="N7" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O7" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P7" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q7" s="35" t="s">
         <v>703</v>
@@ -6266,7 +6258,7 @@
         <v>331</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D8" s="32" t="s">
         <v>630</v>
@@ -6299,13 +6291,13 @@
         <v>21</v>
       </c>
       <c r="N8" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O8" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P8" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q8" s="35" t="s">
         <v>703</v>
@@ -6337,7 +6329,7 @@
         <v>332</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D9" s="32" t="s">
         <v>630</v>
@@ -6370,13 +6362,13 @@
         <v>22</v>
       </c>
       <c r="N9" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O9" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P9" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q9" s="35" t="s">
         <v>703</v>
@@ -6408,7 +6400,7 @@
         <v>333</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D10" s="32" t="s">
         <v>630</v>
@@ -6441,13 +6433,13 @@
         <v>23</v>
       </c>
       <c r="N10" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O10" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P10" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q10" s="35" t="s">
         <v>703</v>
@@ -6479,7 +6471,7 @@
         <v>334</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D11" s="32" t="s">
         <v>630</v>
@@ -6512,13 +6504,13 @@
         <v>24</v>
       </c>
       <c r="N11" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O11" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P11" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q11" s="35" t="s">
         <v>703</v>
@@ -6550,7 +6542,7 @@
         <v>335</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D12" s="32" t="s">
         <v>630</v>
@@ -6583,13 +6575,13 @@
         <v>25</v>
       </c>
       <c r="N12" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O12" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P12" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q12" s="35" t="s">
         <v>703</v>
@@ -6621,7 +6613,7 @@
         <v>336</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D13" s="32" t="s">
         <v>630</v>
@@ -6654,13 +6646,13 @@
         <v>26</v>
       </c>
       <c r="N13" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O13" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P13" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q13" s="35" t="s">
         <v>703</v>
@@ -6692,7 +6684,7 @@
         <v>337</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D14" s="32" t="s">
         <v>630</v>
@@ -6725,13 +6717,13 @@
         <v>27</v>
       </c>
       <c r="N14" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O14" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P14" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q14" s="35" t="s">
         <v>703</v>
@@ -6763,7 +6755,7 @@
         <v>338</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D15" s="32" t="s">
         <v>630</v>
@@ -6796,13 +6788,13 @@
         <v>28</v>
       </c>
       <c r="N15" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O15" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P15" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q15" s="35" t="s">
         <v>703</v>
@@ -6834,7 +6826,7 @@
         <v>339</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D16" s="32" t="s">
         <v>630</v>
@@ -6867,13 +6859,13 @@
         <v>29</v>
       </c>
       <c r="N16" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O16" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P16" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q16" s="35" t="s">
         <v>703</v>
@@ -6905,7 +6897,7 @@
         <v>340</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D17" s="32" t="s">
         <v>630</v>
@@ -6938,13 +6930,13 @@
         <v>30</v>
       </c>
       <c r="N17" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O17" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P17" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q17" s="35" t="s">
         <v>703</v>
@@ -6976,7 +6968,7 @@
         <v>341</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D18" s="32" t="s">
         <v>630</v>
@@ -7009,13 +7001,13 @@
         <v>31</v>
       </c>
       <c r="N18" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O18" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P18" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q18" s="35" t="s">
         <v>703</v>
@@ -7047,7 +7039,7 @@
         <v>342</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D19" s="32" t="s">
         <v>630</v>
@@ -7080,13 +7072,13 @@
         <v>32</v>
       </c>
       <c r="N19" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O19" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P19" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q19" s="35" t="s">
         <v>703</v>
@@ -7118,7 +7110,7 @@
         <v>343</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D20" s="32" t="s">
         <v>630</v>
@@ -7151,13 +7143,13 @@
         <v>33</v>
       </c>
       <c r="N20" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O20" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P20" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q20" s="35" t="s">
         <v>703</v>
@@ -7189,7 +7181,7 @@
         <v>344</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D21" s="32" t="s">
         <v>630</v>
@@ -7222,13 +7214,13 @@
         <v>34</v>
       </c>
       <c r="N21" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O21" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P21" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q21" s="35" t="s">
         <v>703</v>
@@ -7260,7 +7252,7 @@
         <v>345</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D22" s="32" t="s">
         <v>630</v>
@@ -7293,13 +7285,13 @@
         <v>35</v>
       </c>
       <c r="N22" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O22" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P22" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q22" s="35" t="s">
         <v>703</v>
@@ -7331,7 +7323,7 @@
         <v>346</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D23" s="32" t="s">
         <v>630</v>
@@ -7364,13 +7356,13 @@
         <v>36</v>
       </c>
       <c r="N23" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O23" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P23" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q23" s="35" t="s">
         <v>703</v>
@@ -7402,7 +7394,7 @@
         <v>347</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D24" s="32" t="s">
         <v>630</v>
@@ -7435,13 +7427,13 @@
         <v>37</v>
       </c>
       <c r="N24" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O24" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P24" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q24" s="35" t="s">
         <v>703</v>
@@ -7473,7 +7465,7 @@
         <v>348</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D25" s="32" t="s">
         <v>630</v>
@@ -7506,13 +7498,13 @@
         <v>38</v>
       </c>
       <c r="N25" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O25" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P25" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q25" s="35" t="s">
         <v>703</v>
@@ -7544,7 +7536,7 @@
         <v>349</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D26" s="32" t="s">
         <v>630</v>
@@ -7577,13 +7569,13 @@
         <v>39</v>
       </c>
       <c r="N26" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O26" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P26" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q26" s="35" t="s">
         <v>703</v>
@@ -7615,7 +7607,7 @@
         <v>350</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D27" s="32" t="s">
         <v>630</v>
@@ -7648,13 +7640,13 @@
         <v>40</v>
       </c>
       <c r="N27" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O27" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P27" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q27" s="35" t="s">
         <v>703</v>
@@ -7686,7 +7678,7 @@
         <v>351</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D28" s="32" t="s">
         <v>630</v>
@@ -7719,13 +7711,13 @@
         <v>41</v>
       </c>
       <c r="N28" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O28" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P28" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q28" s="35" t="s">
         <v>703</v>
@@ -7757,7 +7749,7 @@
         <v>352</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D29" s="32" t="s">
         <v>630</v>
@@ -7790,13 +7782,13 @@
         <v>42</v>
       </c>
       <c r="N29" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O29" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P29" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q29" s="35" t="s">
         <v>703</v>
@@ -7828,7 +7820,7 @@
         <v>353</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D30" s="32" t="s">
         <v>630</v>
@@ -7861,13 +7853,13 @@
         <v>43</v>
       </c>
       <c r="N30" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O30" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P30" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q30" s="35" t="s">
         <v>703</v>
@@ -7899,7 +7891,7 @@
         <v>354</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D31" s="32" t="s">
         <v>630</v>
@@ -7932,13 +7924,13 @@
         <v>44</v>
       </c>
       <c r="N31" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O31" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P31" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q31" s="35" t="s">
         <v>703</v>
@@ -7970,7 +7962,7 @@
         <v>355</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D32" s="32" t="s">
         <v>630</v>
@@ -8003,13 +7995,13 @@
         <v>45</v>
       </c>
       <c r="N32" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O32" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P32" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q32" s="35" t="s">
         <v>703</v>
@@ -8041,7 +8033,7 @@
         <v>356</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D33" s="32" t="s">
         <v>630</v>
@@ -8074,13 +8066,13 @@
         <v>46</v>
       </c>
       <c r="N33" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O33" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P33" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q33" s="35" t="s">
         <v>703</v>
@@ -8112,7 +8104,7 @@
         <v>357</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D34" s="32" t="s">
         <v>630</v>
@@ -8145,13 +8137,13 @@
         <v>47</v>
       </c>
       <c r="N34" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O34" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P34" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q34" s="35" t="s">
         <v>703</v>
@@ -8183,7 +8175,7 @@
         <v>358</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D35" s="32" t="s">
         <v>630</v>
@@ -8216,13 +8208,13 @@
         <v>48</v>
       </c>
       <c r="N35" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O35" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P35" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q35" s="35" t="s">
         <v>703</v>
@@ -8254,7 +8246,7 @@
         <v>359</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D36" s="32" t="s">
         <v>630</v>
@@ -8287,13 +8279,13 @@
         <v>49</v>
       </c>
       <c r="N36" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O36" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P36" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q36" s="35" t="s">
         <v>703</v>
@@ -8325,7 +8317,7 @@
         <v>360</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D37" s="32" t="s">
         <v>630</v>
@@ -8358,13 +8350,13 @@
         <v>50</v>
       </c>
       <c r="N37" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O37" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P37" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q37" s="35" t="s">
         <v>703</v>
@@ -8396,7 +8388,7 @@
         <v>361</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D38" s="32" t="s">
         <v>630</v>
@@ -8429,13 +8421,13 @@
         <v>51</v>
       </c>
       <c r="N38" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O38" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P38" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q38" s="35" t="s">
         <v>703</v>
@@ -8467,7 +8459,7 @@
         <v>362</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D39" s="32" t="s">
         <v>630</v>
@@ -8500,13 +8492,13 @@
         <v>52</v>
       </c>
       <c r="N39" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O39" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P39" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q39" s="35" t="s">
         <v>703</v>
@@ -8538,7 +8530,7 @@
         <v>363</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D40" s="32" t="s">
         <v>630</v>
@@ -8571,13 +8563,13 @@
         <v>53</v>
       </c>
       <c r="N40" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O40" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P40" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q40" s="35" t="s">
         <v>703</v>
@@ -8609,7 +8601,7 @@
         <v>364</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D41" s="32" t="s">
         <v>630</v>
@@ -8642,13 +8634,13 @@
         <v>54</v>
       </c>
       <c r="N41" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O41" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P41" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q41" s="35" t="s">
         <v>703</v>
@@ -8680,7 +8672,7 @@
         <v>365</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D42" s="32" t="s">
         <v>630</v>
@@ -8713,13 +8705,13 @@
         <v>55</v>
       </c>
       <c r="N42" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O42" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P42" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q42" s="35" t="s">
         <v>703</v>
@@ -8751,7 +8743,7 @@
         <v>366</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D43" s="32" t="s">
         <v>630</v>
@@ -8784,13 +8776,13 @@
         <v>56</v>
       </c>
       <c r="N43" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O43" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P43" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q43" s="35" t="s">
         <v>703</v>
@@ -8822,7 +8814,7 @@
         <v>367</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D44" s="32" t="s">
         <v>630</v>
@@ -8855,13 +8847,13 @@
         <v>57</v>
       </c>
       <c r="N44" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O44" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P44" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q44" s="35" t="s">
         <v>703</v>
@@ -8890,10 +8882,10 @@
         <v>45</v>
       </c>
       <c r="B45" s="47" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D45" s="32" t="s">
         <v>630</v>
@@ -8926,13 +8918,13 @@
         <v>58</v>
       </c>
       <c r="N45" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O45" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P45" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q45" s="35" t="s">
         <v>703</v>
@@ -8964,7 +8956,7 @@
         <v>368</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D46" s="32" t="s">
         <v>630</v>
@@ -8997,13 +8989,13 @@
         <v>59</v>
       </c>
       <c r="N46" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O46" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P46" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q46" s="35" t="s">
         <v>703</v>
@@ -9032,10 +9024,10 @@
         <v>47</v>
       </c>
       <c r="B47" s="47" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D47" s="32" t="s">
         <v>630</v>
@@ -9068,13 +9060,13 @@
         <v>15</v>
       </c>
       <c r="N47" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O47" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P47" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q47" s="35" t="s">
         <v>703</v>
@@ -9106,7 +9098,7 @@
         <v>369</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D48" s="32" t="s">
         <v>630</v>
@@ -9139,13 +9131,13 @@
         <v>60</v>
       </c>
       <c r="N48" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O48" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P48" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q48" s="35" t="s">
         <v>703</v>
@@ -9177,7 +9169,7 @@
         <v>370</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D49" s="32" t="s">
         <v>630</v>
@@ -9210,13 +9202,13 @@
         <v>61</v>
       </c>
       <c r="N49" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O49" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P49" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q49" s="35" t="s">
         <v>703</v>
@@ -9248,7 +9240,7 @@
         <v>371</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D50" s="32" t="s">
         <v>630</v>
@@ -9281,13 +9273,13 @@
         <v>62</v>
       </c>
       <c r="N50" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O50" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P50" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q50" s="35" t="s">
         <v>703</v>
@@ -9319,7 +9311,7 @@
         <v>372</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D51" s="32" t="s">
         <v>630</v>
@@ -9352,13 +9344,13 @@
         <v>63</v>
       </c>
       <c r="N51" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O51" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P51" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q51" s="35" t="s">
         <v>703</v>
@@ -9390,7 +9382,7 @@
         <v>373</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D52" s="32" t="s">
         <v>630</v>
@@ -9423,13 +9415,13 @@
         <v>64</v>
       </c>
       <c r="N52" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O52" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P52" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q52" s="35" t="s">
         <v>703</v>
@@ -9458,10 +9450,10 @@
         <v>53</v>
       </c>
       <c r="B53" s="47" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D53" s="32" t="s">
         <v>630</v>
@@ -9494,13 +9486,13 @@
         <v>65</v>
       </c>
       <c r="N53" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O53" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P53" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q53" s="35" t="s">
         <v>703</v>
@@ -9532,7 +9524,7 @@
         <v>374</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D54" s="32" t="s">
         <v>630</v>
@@ -9565,13 +9557,13 @@
         <v>66</v>
       </c>
       <c r="N54" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O54" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P54" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q54" s="35" t="s">
         <v>703</v>
@@ -9603,7 +9595,7 @@
         <v>375</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D55" s="32" t="s">
         <v>630</v>
@@ -9636,13 +9628,13 @@
         <v>67</v>
       </c>
       <c r="N55" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O55" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P55" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q55" s="35" t="s">
         <v>703</v>
@@ -9674,7 +9666,7 @@
         <v>376</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D56" s="32" t="s">
         <v>630</v>
@@ -9707,13 +9699,13 @@
         <v>68</v>
       </c>
       <c r="N56" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O56" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P56" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q56" s="35" t="s">
         <v>703</v>
@@ -9745,7 +9737,7 @@
         <v>377</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D57" s="32" t="s">
         <v>630</v>
@@ -9778,13 +9770,13 @@
         <v>69</v>
       </c>
       <c r="N57" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O57" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P57" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q57" s="35" t="s">
         <v>703</v>
@@ -9816,7 +9808,7 @@
         <v>378</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D58" s="32" t="s">
         <v>630</v>
@@ -9849,13 +9841,13 @@
         <v>70</v>
       </c>
       <c r="N58" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O58" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P58" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q58" s="35" t="s">
         <v>703</v>
@@ -9887,7 +9879,7 @@
         <v>379</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D59" s="32" t="s">
         <v>630</v>
@@ -9920,13 +9912,13 @@
         <v>71</v>
       </c>
       <c r="N59" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O59" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P59" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q59" s="35" t="s">
         <v>703</v>
@@ -9958,7 +9950,7 @@
         <v>380</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D60" s="32" t="s">
         <v>630</v>
@@ -9991,13 +9983,13 @@
         <v>72</v>
       </c>
       <c r="N60" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O60" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P60" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q60" s="35" t="s">
         <v>703</v>
@@ -10029,7 +10021,7 @@
         <v>381</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D61" s="32" t="s">
         <v>630</v>
@@ -10062,13 +10054,13 @@
         <v>73</v>
       </c>
       <c r="N61" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O61" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P61" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q61" s="35" t="s">
         <v>703</v>
@@ -10100,7 +10092,7 @@
         <v>382</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D62" s="32" t="s">
         <v>630</v>
@@ -10133,13 +10125,13 @@
         <v>74</v>
       </c>
       <c r="N62" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O62" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P62" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q62" s="35" t="s">
         <v>703</v>
@@ -10171,7 +10163,7 @@
         <v>383</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D63" s="32" t="s">
         <v>630</v>
@@ -10204,13 +10196,13 @@
         <v>75</v>
       </c>
       <c r="N63" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O63" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P63" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q63" s="35" t="s">
         <v>703</v>
@@ -10242,7 +10234,7 @@
         <v>384</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D64" s="32" t="s">
         <v>630</v>
@@ -10275,13 +10267,13 @@
         <v>76</v>
       </c>
       <c r="N64" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O64" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P64" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q64" s="35" t="s">
         <v>703</v>
@@ -10313,7 +10305,7 @@
         <v>385</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D65" s="32" t="s">
         <v>630</v>
@@ -10346,13 +10338,13 @@
         <v>77</v>
       </c>
       <c r="N65" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O65" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P65" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q65" s="35" t="s">
         <v>703</v>
@@ -10384,7 +10376,7 @@
         <v>386</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D66" s="32" t="s">
         <v>630</v>
@@ -10417,13 +10409,13 @@
         <v>78</v>
       </c>
       <c r="N66" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O66" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P66" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q66" s="35" t="s">
         <v>703</v>
@@ -10455,7 +10447,7 @@
         <v>387</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D67" s="32" t="s">
         <v>630</v>
@@ -10488,13 +10480,13 @@
         <v>79</v>
       </c>
       <c r="N67" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O67" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P67" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q67" s="35" t="s">
         <v>703</v>
@@ -10526,7 +10518,7 @@
         <v>388</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D68" s="32" t="s">
         <v>630</v>
@@ -10559,13 +10551,13 @@
         <v>80</v>
       </c>
       <c r="N68" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O68" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P68" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q68" s="35" t="s">
         <v>703</v>
@@ -10597,7 +10589,7 @@
         <v>389</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D69" s="32" t="s">
         <v>630</v>
@@ -10630,13 +10622,13 @@
         <v>81</v>
       </c>
       <c r="N69" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O69" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P69" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q69" s="35" t="s">
         <v>703</v>
@@ -10668,7 +10660,7 @@
         <v>390</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D70" s="32" t="s">
         <v>630</v>
@@ -10701,13 +10693,13 @@
         <v>82</v>
       </c>
       <c r="N70" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O70" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P70" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q70" s="35" t="s">
         <v>703</v>
@@ -10739,7 +10731,7 @@
         <v>391</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D71" s="32" t="s">
         <v>630</v>
@@ -10772,13 +10764,13 @@
         <v>83</v>
       </c>
       <c r="N71" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O71" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P71" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q71" s="35" t="s">
         <v>703</v>
@@ -10810,7 +10802,7 @@
         <v>392</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D72" s="32" t="s">
         <v>630</v>
@@ -10843,13 +10835,13 @@
         <v>84</v>
       </c>
       <c r="N72" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O72" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P72" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q72" s="35" t="s">
         <v>703</v>
@@ -10881,7 +10873,7 @@
         <v>393</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D73" s="32" t="s">
         <v>630</v>
@@ -10914,13 +10906,13 @@
         <v>85</v>
       </c>
       <c r="N73" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O73" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P73" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q73" s="35" t="s">
         <v>703</v>
@@ -10952,7 +10944,7 @@
         <v>394</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D74" s="32" t="s">
         <v>630</v>
@@ -10985,13 +10977,13 @@
         <v>86</v>
       </c>
       <c r="N74" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O74" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P74" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q74" s="35" t="s">
         <v>703</v>
@@ -11023,7 +11015,7 @@
         <v>395</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D75" s="32" t="s">
         <v>630</v>
@@ -11056,13 +11048,13 @@
         <v>87</v>
       </c>
       <c r="N75" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O75" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P75" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q75" s="35" t="s">
         <v>703</v>
@@ -11094,7 +11086,7 @@
         <v>396</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D76" s="32" t="s">
         <v>630</v>
@@ -11127,13 +11119,13 @@
         <v>88</v>
       </c>
       <c r="N76" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O76" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P76" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q76" s="35" t="s">
         <v>703</v>
@@ -11165,7 +11157,7 @@
         <v>397</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D77" s="32" t="s">
         <v>630</v>
@@ -11198,13 +11190,13 @@
         <v>89</v>
       </c>
       <c r="N77" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O77" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P77" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q77" s="35" t="s">
         <v>703</v>
@@ -11236,7 +11228,7 @@
         <v>398</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D78" s="32" t="s">
         <v>630</v>
@@ -11269,13 +11261,13 @@
         <v>90</v>
       </c>
       <c r="N78" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O78" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P78" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q78" s="35" t="s">
         <v>703</v>
@@ -11307,7 +11299,7 @@
         <v>399</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D79" s="32" t="s">
         <v>630</v>
@@ -11340,13 +11332,13 @@
         <v>91</v>
       </c>
       <c r="N79" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O79" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P79" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q79" s="35" t="s">
         <v>703</v>
@@ -11378,7 +11370,7 @@
         <v>400</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D80" s="32" t="s">
         <v>630</v>
@@ -11411,13 +11403,13 @@
         <v>92</v>
       </c>
       <c r="N80" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O80" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P80" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q80" s="35" t="s">
         <v>703</v>
@@ -11449,7 +11441,7 @@
         <v>401</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D81" s="32" t="s">
         <v>630</v>
@@ -11482,13 +11474,13 @@
         <v>93</v>
       </c>
       <c r="N81" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O81" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P81" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q81" s="35" t="s">
         <v>703</v>
@@ -11520,7 +11512,7 @@
         <v>402</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D82" s="32" t="s">
         <v>630</v>
@@ -11553,13 +11545,13 @@
         <v>94</v>
       </c>
       <c r="N82" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O82" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P82" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q82" s="35" t="s">
         <v>703</v>
@@ -11591,7 +11583,7 @@
         <v>403</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D83" s="32" t="s">
         <v>630</v>
@@ -11624,13 +11616,13 @@
         <v>95</v>
       </c>
       <c r="N83" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O83" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P83" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q83" s="35" t="s">
         <v>703</v>
@@ -11662,7 +11654,7 @@
         <v>404</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D84" s="32" t="s">
         <v>630</v>
@@ -11695,13 +11687,13 @@
         <v>96</v>
       </c>
       <c r="N84" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O84" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P84" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q84" s="35" t="s">
         <v>703</v>
@@ -11733,7 +11725,7 @@
         <v>405</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D85" s="32" t="s">
         <v>630</v>
@@ -11766,13 +11758,13 @@
         <v>97</v>
       </c>
       <c r="N85" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O85" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P85" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q85" s="35" t="s">
         <v>703</v>
@@ -11804,7 +11796,7 @@
         <v>406</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D86" s="32" t="s">
         <v>630</v>
@@ -11837,13 +11829,13 @@
         <v>98</v>
       </c>
       <c r="N86" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O86" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P86" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q86" s="35" t="s">
         <v>703</v>
@@ -11875,7 +11867,7 @@
         <v>407</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D87" s="32" t="s">
         <v>630</v>
@@ -11908,13 +11900,13 @@
         <v>99</v>
       </c>
       <c r="N87" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O87" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P87" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q87" s="35" t="s">
         <v>703</v>
@@ -11946,7 +11938,7 @@
         <v>408</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D88" s="32" t="s">
         <v>630</v>
@@ -11979,13 +11971,13 @@
         <v>100</v>
       </c>
       <c r="N88" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O88" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P88" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q88" s="35" t="s">
         <v>703</v>
@@ -12017,7 +12009,7 @@
         <v>409</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D89" s="32" t="s">
         <v>630</v>
@@ -12050,13 +12042,13 @@
         <v>101</v>
       </c>
       <c r="N89" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O89" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P89" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q89" s="35" t="s">
         <v>703</v>
@@ -12088,7 +12080,7 @@
         <v>410</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D90" s="32" t="s">
         <v>630</v>
@@ -12121,13 +12113,13 @@
         <v>102</v>
       </c>
       <c r="N90" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O90" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P90" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q90" s="35" t="s">
         <v>703</v>
@@ -12159,7 +12151,7 @@
         <v>411</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D91" s="32" t="s">
         <v>630</v>
@@ -12192,13 +12184,13 @@
         <v>103</v>
       </c>
       <c r="N91" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O91" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P91" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q91" s="35" t="s">
         <v>703</v>
@@ -12230,7 +12222,7 @@
         <v>412</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D92" s="32" t="s">
         <v>630</v>
@@ -12263,13 +12255,13 @@
         <v>104</v>
       </c>
       <c r="N92" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O92" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P92" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q92" s="35" t="s">
         <v>703</v>
@@ -12301,7 +12293,7 @@
         <v>413</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D93" s="32" t="s">
         <v>630</v>
@@ -12334,13 +12326,13 @@
         <v>105</v>
       </c>
       <c r="N93" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O93" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P93" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q93" s="35" t="s">
         <v>703</v>
@@ -12372,7 +12364,7 @@
         <v>414</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D94" s="32" t="s">
         <v>630</v>
@@ -12405,13 +12397,13 @@
         <v>106</v>
       </c>
       <c r="N94" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O94" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P94" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q94" s="35" t="s">
         <v>703</v>
@@ -12443,7 +12435,7 @@
         <v>415</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D95" s="32" t="s">
         <v>630</v>
@@ -12476,13 +12468,13 @@
         <v>107</v>
       </c>
       <c r="N95" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O95" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P95" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q95" s="35" t="s">
         <v>703</v>
@@ -12514,7 +12506,7 @@
         <v>416</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D96" s="32" t="s">
         <v>630</v>
@@ -12547,13 +12539,13 @@
         <v>108</v>
       </c>
       <c r="N96" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O96" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P96" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q96" s="35" t="s">
         <v>703</v>
@@ -12585,7 +12577,7 @@
         <v>417</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D97" s="32" t="s">
         <v>630</v>
@@ -12618,13 +12610,13 @@
         <v>109</v>
       </c>
       <c r="N97" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O97" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P97" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q97" s="35" t="s">
         <v>703</v>
@@ -12656,7 +12648,7 @@
         <v>418</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D98" s="32" t="s">
         <v>630</v>
@@ -12689,13 +12681,13 @@
         <v>110</v>
       </c>
       <c r="N98" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O98" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P98" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q98" s="35" t="s">
         <v>703</v>
@@ -12727,7 +12719,7 @@
         <v>419</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D99" s="32" t="s">
         <v>630</v>
@@ -12760,13 +12752,13 @@
         <v>111</v>
       </c>
       <c r="N99" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O99" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P99" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q99" s="35" t="s">
         <v>703</v>
@@ -12798,7 +12790,7 @@
         <v>420</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D100" s="32" t="s">
         <v>630</v>
@@ -12831,13 +12823,13 @@
         <v>112</v>
       </c>
       <c r="N100" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O100" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P100" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q100" s="35" t="s">
         <v>703</v>
@@ -12869,7 +12861,7 @@
         <v>421</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D101" s="32" t="s">
         <v>630</v>
@@ -12902,13 +12894,13 @@
         <v>113</v>
       </c>
       <c r="N101" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O101" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P101" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q101" s="35" t="s">
         <v>703</v>
@@ -12940,7 +12932,7 @@
         <v>422</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D102" s="32" t="s">
         <v>630</v>
@@ -12973,13 +12965,13 @@
         <v>114</v>
       </c>
       <c r="N102" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O102" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P102" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q102" s="35" t="s">
         <v>703</v>
@@ -13011,7 +13003,7 @@
         <v>423</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D103" s="32" t="s">
         <v>630</v>
@@ -13044,13 +13036,13 @@
         <v>115</v>
       </c>
       <c r="N103" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O103" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P103" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q103" s="35" t="s">
         <v>703</v>
@@ -13082,7 +13074,7 @@
         <v>424</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D104" s="32" t="s">
         <v>630</v>
@@ -13115,13 +13107,13 @@
         <v>116</v>
       </c>
       <c r="N104" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O104" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P104" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q104" s="35" t="s">
         <v>703</v>
@@ -13153,7 +13145,7 @@
         <v>425</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D105" s="32" t="s">
         <v>630</v>
@@ -13186,13 +13178,13 @@
         <v>117</v>
       </c>
       <c r="N105" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O105" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P105" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q105" s="35" t="s">
         <v>703</v>
@@ -13224,7 +13216,7 @@
         <v>426</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D106" s="32" t="s">
         <v>630</v>
@@ -13257,13 +13249,13 @@
         <v>118</v>
       </c>
       <c r="N106" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O106" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P106" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q106" s="35" t="s">
         <v>703</v>
@@ -13295,7 +13287,7 @@
         <v>427</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D107" s="32" t="s">
         <v>630</v>
@@ -13328,13 +13320,13 @@
         <v>119</v>
       </c>
       <c r="N107" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O107" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P107" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q107" s="35" t="s">
         <v>703</v>
@@ -13366,7 +13358,7 @@
         <v>428</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D108" s="32" t="s">
         <v>630</v>
@@ -13399,13 +13391,13 @@
         <v>50</v>
       </c>
       <c r="N108" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O108" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P108" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q108" s="35" t="s">
         <v>703</v>
@@ -13437,7 +13429,7 @@
         <v>429</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D109" s="32" t="s">
         <v>630</v>
@@ -13470,13 +13462,13 @@
         <v>120</v>
       </c>
       <c r="N109" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O109" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P109" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q109" s="35" t="s">
         <v>703</v>
@@ -13508,7 +13500,7 @@
         <v>430</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D110" s="32" t="s">
         <v>630</v>
@@ -13541,13 +13533,13 @@
         <v>121</v>
       </c>
       <c r="N110" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O110" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P110" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q110" s="35" t="s">
         <v>703</v>
@@ -13579,7 +13571,7 @@
         <v>431</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D111" s="32" t="s">
         <v>630</v>
@@ -13612,13 +13604,13 @@
         <v>122</v>
       </c>
       <c r="N111" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O111" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P111" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q111" s="35" t="s">
         <v>703</v>
@@ -13650,7 +13642,7 @@
         <v>432</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D112" s="32" t="s">
         <v>630</v>
@@ -13683,13 +13675,13 @@
         <v>123</v>
       </c>
       <c r="N112" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O112" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P112" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q112" s="35" t="s">
         <v>703</v>
@@ -13721,7 +13713,7 @@
         <v>433</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D113" s="32" t="s">
         <v>630</v>
@@ -13754,13 +13746,13 @@
         <v>124</v>
       </c>
       <c r="N113" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O113" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P113" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q113" s="35" t="s">
         <v>703</v>
@@ -13792,7 +13784,7 @@
         <v>434</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D114" s="32" t="s">
         <v>630</v>
@@ -13825,13 +13817,13 @@
         <v>125</v>
       </c>
       <c r="N114" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O114" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P114" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q114" s="35" t="s">
         <v>703</v>
@@ -13863,7 +13855,7 @@
         <v>435</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D115" s="32" t="s">
         <v>630</v>
@@ -13896,13 +13888,13 @@
         <v>126</v>
       </c>
       <c r="N115" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O115" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P115" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q115" s="35" t="s">
         <v>703</v>
@@ -13934,7 +13926,7 @@
         <v>436</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D116" s="32" t="s">
         <v>630</v>
@@ -13967,13 +13959,13 @@
         <v>127</v>
       </c>
       <c r="N116" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O116" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P116" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q116" s="35" t="s">
         <v>703</v>
@@ -14005,7 +13997,7 @@
         <v>437</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D117" s="32" t="s">
         <v>630</v>
@@ -14038,13 +14030,13 @@
         <v>128</v>
       </c>
       <c r="N117" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O117" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P117" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q117" s="35" t="s">
         <v>703</v>
@@ -14076,7 +14068,7 @@
         <v>438</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D118" s="32" t="s">
         <v>630</v>
@@ -14109,13 +14101,13 @@
         <v>129</v>
       </c>
       <c r="N118" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O118" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P118" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q118" s="35" t="s">
         <v>703</v>
@@ -14147,7 +14139,7 @@
         <v>439</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D119" s="32" t="s">
         <v>630</v>
@@ -14180,13 +14172,13 @@
         <v>27</v>
       </c>
       <c r="N119" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O119" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P119" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q119" s="35" t="s">
         <v>703</v>
@@ -14218,7 +14210,7 @@
         <v>440</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D120" s="32" t="s">
         <v>630</v>
@@ -14251,13 +14243,13 @@
         <v>130</v>
       </c>
       <c r="N120" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O120" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P120" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q120" s="35" t="s">
         <v>703</v>
@@ -14286,10 +14278,10 @@
         <v>121</v>
       </c>
       <c r="B121" s="47" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D121" s="32" t="s">
         <v>630</v>
@@ -14322,13 +14314,13 @@
         <v>131</v>
       </c>
       <c r="N121" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O121" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P121" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q121" s="35" t="s">
         <v>703</v>
@@ -14360,7 +14352,7 @@
         <v>441</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D122" s="32" t="s">
         <v>630</v>
@@ -14393,13 +14385,13 @@
         <v>132</v>
       </c>
       <c r="N122" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O122" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P122" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q122" s="35" t="s">
         <v>703</v>
@@ -14431,7 +14423,7 @@
         <v>442</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D123" s="32" t="s">
         <v>630</v>
@@ -14464,13 +14456,13 @@
         <v>133</v>
       </c>
       <c r="N123" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O123" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P123" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q123" s="35" t="s">
         <v>703</v>
@@ -14502,7 +14494,7 @@
         <v>443</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D124" s="32" t="s">
         <v>630</v>
@@ -14535,13 +14527,13 @@
         <v>134</v>
       </c>
       <c r="N124" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O124" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P124" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q124" s="35" t="s">
         <v>703</v>
@@ -14573,7 +14565,7 @@
         <v>444</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D125" s="32" t="s">
         <v>630</v>
@@ -14606,13 +14598,13 @@
         <v>135</v>
       </c>
       <c r="N125" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O125" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P125" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q125" s="35" t="s">
         <v>703</v>
@@ -14644,7 +14636,7 @@
         <v>445</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D126" s="32" t="s">
         <v>630</v>
@@ -14677,13 +14669,13 @@
         <v>136</v>
       </c>
       <c r="N126" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O126" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P126" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q126" s="35" t="s">
         <v>703</v>
@@ -14715,7 +14707,7 @@
         <v>446</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D127" s="32" t="s">
         <v>630</v>
@@ -14748,13 +14740,13 @@
         <v>137</v>
       </c>
       <c r="N127" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O127" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P127" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q127" s="35" t="s">
         <v>703</v>
@@ -14786,7 +14778,7 @@
         <v>447</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D128" s="32" t="s">
         <v>630</v>
@@ -14819,13 +14811,13 @@
         <v>138</v>
       </c>
       <c r="N128" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O128" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P128" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q128" s="35" t="s">
         <v>703</v>
@@ -14857,7 +14849,7 @@
         <v>448</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D129" s="32" t="s">
         <v>630</v>
@@ -14890,13 +14882,13 @@
         <v>139</v>
       </c>
       <c r="N129" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O129" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P129" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q129" s="35" t="s">
         <v>703</v>
@@ -14928,7 +14920,7 @@
         <v>449</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D130" s="32" t="s">
         <v>630</v>
@@ -14961,13 +14953,13 @@
         <v>140</v>
       </c>
       <c r="N130" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O130" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P130" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q130" s="35" t="s">
         <v>703</v>
@@ -14999,7 +14991,7 @@
         <v>450</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D131" s="32" t="s">
         <v>630</v>
@@ -15032,13 +15024,13 @@
         <v>141</v>
       </c>
       <c r="N131" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O131" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P131" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q131" s="35" t="s">
         <v>703</v>
@@ -15070,7 +15062,7 @@
         <v>451</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D132" s="32" t="s">
         <v>630</v>
@@ -15103,13 +15095,13 @@
         <v>142</v>
       </c>
       <c r="N132" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O132" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P132" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q132" s="35" t="s">
         <v>703</v>
@@ -15141,7 +15133,7 @@
         <v>452</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D133" s="32" t="s">
         <v>630</v>
@@ -15174,13 +15166,13 @@
         <v>143</v>
       </c>
       <c r="N133" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O133" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P133" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q133" s="35" t="s">
         <v>703</v>
@@ -15212,7 +15204,7 @@
         <v>453</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D134" s="32" t="s">
         <v>630</v>
@@ -15245,13 +15237,13 @@
         <v>144</v>
       </c>
       <c r="N134" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O134" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P134" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q134" s="35" t="s">
         <v>703</v>
@@ -15283,7 +15275,7 @@
         <v>454</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D135" s="32" t="s">
         <v>630</v>
@@ -15316,13 +15308,13 @@
         <v>145</v>
       </c>
       <c r="N135" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O135" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P135" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q135" s="35" t="s">
         <v>703</v>
@@ -15354,7 +15346,7 @@
         <v>455</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D136" s="32" t="s">
         <v>630</v>
@@ -15387,13 +15379,13 @@
         <v>146</v>
       </c>
       <c r="N136" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O136" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P136" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q136" s="35" t="s">
         <v>703</v>
@@ -15425,7 +15417,7 @@
         <v>456</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D137" s="32" t="s">
         <v>630</v>
@@ -15458,13 +15450,13 @@
         <v>147</v>
       </c>
       <c r="N137" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O137" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P137" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q137" s="35" t="s">
         <v>703</v>
@@ -15496,7 +15488,7 @@
         <v>457</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D138" s="32" t="s">
         <v>630</v>
@@ -15529,13 +15521,13 @@
         <v>148</v>
       </c>
       <c r="N138" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O138" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P138" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q138" s="35" t="s">
         <v>703</v>
@@ -15567,7 +15559,7 @@
         <v>458</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D139" s="32" t="s">
         <v>630</v>
@@ -15600,13 +15592,13 @@
         <v>149</v>
       </c>
       <c r="N139" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O139" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P139" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q139" s="35" t="s">
         <v>703</v>
@@ -15638,7 +15630,7 @@
         <v>459</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D140" s="32" t="s">
         <v>630</v>
@@ -15671,13 +15663,13 @@
         <v>150</v>
       </c>
       <c r="N140" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O140" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P140" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q140" s="35" t="s">
         <v>703</v>
@@ -15709,7 +15701,7 @@
         <v>460</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D141" s="32" t="s">
         <v>630</v>
@@ -15742,13 +15734,13 @@
         <v>151</v>
       </c>
       <c r="N141" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O141" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P141" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q141" s="35" t="s">
         <v>703</v>
@@ -15780,7 +15772,7 @@
         <v>461</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D142" s="32" t="s">
         <v>630</v>
@@ -15813,13 +15805,13 @@
         <v>152</v>
       </c>
       <c r="N142" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O142" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P142" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q142" s="35" t="s">
         <v>703</v>
@@ -15851,7 +15843,7 @@
         <v>462</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D143" s="32" t="s">
         <v>630</v>
@@ -15884,13 +15876,13 @@
         <v>153</v>
       </c>
       <c r="N143" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O143" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P143" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q143" s="35" t="s">
         <v>703</v>
@@ -15922,7 +15914,7 @@
         <v>463</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D144" s="32" t="s">
         <v>630</v>
@@ -15955,13 +15947,13 @@
         <v>154</v>
       </c>
       <c r="N144" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O144" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P144" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q144" s="35" t="s">
         <v>703</v>
@@ -15993,7 +15985,7 @@
         <v>464</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D145" s="32" t="s">
         <v>630</v>
@@ -16026,13 +16018,13 @@
         <v>155</v>
       </c>
       <c r="N145" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O145" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P145" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q145" s="35" t="s">
         <v>703</v>
@@ -16064,7 +16056,7 @@
         <v>465</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D146" s="32" t="s">
         <v>630</v>
@@ -16097,13 +16089,13 @@
         <v>156</v>
       </c>
       <c r="N146" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O146" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P146" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q146" s="35" t="s">
         <v>703</v>
@@ -16135,7 +16127,7 @@
         <v>466</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D147" s="32" t="s">
         <v>630</v>
@@ -16168,13 +16160,13 @@
         <v>157</v>
       </c>
       <c r="N147" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O147" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P147" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q147" s="35" t="s">
         <v>703</v>
@@ -16206,7 +16198,7 @@
         <v>467</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D148" s="32" t="s">
         <v>630</v>
@@ -16239,13 +16231,13 @@
         <v>158</v>
       </c>
       <c r="N148" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O148" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P148" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q148" s="35" t="s">
         <v>703</v>
@@ -16277,7 +16269,7 @@
         <v>468</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D149" s="32" t="s">
         <v>630</v>
@@ -16310,13 +16302,13 @@
         <v>159</v>
       </c>
       <c r="N149" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O149" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P149" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q149" s="35" t="s">
         <v>703</v>
@@ -16348,7 +16340,7 @@
         <v>469</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D150" s="32" t="s">
         <v>630</v>
@@ -16381,13 +16373,13 @@
         <v>160</v>
       </c>
       <c r="N150" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O150" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P150" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q150" s="35" t="s">
         <v>703</v>
@@ -16419,7 +16411,7 @@
         <v>470</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D151" s="32" t="s">
         <v>630</v>
@@ -16452,13 +16444,13 @@
         <v>161</v>
       </c>
       <c r="N151" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O151" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P151" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q151" s="35" t="s">
         <v>703</v>
@@ -16490,7 +16482,7 @@
         <v>471</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D152" s="32" t="s">
         <v>630</v>
@@ -16523,13 +16515,13 @@
         <v>162</v>
       </c>
       <c r="N152" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O152" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P152" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q152" s="35" t="s">
         <v>703</v>
@@ -16561,7 +16553,7 @@
         <v>472</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D153" s="32" t="s">
         <v>630</v>
@@ -16594,13 +16586,13 @@
         <v>163</v>
       </c>
       <c r="N153" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O153" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P153" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q153" s="35" t="s">
         <v>703</v>
@@ -16632,7 +16624,7 @@
         <v>473</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D154" s="32" t="s">
         <v>630</v>
@@ -16665,13 +16657,13 @@
         <v>164</v>
       </c>
       <c r="N154" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O154" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P154" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q154" s="35" t="s">
         <v>703</v>
@@ -16703,7 +16695,7 @@
         <v>474</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D155" s="32" t="s">
         <v>630</v>
@@ -16736,13 +16728,13 @@
         <v>165</v>
       </c>
       <c r="N155" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O155" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P155" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q155" s="35" t="s">
         <v>703</v>
@@ -16774,7 +16766,7 @@
         <v>475</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D156" s="32" t="s">
         <v>630</v>
@@ -16807,13 +16799,13 @@
         <v>81</v>
       </c>
       <c r="N156" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O156" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P156" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q156" s="35" t="s">
         <v>703</v>
@@ -16845,7 +16837,7 @@
         <v>476</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D157" s="32" t="s">
         <v>630</v>
@@ -16878,13 +16870,13 @@
         <v>166</v>
       </c>
       <c r="N157" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O157" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P157" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q157" s="35" t="s">
         <v>703</v>
@@ -16916,7 +16908,7 @@
         <v>477</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D158" s="32" t="s">
         <v>630</v>
@@ -16949,13 +16941,13 @@
         <v>167</v>
       </c>
       <c r="N158" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O158" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P158" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q158" s="35" t="s">
         <v>703</v>
@@ -16987,7 +16979,7 @@
         <v>478</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D159" s="32" t="s">
         <v>630</v>
@@ -17020,13 +17012,13 @@
         <v>168</v>
       </c>
       <c r="N159" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O159" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P159" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q159" s="35" t="s">
         <v>703</v>
@@ -17058,7 +17050,7 @@
         <v>479</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D160" s="32" t="s">
         <v>630</v>
@@ -17091,13 +17083,13 @@
         <v>169</v>
       </c>
       <c r="N160" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O160" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P160" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q160" s="35" t="s">
         <v>703</v>
@@ -17129,7 +17121,7 @@
         <v>480</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D161" s="32" t="s">
         <v>630</v>
@@ -17162,13 +17154,13 @@
         <v>170</v>
       </c>
       <c r="N161" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O161" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P161" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q161" s="35" t="s">
         <v>703</v>
@@ -17200,7 +17192,7 @@
         <v>481</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D162" s="32" t="s">
         <v>630</v>
@@ -17233,13 +17225,13 @@
         <v>171</v>
       </c>
       <c r="N162" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O162" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P162" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q162" s="35" t="s">
         <v>703</v>
@@ -17271,7 +17263,7 @@
         <v>482</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D163" s="32" t="s">
         <v>630</v>
@@ -17304,13 +17296,13 @@
         <v>172</v>
       </c>
       <c r="N163" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O163" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P163" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q163" s="35" t="s">
         <v>703</v>
@@ -17342,7 +17334,7 @@
         <v>483</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D164" s="32" t="s">
         <v>630</v>
@@ -17375,13 +17367,13 @@
         <v>173</v>
       </c>
       <c r="N164" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O164" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P164" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q164" s="35" t="s">
         <v>703</v>
@@ -17413,7 +17405,7 @@
         <v>484</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D165" s="32" t="s">
         <v>630</v>
@@ -17446,13 +17438,13 @@
         <v>170</v>
       </c>
       <c r="N165" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O165" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P165" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q165" s="35" t="s">
         <v>703</v>
@@ -17484,7 +17476,7 @@
         <v>485</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D166" s="32" t="s">
         <v>630</v>
@@ -17517,13 +17509,13 @@
         <v>174</v>
       </c>
       <c r="N166" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O166" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P166" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q166" s="35" t="s">
         <v>703</v>
@@ -17555,7 +17547,7 @@
         <v>486</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D167" s="32" t="s">
         <v>630</v>
@@ -17588,13 +17580,13 @@
         <v>175</v>
       </c>
       <c r="N167" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O167" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P167" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q167" s="35" t="s">
         <v>703</v>
@@ -17626,7 +17618,7 @@
         <v>487</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D168" s="32" t="s">
         <v>630</v>
@@ -17659,13 +17651,13 @@
         <v>176</v>
       </c>
       <c r="N168" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O168" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P168" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q168" s="35" t="s">
         <v>703</v>
@@ -17697,7 +17689,7 @@
         <v>488</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D169" s="32" t="s">
         <v>630</v>
@@ -17730,13 +17722,13 @@
         <v>177</v>
       </c>
       <c r="N169" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O169" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P169" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q169" s="35" t="s">
         <v>703</v>
@@ -17768,7 +17760,7 @@
         <v>489</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D170" s="32" t="s">
         <v>630</v>
@@ -17801,13 +17793,13 @@
         <v>178</v>
       </c>
       <c r="N170" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O170" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P170" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q170" s="35" t="s">
         <v>703</v>
@@ -17839,7 +17831,7 @@
         <v>490</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D171" s="32" t="s">
         <v>630</v>
@@ -17872,13 +17864,13 @@
         <v>179</v>
       </c>
       <c r="N171" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O171" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P171" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q171" s="35" t="s">
         <v>703</v>
@@ -17910,7 +17902,7 @@
         <v>491</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D172" s="32" t="s">
         <v>630</v>
@@ -17943,13 +17935,13 @@
         <v>180</v>
       </c>
       <c r="N172" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O172" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P172" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q172" s="35" t="s">
         <v>703</v>
@@ -17981,7 +17973,7 @@
         <v>492</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D173" s="32" t="s">
         <v>630</v>
@@ -18014,13 +18006,13 @@
         <v>181</v>
       </c>
       <c r="N173" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O173" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P173" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q173" s="35" t="s">
         <v>703</v>
@@ -18052,7 +18044,7 @@
         <v>493</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D174" s="32" t="s">
         <v>630</v>
@@ -18085,13 +18077,13 @@
         <v>182</v>
       </c>
       <c r="N174" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O174" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P174" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q174" s="35" t="s">
         <v>703</v>
@@ -18123,7 +18115,7 @@
         <v>494</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D175" s="32" t="s">
         <v>630</v>
@@ -18156,13 +18148,13 @@
         <v>183</v>
       </c>
       <c r="N175" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O175" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P175" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q175" s="35" t="s">
         <v>703</v>
@@ -18194,7 +18186,7 @@
         <v>495</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D176" s="32" t="s">
         <v>630</v>
@@ -18227,13 +18219,13 @@
         <v>139</v>
       </c>
       <c r="N176" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O176" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P176" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q176" s="35" t="s">
         <v>703</v>
@@ -18265,7 +18257,7 @@
         <v>496</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D177" s="32" t="s">
         <v>630</v>
@@ -18298,13 +18290,13 @@
         <v>184</v>
       </c>
       <c r="N177" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O177" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P177" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q177" s="35" t="s">
         <v>703</v>
@@ -18336,7 +18328,7 @@
         <v>497</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D178" s="32" t="s">
         <v>630</v>
@@ -18369,13 +18361,13 @@
         <v>185</v>
       </c>
       <c r="N178" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O178" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P178" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q178" s="35" t="s">
         <v>703</v>
@@ -18407,7 +18399,7 @@
         <v>498</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D179" s="32" t="s">
         <v>630</v>
@@ -18440,13 +18432,13 @@
         <v>186</v>
       </c>
       <c r="N179" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O179" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P179" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q179" s="35" t="s">
         <v>703</v>
@@ -18478,7 +18470,7 @@
         <v>499</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D180" s="32" t="s">
         <v>630</v>
@@ -18511,13 +18503,13 @@
         <v>187</v>
       </c>
       <c r="N180" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O180" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P180" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q180" s="35" t="s">
         <v>703</v>
@@ -18549,7 +18541,7 @@
         <v>500</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D181" s="32" t="s">
         <v>630</v>
@@ -18582,13 +18574,13 @@
         <v>188</v>
       </c>
       <c r="N181" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O181" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P181" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q181" s="35" t="s">
         <v>703</v>
@@ -18620,7 +18612,7 @@
         <v>501</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D182" s="32" t="s">
         <v>630</v>
@@ -18653,13 +18645,13 @@
         <v>189</v>
       </c>
       <c r="N182" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O182" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P182" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q182" s="35" t="s">
         <v>703</v>
@@ -18691,7 +18683,7 @@
         <v>502</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D183" s="32" t="s">
         <v>630</v>
@@ -18724,13 +18716,13 @@
         <v>190</v>
       </c>
       <c r="N183" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O183" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P183" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q183" s="35" t="s">
         <v>703</v>
@@ -18762,7 +18754,7 @@
         <v>503</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D184" s="32" t="s">
         <v>630</v>
@@ -18795,13 +18787,13 @@
         <v>191</v>
       </c>
       <c r="N184" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O184" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P184" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q184" s="35" t="s">
         <v>703</v>
@@ -18833,7 +18825,7 @@
         <v>504</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D185" s="32" t="s">
         <v>630</v>
@@ -18866,13 +18858,13 @@
         <v>192</v>
       </c>
       <c r="N185" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O185" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P185" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q185" s="35" t="s">
         <v>703</v>
@@ -18904,7 +18896,7 @@
         <v>505</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D186" s="32" t="s">
         <v>630</v>
@@ -18937,13 +18929,13 @@
         <v>193</v>
       </c>
       <c r="N186" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O186" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P186" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q186" s="35" t="s">
         <v>703</v>
@@ -18975,7 +18967,7 @@
         <v>506</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D187" s="32" t="s">
         <v>630</v>
@@ -19008,13 +19000,13 @@
         <v>194</v>
       </c>
       <c r="N187" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O187" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P187" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q187" s="35" t="s">
         <v>703</v>
@@ -19046,7 +19038,7 @@
         <v>507</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D188" s="32" t="s">
         <v>630</v>
@@ -19079,13 +19071,13 @@
         <v>195</v>
       </c>
       <c r="N188" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O188" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P188" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q188" s="35" t="s">
         <v>703</v>
@@ -19117,7 +19109,7 @@
         <v>508</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D189" s="32" t="s">
         <v>630</v>
@@ -19150,13 +19142,13 @@
         <v>196</v>
       </c>
       <c r="N189" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O189" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P189" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q189" s="35" t="s">
         <v>703</v>
@@ -19188,7 +19180,7 @@
         <v>509</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D190" s="32" t="s">
         <v>630</v>
@@ -19221,13 +19213,13 @@
         <v>197</v>
       </c>
       <c r="N190" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O190" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P190" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q190" s="35" t="s">
         <v>703</v>
@@ -19259,7 +19251,7 @@
         <v>510</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D191" s="32" t="s">
         <v>630</v>
@@ -19292,13 +19284,13 @@
         <v>198</v>
       </c>
       <c r="N191" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O191" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P191" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q191" s="35" t="s">
         <v>703</v>
@@ -19330,7 +19322,7 @@
         <v>511</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D192" s="32" t="s">
         <v>630</v>
@@ -19363,13 +19355,13 @@
         <v>199</v>
       </c>
       <c r="N192" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O192" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P192" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q192" s="35" t="s">
         <v>703</v>
@@ -19401,7 +19393,7 @@
         <v>512</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D193" s="32" t="s">
         <v>630</v>
@@ -19434,13 +19426,13 @@
         <v>200</v>
       </c>
       <c r="N193" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O193" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P193" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q193" s="35" t="s">
         <v>703</v>
@@ -19472,7 +19464,7 @@
         <v>513</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D194" s="32" t="s">
         <v>630</v>
@@ -19505,13 +19497,13 @@
         <v>201</v>
       </c>
       <c r="N194" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O194" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P194" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q194" s="35" t="s">
         <v>703</v>
@@ -19543,7 +19535,7 @@
         <v>514</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D195" s="32" t="s">
         <v>630</v>
@@ -19576,13 +19568,13 @@
         <v>202</v>
       </c>
       <c r="N195" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O195" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P195" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q195" s="35" t="s">
         <v>703</v>
@@ -19614,7 +19606,7 @@
         <v>515</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D196" s="32" t="s">
         <v>630</v>
@@ -19647,13 +19639,13 @@
         <v>203</v>
       </c>
       <c r="N196" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O196" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P196" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q196" s="35" t="s">
         <v>703</v>
@@ -19685,7 +19677,7 @@
         <v>516</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D197" s="32" t="s">
         <v>630</v>
@@ -19718,13 +19710,13 @@
         <v>204</v>
       </c>
       <c r="N197" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O197" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P197" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q197" s="35" t="s">
         <v>703</v>
@@ -19756,7 +19748,7 @@
         <v>517</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D198" s="32" t="s">
         <v>630</v>
@@ -19789,13 +19781,13 @@
         <v>205</v>
       </c>
       <c r="N198" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O198" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P198" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q198" s="35" t="s">
         <v>703</v>
@@ -19827,7 +19819,7 @@
         <v>518</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D199" s="32" t="s">
         <v>630</v>
@@ -19860,13 +19852,13 @@
         <v>109</v>
       </c>
       <c r="N199" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O199" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P199" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q199" s="35" t="s">
         <v>703</v>
@@ -19898,7 +19890,7 @@
         <v>519</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D200" s="32" t="s">
         <v>630</v>
@@ -19931,13 +19923,13 @@
         <v>206</v>
       </c>
       <c r="N200" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O200" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P200" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q200" s="35" t="s">
         <v>703</v>
@@ -19969,7 +19961,7 @@
         <v>520</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D201" s="32" t="s">
         <v>630</v>
@@ -20002,13 +19994,13 @@
         <v>207</v>
       </c>
       <c r="N201" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O201" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P201" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q201" s="35" t="s">
         <v>703</v>
@@ -20040,7 +20032,7 @@
         <v>521</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D202" s="32" t="s">
         <v>630</v>
@@ -20073,13 +20065,13 @@
         <v>208</v>
       </c>
       <c r="N202" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O202" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P202" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q202" s="35" t="s">
         <v>703</v>
@@ -20111,7 +20103,7 @@
         <v>522</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D203" s="32" t="s">
         <v>630</v>
@@ -20144,13 +20136,13 @@
         <v>209</v>
       </c>
       <c r="N203" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O203" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P203" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q203" s="35" t="s">
         <v>703</v>
@@ -20182,7 +20174,7 @@
         <v>523</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D204" s="32" t="s">
         <v>630</v>
@@ -20215,13 +20207,13 @@
         <v>210</v>
       </c>
       <c r="N204" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O204" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P204" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q204" s="35" t="s">
         <v>703</v>
@@ -20253,7 +20245,7 @@
         <v>524</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D205" s="32" t="s">
         <v>630</v>
@@ -20286,13 +20278,13 @@
         <v>117</v>
       </c>
       <c r="N205" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O205" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P205" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q205" s="35" t="s">
         <v>703</v>
@@ -20324,7 +20316,7 @@
         <v>525</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D206" s="32" t="s">
         <v>630</v>
@@ -20357,13 +20349,13 @@
         <v>180</v>
       </c>
       <c r="N206" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O206" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P206" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q206" s="35" t="s">
         <v>703</v>
@@ -20395,7 +20387,7 @@
         <v>526</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D207" s="32" t="s">
         <v>630</v>
@@ -20428,13 +20420,13 @@
         <v>211</v>
       </c>
       <c r="N207" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O207" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P207" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q207" s="35" t="s">
         <v>703</v>
@@ -20466,7 +20458,7 @@
         <v>527</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D208" s="32" t="s">
         <v>630</v>
@@ -20499,13 +20491,13 @@
         <v>212</v>
       </c>
       <c r="N208" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O208" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P208" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q208" s="35" t="s">
         <v>703</v>
@@ -20537,7 +20529,7 @@
         <v>528</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D209" s="32" t="s">
         <v>630</v>
@@ -20570,13 +20562,13 @@
         <v>213</v>
       </c>
       <c r="N209" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O209" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P209" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q209" s="35" t="s">
         <v>703</v>
@@ -20608,7 +20600,7 @@
         <v>529</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D210" s="32" t="s">
         <v>630</v>
@@ -20641,13 +20633,13 @@
         <v>214</v>
       </c>
       <c r="N210" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O210" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P210" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q210" s="35" t="s">
         <v>703</v>
@@ -20679,7 +20671,7 @@
         <v>530</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D211" s="32" t="s">
         <v>630</v>
@@ -20712,13 +20704,13 @@
         <v>215</v>
       </c>
       <c r="N211" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O211" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P211" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q211" s="35" t="s">
         <v>703</v>
@@ -20750,7 +20742,7 @@
         <v>531</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D212" s="32" t="s">
         <v>630</v>
@@ -20783,13 +20775,13 @@
         <v>216</v>
       </c>
       <c r="N212" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O212" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P212" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q212" s="35" t="s">
         <v>703</v>
@@ -20821,7 +20813,7 @@
         <v>532</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D213" s="32" t="s">
         <v>630</v>
@@ -20854,13 +20846,13 @@
         <v>217</v>
       </c>
       <c r="N213" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O213" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P213" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q213" s="35" t="s">
         <v>703</v>
@@ -20892,7 +20884,7 @@
         <v>533</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D214" s="32" t="s">
         <v>630</v>
@@ -20925,13 +20917,13 @@
         <v>218</v>
       </c>
       <c r="N214" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O214" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P214" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q214" s="35" t="s">
         <v>703</v>
@@ -20963,7 +20955,7 @@
         <v>534</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D215" s="32" t="s">
         <v>630</v>
@@ -20996,13 +20988,13 @@
         <v>219</v>
       </c>
       <c r="N215" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O215" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P215" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q215" s="35" t="s">
         <v>703</v>
@@ -21034,7 +21026,7 @@
         <v>535</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D216" s="32" t="s">
         <v>630</v>
@@ -21067,13 +21059,13 @@
         <v>220</v>
       </c>
       <c r="N216" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O216" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P216" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q216" s="35" t="s">
         <v>703</v>
@@ -21105,7 +21097,7 @@
         <v>536</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D217" s="32" t="s">
         <v>630</v>
@@ -21138,13 +21130,13 @@
         <v>221</v>
       </c>
       <c r="N217" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O217" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P217" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q217" s="35" t="s">
         <v>703</v>
@@ -21176,7 +21168,7 @@
         <v>537</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D218" s="32" t="s">
         <v>630</v>
@@ -21209,13 +21201,13 @@
         <v>222</v>
       </c>
       <c r="N218" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O218" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P218" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q218" s="35" t="s">
         <v>703</v>
@@ -21247,7 +21239,7 @@
         <v>538</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D219" s="32" t="s">
         <v>630</v>
@@ -21280,13 +21272,13 @@
         <v>223</v>
       </c>
       <c r="N219" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O219" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P219" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q219" s="35" t="s">
         <v>703</v>
@@ -21318,7 +21310,7 @@
         <v>539</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D220" s="32" t="s">
         <v>630</v>
@@ -21351,13 +21343,13 @@
         <v>224</v>
       </c>
       <c r="N220" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O220" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P220" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q220" s="35" t="s">
         <v>703</v>
@@ -21389,7 +21381,7 @@
         <v>540</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D221" s="32" t="s">
         <v>630</v>
@@ -21422,13 +21414,13 @@
         <v>225</v>
       </c>
       <c r="N221" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O221" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P221" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q221" s="35" t="s">
         <v>703</v>
@@ -21460,7 +21452,7 @@
         <v>541</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D222" s="32" t="s">
         <v>630</v>
@@ -21493,13 +21485,13 @@
         <v>136</v>
       </c>
       <c r="N222" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O222" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P222" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q222" s="35" t="s">
         <v>703</v>
@@ -21531,7 +21523,7 @@
         <v>542</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D223" s="32" t="s">
         <v>630</v>
@@ -21564,13 +21556,13 @@
         <v>226</v>
       </c>
       <c r="N223" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O223" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P223" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q223" s="35" t="s">
         <v>703</v>
@@ -21602,7 +21594,7 @@
         <v>543</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D224" s="32" t="s">
         <v>630</v>
@@ -21635,13 +21627,13 @@
         <v>227</v>
       </c>
       <c r="N224" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O224" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P224" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q224" s="35" t="s">
         <v>703</v>
@@ -21673,7 +21665,7 @@
         <v>544</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D225" s="32" t="s">
         <v>630</v>
@@ -21706,13 +21698,13 @@
         <v>228</v>
       </c>
       <c r="N225" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O225" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P225" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q225" s="35" t="s">
         <v>703</v>
@@ -21744,7 +21736,7 @@
         <v>545</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D226" s="32" t="s">
         <v>630</v>
@@ -21777,13 +21769,13 @@
         <v>229</v>
       </c>
       <c r="N226" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O226" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P226" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q226" s="35" t="s">
         <v>703</v>
@@ -21815,7 +21807,7 @@
         <v>546</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D227" s="32" t="s">
         <v>630</v>
@@ -21848,13 +21840,13 @@
         <v>230</v>
       </c>
       <c r="N227" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O227" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P227" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q227" s="35" t="s">
         <v>703</v>
@@ -21886,7 +21878,7 @@
         <v>547</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D228" s="32" t="s">
         <v>630</v>
@@ -21919,13 +21911,13 @@
         <v>231</v>
       </c>
       <c r="N228" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O228" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P228" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q228" s="35" t="s">
         <v>703</v>
@@ -21957,7 +21949,7 @@
         <v>548</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D229" s="32" t="s">
         <v>630</v>
@@ -21990,13 +21982,13 @@
         <v>232</v>
       </c>
       <c r="N229" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O229" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P229" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q229" s="35" t="s">
         <v>703</v>
@@ -22028,7 +22020,7 @@
         <v>549</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D230" s="32" t="s">
         <v>630</v>
@@ -22061,13 +22053,13 @@
         <v>233</v>
       </c>
       <c r="N230" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O230" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P230" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q230" s="35" t="s">
         <v>703</v>
@@ -22099,7 +22091,7 @@
         <v>550</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D231" s="32" t="s">
         <v>630</v>
@@ -22132,13 +22124,13 @@
         <v>234</v>
       </c>
       <c r="N231" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O231" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P231" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q231" s="35" t="s">
         <v>703</v>
@@ -22170,7 +22162,7 @@
         <v>551</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D232" s="32" t="s">
         <v>630</v>
@@ -22203,13 +22195,13 @@
         <v>235</v>
       </c>
       <c r="N232" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O232" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P232" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q232" s="35" t="s">
         <v>703</v>
@@ -22241,7 +22233,7 @@
         <v>552</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D233" s="32" t="s">
         <v>630</v>
@@ -22274,13 +22266,13 @@
         <v>236</v>
       </c>
       <c r="N233" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O233" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P233" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q233" s="35" t="s">
         <v>703</v>
@@ -22312,7 +22304,7 @@
         <v>553</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D234" s="32" t="s">
         <v>630</v>
@@ -22345,13 +22337,13 @@
         <v>237</v>
       </c>
       <c r="N234" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O234" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P234" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q234" s="35" t="s">
         <v>703</v>
@@ -22383,7 +22375,7 @@
         <v>554</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D235" s="32" t="s">
         <v>630</v>
@@ -22416,13 +22408,13 @@
         <v>238</v>
       </c>
       <c r="N235" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O235" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P235" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q235" s="35" t="s">
         <v>703</v>
@@ -22454,7 +22446,7 @@
         <v>555</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D236" s="32" t="s">
         <v>630</v>
@@ -22487,13 +22479,13 @@
         <v>239</v>
       </c>
       <c r="N236" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O236" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P236" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q236" s="35" t="s">
         <v>703</v>
@@ -22525,7 +22517,7 @@
         <v>556</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D237" s="32" t="s">
         <v>630</v>
@@ -22558,13 +22550,13 @@
         <v>240</v>
       </c>
       <c r="N237" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O237" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P237" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q237" s="35" t="s">
         <v>703</v>
@@ -22593,10 +22585,10 @@
         <v>238</v>
       </c>
       <c r="B238" s="47" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D238" s="32" t="s">
         <v>630</v>
@@ -22629,13 +22621,13 @@
         <v>140</v>
       </c>
       <c r="N238" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O238" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P238" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q238" s="35" t="s">
         <v>703</v>
@@ -22667,7 +22659,7 @@
         <v>557</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D239" s="32" t="s">
         <v>630</v>
@@ -22700,13 +22692,13 @@
         <v>241</v>
       </c>
       <c r="N239" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O239" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P239" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q239" s="35" t="s">
         <v>703</v>
@@ -22738,7 +22730,7 @@
         <v>558</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D240" s="32" t="s">
         <v>630</v>
@@ -22771,13 +22763,13 @@
         <v>242</v>
       </c>
       <c r="N240" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O240" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P240" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q240" s="35" t="s">
         <v>703</v>
@@ -22809,7 +22801,7 @@
         <v>559</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D241" s="32" t="s">
         <v>630</v>
@@ -22842,13 +22834,13 @@
         <v>243</v>
       </c>
       <c r="N241" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O241" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P241" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q241" s="35" t="s">
         <v>703</v>
@@ -22880,7 +22872,7 @@
         <v>560</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D242" s="32" t="s">
         <v>630</v>
@@ -22913,13 +22905,13 @@
         <v>244</v>
       </c>
       <c r="N242" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O242" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P242" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q242" s="35" t="s">
         <v>703</v>
@@ -22951,7 +22943,7 @@
         <v>561</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D243" s="32" t="s">
         <v>630</v>
@@ -22984,13 +22976,13 @@
         <v>245</v>
       </c>
       <c r="N243" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O243" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P243" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q243" s="35" t="s">
         <v>703</v>
@@ -23022,7 +23014,7 @@
         <v>562</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D244" s="32" t="s">
         <v>630</v>
@@ -23055,13 +23047,13 @@
         <v>246</v>
       </c>
       <c r="N244" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O244" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P244" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q244" s="35" t="s">
         <v>703</v>
@@ -23093,7 +23085,7 @@
         <v>563</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D245" s="32" t="s">
         <v>630</v>
@@ -23126,13 +23118,13 @@
         <v>138</v>
       </c>
       <c r="N245" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O245" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P245" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q245" s="35" t="s">
         <v>703</v>
@@ -23164,7 +23156,7 @@
         <v>564</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D246" s="32" t="s">
         <v>630</v>
@@ -23197,13 +23189,13 @@
         <v>247</v>
       </c>
       <c r="N246" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O246" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P246" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q246" s="35" t="s">
         <v>703</v>
@@ -23235,7 +23227,7 @@
         <v>565</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D247" s="32" t="s">
         <v>630</v>
@@ -23268,13 +23260,13 @@
         <v>248</v>
       </c>
       <c r="N247" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O247" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P247" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q247" s="35" t="s">
         <v>703</v>
@@ -23306,7 +23298,7 @@
         <v>566</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D248" s="32" t="s">
         <v>630</v>
@@ -23339,13 +23331,13 @@
         <v>249</v>
       </c>
       <c r="N248" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O248" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P248" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q248" s="35" t="s">
         <v>703</v>
@@ -23377,7 +23369,7 @@
         <v>567</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D249" s="32" t="s">
         <v>630</v>
@@ -23410,13 +23402,13 @@
         <v>250</v>
       </c>
       <c r="N249" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O249" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P249" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q249" s="35" t="s">
         <v>703</v>
@@ -23448,7 +23440,7 @@
         <v>568</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D250" s="32" t="s">
         <v>630</v>
@@ -23481,13 +23473,13 @@
         <v>251</v>
       </c>
       <c r="N250" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O250" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P250" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q250" s="35" t="s">
         <v>703</v>
@@ -23519,7 +23511,7 @@
         <v>569</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D251" s="32" t="s">
         <v>630</v>
@@ -23552,13 +23544,13 @@
         <v>252</v>
       </c>
       <c r="N251" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O251" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P251" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q251" s="35" t="s">
         <v>703</v>
@@ -23590,7 +23582,7 @@
         <v>570</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D252" s="32" t="s">
         <v>630</v>
@@ -23623,13 +23615,13 @@
         <v>253</v>
       </c>
       <c r="N252" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O252" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P252" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q252" s="35" t="s">
         <v>703</v>
@@ -23661,7 +23653,7 @@
         <v>571</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D253" s="32" t="s">
         <v>630</v>
@@ -23694,13 +23686,13 @@
         <v>254</v>
       </c>
       <c r="N253" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O253" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P253" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q253" s="35" t="s">
         <v>703</v>
@@ -23732,7 +23724,7 @@
         <v>572</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D254" s="32" t="s">
         <v>630</v>
@@ -23765,13 +23757,13 @@
         <v>255</v>
       </c>
       <c r="N254" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O254" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P254" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q254" s="35" t="s">
         <v>703</v>
@@ -23803,7 +23795,7 @@
         <v>573</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D255" s="32" t="s">
         <v>630</v>
@@ -23836,13 +23828,13 @@
         <v>256</v>
       </c>
       <c r="N255" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O255" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P255" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q255" s="35" t="s">
         <v>703</v>
@@ -23874,7 +23866,7 @@
         <v>574</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D256" s="32" t="s">
         <v>630</v>
@@ -23907,13 +23899,13 @@
         <v>257</v>
       </c>
       <c r="N256" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O256" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P256" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q256" s="35" t="s">
         <v>703</v>
@@ -23945,7 +23937,7 @@
         <v>575</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D257" s="32" t="s">
         <v>630</v>
@@ -23978,13 +23970,13 @@
         <v>258</v>
       </c>
       <c r="N257" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O257" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P257" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q257" s="35" t="s">
         <v>703</v>
@@ -24016,7 +24008,7 @@
         <v>576</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D258" s="32" t="s">
         <v>630</v>
@@ -24049,13 +24041,13 @@
         <v>259</v>
       </c>
       <c r="N258" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O258" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P258" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q258" s="35" t="s">
         <v>703</v>
@@ -24087,7 +24079,7 @@
         <v>577</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D259" s="32" t="s">
         <v>630</v>
@@ -24120,13 +24112,13 @@
         <v>260</v>
       </c>
       <c r="N259" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O259" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P259" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q259" s="35" t="s">
         <v>703</v>
@@ -24158,7 +24150,7 @@
         <v>578</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D260" s="32" t="s">
         <v>630</v>
@@ -24191,13 +24183,13 @@
         <v>261</v>
       </c>
       <c r="N260" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O260" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P260" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q260" s="35" t="s">
         <v>703</v>
@@ -24229,7 +24221,7 @@
         <v>579</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D261" s="32" t="s">
         <v>630</v>
@@ -24262,13 +24254,13 @@
         <v>262</v>
       </c>
       <c r="N261" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O261" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P261" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q261" s="35" t="s">
         <v>703</v>
@@ -24300,7 +24292,7 @@
         <v>580</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D262" s="32" t="s">
         <v>630</v>
@@ -24333,13 +24325,13 @@
         <v>263</v>
       </c>
       <c r="N262" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O262" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P262" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q262" s="35" t="s">
         <v>703</v>
@@ -24371,7 +24363,7 @@
         <v>581</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D263" s="32" t="s">
         <v>630</v>
@@ -24404,13 +24396,13 @@
         <v>264</v>
       </c>
       <c r="N263" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O263" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P263" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q263" s="35" t="s">
         <v>703</v>
@@ -24442,7 +24434,7 @@
         <v>582</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D264" s="32" t="s">
         <v>630</v>
@@ -24475,13 +24467,13 @@
         <v>265</v>
       </c>
       <c r="N264" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O264" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P264" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q264" s="35" t="s">
         <v>703</v>
@@ -24513,7 +24505,7 @@
         <v>583</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D265" s="32" t="s">
         <v>630</v>
@@ -24546,13 +24538,13 @@
         <v>266</v>
       </c>
       <c r="N265" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O265" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P265" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q265" s="35" t="s">
         <v>703</v>
@@ -24584,7 +24576,7 @@
         <v>584</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D266" s="32" t="s">
         <v>630</v>
@@ -24617,13 +24609,13 @@
         <v>267</v>
       </c>
       <c r="N266" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O266" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P266" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q266" s="35" t="s">
         <v>703</v>
@@ -24655,7 +24647,7 @@
         <v>585</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D267" s="32" t="s">
         <v>630</v>
@@ -24688,13 +24680,13 @@
         <v>268</v>
       </c>
       <c r="N267" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O267" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P267" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q267" s="35" t="s">
         <v>703</v>
@@ -24726,7 +24718,7 @@
         <v>586</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D268" s="32" t="s">
         <v>630</v>
@@ -24759,13 +24751,13 @@
         <v>269</v>
       </c>
       <c r="N268" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O268" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P268" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q268" s="35" t="s">
         <v>703</v>
@@ -24797,7 +24789,7 @@
         <v>587</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D269" s="32" t="s">
         <v>630</v>
@@ -24830,13 +24822,13 @@
         <v>118</v>
       </c>
       <c r="N269" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O269" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P269" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q269" s="35" t="s">
         <v>703</v>
@@ -24868,7 +24860,7 @@
         <v>588</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D270" s="32" t="s">
         <v>630</v>
@@ -24901,13 +24893,13 @@
         <v>270</v>
       </c>
       <c r="N270" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O270" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P270" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q270" s="35" t="s">
         <v>703</v>
@@ -24939,7 +24931,7 @@
         <v>589</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D271" s="32" t="s">
         <v>630</v>
@@ -24972,13 +24964,13 @@
         <v>271</v>
       </c>
       <c r="N271" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O271" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P271" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q271" s="35" t="s">
         <v>703</v>
@@ -25010,7 +25002,7 @@
         <v>590</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D272" s="32" t="s">
         <v>630</v>
@@ -25043,13 +25035,13 @@
         <v>272</v>
       </c>
       <c r="N272" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O272" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P272" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q272" s="35" t="s">
         <v>703</v>
@@ -25081,7 +25073,7 @@
         <v>591</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D273" s="32" t="s">
         <v>630</v>
@@ -25114,13 +25106,13 @@
         <v>273</v>
       </c>
       <c r="N273" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O273" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P273" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q273" s="35" t="s">
         <v>703</v>
@@ -25152,7 +25144,7 @@
         <v>592</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D274" s="32" t="s">
         <v>630</v>
@@ -25185,13 +25177,13 @@
         <v>274</v>
       </c>
       <c r="N274" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O274" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P274" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q274" s="35" t="s">
         <v>703</v>
@@ -25223,7 +25215,7 @@
         <v>593</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D275" s="32" t="s">
         <v>630</v>
@@ -25256,13 +25248,13 @@
         <v>275</v>
       </c>
       <c r="N275" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O275" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P275" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q275" s="35" t="s">
         <v>703</v>
@@ -25294,7 +25286,7 @@
         <v>594</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D276" s="32" t="s">
         <v>630</v>
@@ -25327,13 +25319,13 @@
         <v>276</v>
       </c>
       <c r="N276" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O276" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P276" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q276" s="35" t="s">
         <v>703</v>
@@ -25365,7 +25357,7 @@
         <v>595</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D277" s="32" t="s">
         <v>630</v>
@@ -25398,13 +25390,13 @@
         <v>277</v>
       </c>
       <c r="N277" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O277" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P277" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q277" s="35" t="s">
         <v>703</v>
@@ -25436,7 +25428,7 @@
         <v>596</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D278" s="32" t="s">
         <v>630</v>
@@ -25469,13 +25461,13 @@
         <v>278</v>
       </c>
       <c r="N278" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O278" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P278" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q278" s="35" t="s">
         <v>703</v>
@@ -25507,7 +25499,7 @@
         <v>597</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D279" s="32" t="s">
         <v>630</v>
@@ -25540,13 +25532,13 @@
         <v>279</v>
       </c>
       <c r="N279" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O279" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P279" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q279" s="35" t="s">
         <v>703</v>
@@ -25578,7 +25570,7 @@
         <v>598</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D280" s="32" t="s">
         <v>630</v>
@@ -25611,13 +25603,13 @@
         <v>280</v>
       </c>
       <c r="N280" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O280" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P280" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q280" s="35" t="s">
         <v>703</v>
@@ -25649,7 +25641,7 @@
         <v>599</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D281" s="32" t="s">
         <v>630</v>
@@ -25682,13 +25674,13 @@
         <v>281</v>
       </c>
       <c r="N281" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O281" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P281" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q281" s="35" t="s">
         <v>703</v>
@@ -25720,7 +25712,7 @@
         <v>600</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D282" s="32" t="s">
         <v>630</v>
@@ -25753,13 +25745,13 @@
         <v>282</v>
       </c>
       <c r="N282" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O282" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P282" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q282" s="35" t="s">
         <v>703</v>
@@ -25791,7 +25783,7 @@
         <v>601</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D283" s="32" t="s">
         <v>630</v>
@@ -25824,13 +25816,13 @@
         <v>283</v>
       </c>
       <c r="N283" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O283" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P283" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q283" s="35" t="s">
         <v>703</v>
@@ -25862,7 +25854,7 @@
         <v>602</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D284" s="32" t="s">
         <v>630</v>
@@ -25895,13 +25887,13 @@
         <v>284</v>
       </c>
       <c r="N284" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O284" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P284" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q284" s="35" t="s">
         <v>703</v>
@@ -25933,7 +25925,7 @@
         <v>603</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D285" s="32" t="s">
         <v>630</v>
@@ -25966,13 +25958,13 @@
         <v>285</v>
       </c>
       <c r="N285" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O285" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P285" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q285" s="35" t="s">
         <v>703</v>
@@ -26004,7 +25996,7 @@
         <v>604</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D286" s="32" t="s">
         <v>630</v>
@@ -26037,13 +26029,13 @@
         <v>286</v>
       </c>
       <c r="N286" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O286" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P286" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q286" s="35" t="s">
         <v>703</v>
@@ -26075,7 +26067,7 @@
         <v>605</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D287" s="32" t="s">
         <v>630</v>
@@ -26108,13 +26100,13 @@
         <v>287</v>
       </c>
       <c r="N287" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O287" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P287" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q287" s="35" t="s">
         <v>703</v>
@@ -26146,7 +26138,7 @@
         <v>606</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D288" s="32" t="s">
         <v>630</v>
@@ -26179,13 +26171,13 @@
         <v>288</v>
       </c>
       <c r="N288" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O288" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P288" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q288" s="35" t="s">
         <v>703</v>
@@ -26217,7 +26209,7 @@
         <v>607</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D289" s="32" t="s">
         <v>630</v>
@@ -26250,13 +26242,13 @@
         <v>289</v>
       </c>
       <c r="N289" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O289" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P289" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q289" s="35" t="s">
         <v>703</v>
@@ -26288,7 +26280,7 @@
         <v>608</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D290" s="32" t="s">
         <v>630</v>
@@ -26321,13 +26313,13 @@
         <v>236</v>
       </c>
       <c r="N290" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O290" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P290" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q290" s="35" t="s">
         <v>703</v>
@@ -26359,7 +26351,7 @@
         <v>609</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D291" s="32" t="s">
         <v>630</v>
@@ -26392,13 +26384,13 @@
         <v>290</v>
       </c>
       <c r="N291" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O291" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P291" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q291" s="35" t="s">
         <v>703</v>
@@ -26430,7 +26422,7 @@
         <v>610</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D292" s="32" t="s">
         <v>630</v>
@@ -26463,13 +26455,13 @@
         <v>291</v>
       </c>
       <c r="N292" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O292" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P292" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q292" s="35" t="s">
         <v>703</v>
@@ -26501,7 +26493,7 @@
         <v>611</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D293" s="32" t="s">
         <v>630</v>
@@ -26534,13 +26526,13 @@
         <v>292</v>
       </c>
       <c r="N293" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O293" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P293" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q293" s="35" t="s">
         <v>703</v>
@@ -26572,7 +26564,7 @@
         <v>612</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D294" s="32" t="s">
         <v>630</v>
@@ -26605,13 +26597,13 @@
         <v>293</v>
       </c>
       <c r="N294" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O294" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P294" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q294" s="35" t="s">
         <v>703</v>
@@ -26643,7 +26635,7 @@
         <v>613</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D295" s="32" t="s">
         <v>630</v>
@@ -26676,13 +26668,13 @@
         <v>235</v>
       </c>
       <c r="N295" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O295" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P295" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q295" s="35" t="s">
         <v>703</v>
@@ -26714,7 +26706,7 @@
         <v>614</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D296" s="32" t="s">
         <v>630</v>
@@ -26747,13 +26739,13 @@
         <v>294</v>
       </c>
       <c r="N296" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O296" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P296" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q296" s="35" t="s">
         <v>703</v>
@@ -26785,7 +26777,7 @@
         <v>615</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D297" s="32" t="s">
         <v>630</v>
@@ -26818,13 +26810,13 @@
         <v>295</v>
       </c>
       <c r="N297" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O297" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P297" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q297" s="35" t="s">
         <v>703</v>
@@ -26856,7 +26848,7 @@
         <v>616</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D298" s="32" t="s">
         <v>630</v>
@@ -26889,13 +26881,13 @@
         <v>296</v>
       </c>
       <c r="N298" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O298" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P298" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q298" s="35" t="s">
         <v>703</v>
@@ -26927,7 +26919,7 @@
         <v>617</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D299" s="32" t="s">
         <v>630</v>
@@ -26960,13 +26952,13 @@
         <v>297</v>
       </c>
       <c r="N299" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O299" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P299" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q299" s="35" t="s">
         <v>703</v>
@@ -26998,7 +26990,7 @@
         <v>618</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D300" s="32" t="s">
         <v>630</v>
@@ -27031,13 +27023,13 @@
         <v>298</v>
       </c>
       <c r="N300" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O300" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P300" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q300" s="35" t="s">
         <v>703</v>
@@ -27069,7 +27061,7 @@
         <v>619</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D301" s="32" t="s">
         <v>630</v>
@@ -27102,13 +27094,13 @@
         <v>299</v>
       </c>
       <c r="N301" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O301" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P301" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q301" s="35" t="s">
         <v>703</v>
@@ -27140,7 +27132,7 @@
         <v>620</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D302" s="32" t="s">
         <v>630</v>
@@ -27173,13 +27165,13 @@
         <v>300</v>
       </c>
       <c r="N302" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O302" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P302" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q302" s="35" t="s">
         <v>703</v>
@@ -27211,7 +27203,7 @@
         <v>621</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D303" s="32" t="s">
         <v>630</v>
@@ -27244,13 +27236,13 @@
         <v>301</v>
       </c>
       <c r="N303" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O303" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P303" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q303" s="35" t="s">
         <v>703</v>
@@ -27282,7 +27274,7 @@
         <v>622</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D304" s="32" t="s">
         <v>630</v>
@@ -27315,13 +27307,13 @@
         <v>302</v>
       </c>
       <c r="N304" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O304" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P304" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q304" s="35" t="s">
         <v>703</v>
@@ -27353,7 +27345,7 @@
         <v>623</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D305" s="32" t="s">
         <v>630</v>
@@ -27386,13 +27378,13 @@
         <v>303</v>
       </c>
       <c r="N305" s="43" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="O305" s="35" t="s">
         <v>703</v>
       </c>
       <c r="P305" s="43" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="Q305" s="35" t="s">
         <v>703</v>
@@ -27418,60 +27410,60 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="12" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="cellIs" dxfId="11" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J1">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="8" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:W1048576">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="2" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930844C8-117A-420F-BA9E-A81FF01903D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -3503,14 +3503,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C26"/>
-  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="65.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="15.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>307</v>
       </c>
@@ -3532,7 +3532,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>308</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
@@ -3554,7 +3554,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>6</v>
       </c>
@@ -3566,7 +3566,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
@@ -3578,7 +3578,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>8</v>
       </c>
@@ -3589,7 +3589,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="38" t="s">
         <v>9</v>
       </c>
@@ -3600,7 +3600,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>309</v>
       </c>
@@ -3611,7 +3611,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>311</v>
       </c>
@@ -3622,7 +3622,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>312</v>
       </c>
@@ -3633,7 +3633,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>10</v>
       </c>
@@ -3644,7 +3644,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>313</v>
       </c>
@@ -3655,7 +3655,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>314</v>
       </c>
@@ -3666,7 +3666,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="4" t="s">
         <v>315</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>316</v>
       </c>
@@ -3688,7 +3688,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -3699,19 +3699,19 @@
         <v>693</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>317</v>
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46148.642853935184</v>
+        <v>46157.683893518515</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>693</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>702</v>
       </c>
@@ -3722,7 +3722,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="38" t="s">
         <v>696</v>
       </c>
@@ -3734,7 +3734,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="38" t="s">
         <v>703</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>306</v>
       </c>
@@ -3757,7 +3757,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>318</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>324</v>
       </c>
@@ -3779,7 +3779,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>326</v>
       </c>
@@ -3790,7 +3790,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="7.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:3" ht="7.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="38" t="s">
         <v>689</v>
       </c>
@@ -3810,34 +3810,34 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA19"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" style="29" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.69921875" style="29" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" style="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="29" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="29" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.796875" style="29" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.296875" style="29" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.296875" style="29" bestFit="1" customWidth="1"/>
     <col min="7" max="11" width="8.5" style="29" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="75.83203125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="55.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.296875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.296875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="75.796875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="55.19921875" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="7" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.83203125" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.796875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="7.296875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="10" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.6640625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="8.1640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.6640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="3.83203125" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.69921875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="8.19921875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="3.796875" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="79.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="57.75" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -3920,7 +3920,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -4011,7 +4011,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -4102,7 +4102,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -4284,7 +4284,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -4375,7 +4375,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -4466,7 +4466,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -4557,7 +4557,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -4648,7 +4648,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -4739,7 +4739,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -4830,7 +4830,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -5012,7 +5012,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -5194,7 +5194,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -5376,7 +5376,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -5467,7 +5467,7 @@
         <v>783</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -5583,13 +5583,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BEF6990-269C-482F-AEAB-0F771E87FB19}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="21" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="21" width="7.69921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="15.45" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>657</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A2" s="22">
         <v>2</v>
       </c>
@@ -5736,13 +5736,13 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B56C5A03-15CD-4694-84A2-E149E46D665B}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.83203125" customWidth="1"/>
+    <col min="2" max="3" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="25">
         <v>1</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="14">
         <v>2</v>
       </c>
@@ -5778,26 +5778,26 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2864B2AC-DDFD-480C-BEC0-F2615FD9637A}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:Y305"/>
-  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.296875" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="8" style="2" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="4.33203125" customWidth="1"/>
-    <col min="9" max="9" width="5.6640625" customWidth="1"/>
-    <col min="10" max="10" width="3.6640625" customWidth="1"/>
-    <col min="11" max="11" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="4.296875" customWidth="1"/>
+    <col min="9" max="9" width="5.69921875" customWidth="1"/>
+    <col min="10" max="10" width="3.69921875" customWidth="1"/>
+    <col min="11" max="11" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5" customWidth="1"/>
     <col min="13" max="13" width="20.5" customWidth="1"/>
-    <col min="14" max="14" width="6.33203125" customWidth="1"/>
+    <col min="14" max="14" width="6.296875" customWidth="1"/>
     <col min="15" max="15" width="32.5" style="34" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.6640625" bestFit="1" customWidth="1"/>
-    <col min="20" max="25" width="3.83203125" customWidth="1"/>
+    <col min="17" max="17" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="3.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>319</v>
       </c>
@@ -5870,7 +5870,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:25" s="2" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="9">
         <v>2</v>
       </c>
@@ -5947,7 +5947,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>3</v>
       </c>
@@ -6024,7 +6024,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>4</v>
       </c>
@@ -6101,7 +6101,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>5</v>
       </c>
@@ -6178,7 +6178,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>6</v>
       </c>
@@ -6255,7 +6255,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>7</v>
       </c>
@@ -6332,7 +6332,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>8</v>
       </c>
@@ -6409,7 +6409,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>9</v>
       </c>
@@ -6486,7 +6486,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>10</v>
       </c>
@@ -6563,7 +6563,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>11</v>
       </c>
@@ -6640,7 +6640,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>12</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>13</v>
       </c>
@@ -6794,7 +6794,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>14</v>
       </c>
@@ -6871,7 +6871,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>15</v>
       </c>
@@ -6948,7 +6948,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>16</v>
       </c>
@@ -7025,7 +7025,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>17</v>
       </c>
@@ -7102,7 +7102,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>18</v>
       </c>
@@ -7179,7 +7179,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>19</v>
       </c>
@@ -7256,7 +7256,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>20</v>
       </c>
@@ -7333,7 +7333,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>21</v>
       </c>
@@ -7410,7 +7410,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>22</v>
       </c>
@@ -7487,7 +7487,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>23</v>
       </c>
@@ -7564,7 +7564,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>24</v>
       </c>
@@ -7641,7 +7641,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>25</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>26</v>
       </c>
@@ -7795,7 +7795,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>27</v>
       </c>
@@ -7872,7 +7872,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>28</v>
       </c>
@@ -7949,7 +7949,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>29</v>
       </c>
@@ -8026,7 +8026,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>30</v>
       </c>
@@ -8103,7 +8103,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>31</v>
       </c>
@@ -8180,7 +8180,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>32</v>
       </c>
@@ -8257,7 +8257,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>33</v>
       </c>
@@ -8334,7 +8334,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="9">
         <v>34</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A35" s="9">
         <v>35</v>
       </c>
@@ -8488,7 +8488,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="9">
         <v>36</v>
       </c>
@@ -8565,7 +8565,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A37" s="9">
         <v>37</v>
       </c>
@@ -8642,7 +8642,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="9">
         <v>38</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="9">
         <v>39</v>
       </c>
@@ -8796,7 +8796,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A40" s="9">
         <v>40</v>
       </c>
@@ -8873,7 +8873,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A41" s="9">
         <v>41</v>
       </c>
@@ -8950,7 +8950,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="9">
         <v>42</v>
       </c>
@@ -9027,7 +9027,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A43" s="9">
         <v>43</v>
       </c>
@@ -9104,7 +9104,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A44" s="9">
         <v>44</v>
       </c>
@@ -9181,7 +9181,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="9">
         <v>45</v>
       </c>
@@ -9258,7 +9258,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="9">
         <v>46</v>
       </c>
@@ -9335,7 +9335,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="9">
         <v>47</v>
       </c>
@@ -9412,7 +9412,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="9">
         <v>48</v>
       </c>
@@ -9489,7 +9489,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="9">
         <v>49</v>
       </c>
@@ -9566,7 +9566,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A50" s="9">
         <v>50</v>
       </c>
@@ -9643,7 +9643,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A51" s="9">
         <v>51</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A52" s="9">
         <v>52</v>
       </c>
@@ -9797,7 +9797,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A53" s="9">
         <v>53</v>
       </c>
@@ -9874,7 +9874,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A54" s="9">
         <v>54</v>
       </c>
@@ -9951,7 +9951,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="9">
         <v>55</v>
       </c>
@@ -10028,7 +10028,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A56" s="9">
         <v>56</v>
       </c>
@@ -10105,7 +10105,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A57" s="9">
         <v>57</v>
       </c>
@@ -10182,7 +10182,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A58" s="9">
         <v>58</v>
       </c>
@@ -10259,7 +10259,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A59" s="9">
         <v>59</v>
       </c>
@@ -10336,7 +10336,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A60" s="9">
         <v>60</v>
       </c>
@@ -10413,7 +10413,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="9">
         <v>61</v>
       </c>
@@ -10490,7 +10490,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A62" s="9">
         <v>62</v>
       </c>
@@ -10567,7 +10567,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="9">
         <v>63</v>
       </c>
@@ -10644,7 +10644,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="9">
         <v>64</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="9">
         <v>65</v>
       </c>
@@ -10798,7 +10798,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="9">
         <v>66</v>
       </c>
@@ -10875,7 +10875,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="9">
         <v>67</v>
       </c>
@@ -10952,7 +10952,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="9">
         <v>68</v>
       </c>
@@ -11029,7 +11029,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="9">
         <v>69</v>
       </c>
@@ -11106,7 +11106,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A70" s="9">
         <v>70</v>
       </c>
@@ -11183,7 +11183,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A71" s="9">
         <v>71</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A72" s="9">
         <v>72</v>
       </c>
@@ -11337,7 +11337,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A73" s="9">
         <v>73</v>
       </c>
@@ -11414,7 +11414,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="9">
         <v>74</v>
       </c>
@@ -11491,7 +11491,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="9">
         <v>75</v>
       </c>
@@ -11568,7 +11568,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="9">
         <v>76</v>
       </c>
@@ -11645,7 +11645,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="9">
         <v>77</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A78" s="9">
         <v>78</v>
       </c>
@@ -11799,7 +11799,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A79" s="9">
         <v>79</v>
       </c>
@@ -11876,7 +11876,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A80" s="9">
         <v>80</v>
       </c>
@@ -11953,7 +11953,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A81" s="9">
         <v>81</v>
       </c>
@@ -12030,7 +12030,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A82" s="9">
         <v>82</v>
       </c>
@@ -12107,7 +12107,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A83" s="9">
         <v>83</v>
       </c>
@@ -12184,7 +12184,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A84" s="9">
         <v>84</v>
       </c>
@@ -12261,7 +12261,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A85" s="9">
         <v>85</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A86" s="9">
         <v>86</v>
       </c>
@@ -12415,7 +12415,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A87" s="9">
         <v>87</v>
       </c>
@@ -12492,7 +12492,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A88" s="9">
         <v>88</v>
       </c>
@@ -12569,7 +12569,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="9">
         <v>89</v>
       </c>
@@ -12646,7 +12646,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="9">
         <v>90</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A91" s="9">
         <v>91</v>
       </c>
@@ -12800,7 +12800,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A92" s="9">
         <v>92</v>
       </c>
@@ -12877,7 +12877,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="9">
         <v>93</v>
       </c>
@@ -12954,7 +12954,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A94" s="9">
         <v>94</v>
       </c>
@@ -13031,7 +13031,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A95" s="9">
         <v>95</v>
       </c>
@@ -13108,7 +13108,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A96" s="9">
         <v>96</v>
       </c>
@@ -13185,7 +13185,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A97" s="9">
         <v>97</v>
       </c>
@@ -13262,7 +13262,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A98" s="9">
         <v>98</v>
       </c>
@@ -13339,7 +13339,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A99" s="9">
         <v>99</v>
       </c>
@@ -13416,7 +13416,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A100" s="9">
         <v>100</v>
       </c>
@@ -13493,7 +13493,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A101" s="9">
         <v>101</v>
       </c>
@@ -13570,7 +13570,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A102" s="9">
         <v>102</v>
       </c>
@@ -13647,7 +13647,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A103" s="9">
         <v>103</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A104" s="9">
         <v>104</v>
       </c>
@@ -13801,7 +13801,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A105" s="9">
         <v>105</v>
       </c>
@@ -13878,7 +13878,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A106" s="9">
         <v>106</v>
       </c>
@@ -13955,7 +13955,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="9">
         <v>107</v>
       </c>
@@ -14032,7 +14032,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A108" s="9">
         <v>108</v>
       </c>
@@ -14109,7 +14109,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A109" s="9">
         <v>109</v>
       </c>
@@ -14186,7 +14186,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="9">
         <v>110</v>
       </c>
@@ -14263,7 +14263,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="9">
         <v>111</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A112" s="9">
         <v>112</v>
       </c>
@@ -14417,7 +14417,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A113" s="9">
         <v>113</v>
       </c>
@@ -14494,7 +14494,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A114" s="9">
         <v>114</v>
       </c>
@@ -14571,7 +14571,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A115" s="9">
         <v>115</v>
       </c>
@@ -14648,7 +14648,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="9">
         <v>116</v>
       </c>
@@ -14725,7 +14725,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A117" s="9">
         <v>117</v>
       </c>
@@ -14802,7 +14802,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="9">
         <v>118</v>
       </c>
@@ -14879,7 +14879,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A119" s="9">
         <v>119</v>
       </c>
@@ -14956,7 +14956,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A120" s="9">
         <v>120</v>
       </c>
@@ -15033,7 +15033,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A121" s="9">
         <v>121</v>
       </c>
@@ -15110,7 +15110,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A122" s="9">
         <v>122</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A123" s="9">
         <v>123</v>
       </c>
@@ -15264,7 +15264,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A124" s="9">
         <v>124</v>
       </c>
@@ -15341,7 +15341,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A125" s="9">
         <v>125</v>
       </c>
@@ -15418,7 +15418,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A126" s="9">
         <v>126</v>
       </c>
@@ -15495,7 +15495,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="9">
         <v>127</v>
       </c>
@@ -15572,7 +15572,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A128" s="9">
         <v>128</v>
       </c>
@@ -15649,7 +15649,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A129" s="9">
         <v>129</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A130" s="9">
         <v>130</v>
       </c>
@@ -15803,7 +15803,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A131" s="9">
         <v>131</v>
       </c>
@@ -15880,7 +15880,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A132" s="9">
         <v>132</v>
       </c>
@@ -15957,7 +15957,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="9">
         <v>133</v>
       </c>
@@ -16034,7 +16034,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A134" s="9">
         <v>134</v>
       </c>
@@ -16111,7 +16111,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A135" s="9">
         <v>135</v>
       </c>
@@ -16188,7 +16188,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A136" s="9">
         <v>136</v>
       </c>
@@ -16265,7 +16265,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A137" s="9">
         <v>137</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="9">
         <v>138</v>
       </c>
@@ -16419,7 +16419,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="9">
         <v>139</v>
       </c>
@@ -16496,7 +16496,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A140" s="9">
         <v>140</v>
       </c>
@@ -16573,7 +16573,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A141" s="9">
         <v>141</v>
       </c>
@@ -16650,7 +16650,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A142" s="9">
         <v>142</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A143" s="9">
         <v>143</v>
       </c>
@@ -16804,7 +16804,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A144" s="9">
         <v>144</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A145" s="9">
         <v>145</v>
       </c>
@@ -16958,7 +16958,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A146" s="9">
         <v>146</v>
       </c>
@@ -17035,7 +17035,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="9">
         <v>147</v>
       </c>
@@ -17112,7 +17112,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A148" s="9">
         <v>148</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A149" s="9">
         <v>149</v>
       </c>
@@ -17266,7 +17266,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A150" s="9">
         <v>150</v>
       </c>
@@ -17343,7 +17343,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A151" s="9">
         <v>151</v>
       </c>
@@ -17420,7 +17420,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A152" s="9">
         <v>152</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A153" s="9">
         <v>153</v>
       </c>
@@ -17574,7 +17574,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A154" s="9">
         <v>154</v>
       </c>
@@ -17651,7 +17651,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A155" s="9">
         <v>155</v>
       </c>
@@ -17728,7 +17728,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A156" s="9">
         <v>156</v>
       </c>
@@ -17805,7 +17805,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A157" s="9">
         <v>157</v>
       </c>
@@ -17882,7 +17882,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A158" s="9">
         <v>158</v>
       </c>
@@ -17959,7 +17959,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A159" s="9">
         <v>159</v>
       </c>
@@ -18036,7 +18036,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A160" s="9">
         <v>160</v>
       </c>
@@ -18113,7 +18113,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A161" s="9">
         <v>161</v>
       </c>
@@ -18190,7 +18190,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A162" s="9">
         <v>162</v>
       </c>
@@ -18267,7 +18267,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A163" s="9">
         <v>163</v>
       </c>
@@ -18344,7 +18344,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A164" s="9">
         <v>164</v>
       </c>
@@ -18421,7 +18421,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A165" s="9">
         <v>165</v>
       </c>
@@ -18498,7 +18498,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A166" s="9">
         <v>166</v>
       </c>
@@ -18575,7 +18575,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A167" s="9">
         <v>167</v>
       </c>
@@ -18652,7 +18652,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A168" s="9">
         <v>168</v>
       </c>
@@ -18729,7 +18729,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A169" s="9">
         <v>169</v>
       </c>
@@ -18806,7 +18806,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A170" s="9">
         <v>170</v>
       </c>
@@ -18883,7 +18883,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A171" s="9">
         <v>171</v>
       </c>
@@ -18960,7 +18960,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A172" s="9">
         <v>172</v>
       </c>
@@ -19037,7 +19037,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A173" s="9">
         <v>173</v>
       </c>
@@ -19114,7 +19114,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A174" s="9">
         <v>174</v>
       </c>
@@ -19191,7 +19191,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="9">
         <v>175</v>
       </c>
@@ -19268,7 +19268,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A176" s="9">
         <v>176</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A177" s="9">
         <v>177</v>
       </c>
@@ -19422,7 +19422,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A178" s="9">
         <v>178</v>
       </c>
@@ -19499,7 +19499,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A179" s="9">
         <v>179</v>
       </c>
@@ -19576,7 +19576,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A180" s="9">
         <v>180</v>
       </c>
@@ -19653,7 +19653,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A181" s="9">
         <v>181</v>
       </c>
@@ -19730,7 +19730,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A182" s="9">
         <v>182</v>
       </c>
@@ -19807,7 +19807,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A183" s="9">
         <v>183</v>
       </c>
@@ -19884,7 +19884,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A184" s="9">
         <v>184</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A185" s="9">
         <v>185</v>
       </c>
@@ -20038,7 +20038,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A186" s="9">
         <v>186</v>
       </c>
@@ -20115,7 +20115,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A187" s="9">
         <v>187</v>
       </c>
@@ -20192,7 +20192,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A188" s="9">
         <v>188</v>
       </c>
@@ -20269,7 +20269,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A189" s="9">
         <v>189</v>
       </c>
@@ -20346,7 +20346,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A190" s="9">
         <v>190</v>
       </c>
@@ -20423,7 +20423,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A191" s="9">
         <v>191</v>
       </c>
@@ -20500,7 +20500,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A192" s="9">
         <v>192</v>
       </c>
@@ -20577,7 +20577,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A193" s="9">
         <v>193</v>
       </c>
@@ -20654,7 +20654,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A194" s="9">
         <v>194</v>
       </c>
@@ -20731,7 +20731,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A195" s="9">
         <v>195</v>
       </c>
@@ -20808,7 +20808,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A196" s="9">
         <v>196</v>
       </c>
@@ -20885,7 +20885,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A197" s="9">
         <v>197</v>
       </c>
@@ -20962,7 +20962,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A198" s="9">
         <v>198</v>
       </c>
@@ -21039,7 +21039,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A199" s="9">
         <v>199</v>
       </c>
@@ -21116,7 +21116,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A200" s="9">
         <v>200</v>
       </c>
@@ -21193,7 +21193,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A201" s="9">
         <v>201</v>
       </c>
@@ -21270,7 +21270,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A202" s="9">
         <v>202</v>
       </c>
@@ -21347,7 +21347,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A203" s="9">
         <v>203</v>
       </c>
@@ -21424,7 +21424,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="9">
         <v>204</v>
       </c>
@@ -21501,7 +21501,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A205" s="9">
         <v>205</v>
       </c>
@@ -21578,7 +21578,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A206" s="9">
         <v>206</v>
       </c>
@@ -21655,7 +21655,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A207" s="9">
         <v>207</v>
       </c>
@@ -21732,7 +21732,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A208" s="9">
         <v>208</v>
       </c>
@@ -21809,7 +21809,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A209" s="9">
         <v>209</v>
       </c>
@@ -21886,7 +21886,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A210" s="9">
         <v>210</v>
       </c>
@@ -21963,7 +21963,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A211" s="9">
         <v>211</v>
       </c>
@@ -22040,7 +22040,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A212" s="9">
         <v>212</v>
       </c>
@@ -22117,7 +22117,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A213" s="9">
         <v>213</v>
       </c>
@@ -22194,7 +22194,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A214" s="9">
         <v>214</v>
       </c>
@@ -22271,7 +22271,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A215" s="9">
         <v>215</v>
       </c>
@@ -22348,7 +22348,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A216" s="9">
         <v>216</v>
       </c>
@@ -22425,7 +22425,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A217" s="9">
         <v>217</v>
       </c>
@@ -22502,7 +22502,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A218" s="9">
         <v>218</v>
       </c>
@@ -22579,7 +22579,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A219" s="9">
         <v>219</v>
       </c>
@@ -22656,7 +22656,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A220" s="9">
         <v>220</v>
       </c>
@@ -22733,7 +22733,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A221" s="9">
         <v>221</v>
       </c>
@@ -22810,7 +22810,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A222" s="9">
         <v>222</v>
       </c>
@@ -22887,7 +22887,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A223" s="9">
         <v>223</v>
       </c>
@@ -22964,7 +22964,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A224" s="9">
         <v>224</v>
       </c>
@@ -23041,7 +23041,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A225" s="9">
         <v>225</v>
       </c>
@@ -23118,7 +23118,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A226" s="9">
         <v>226</v>
       </c>
@@ -23195,7 +23195,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A227" s="9">
         <v>227</v>
       </c>
@@ -23272,7 +23272,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A228" s="9">
         <v>228</v>
       </c>
@@ -23349,7 +23349,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A229" s="9">
         <v>229</v>
       </c>
@@ -23426,7 +23426,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A230" s="9">
         <v>230</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A231" s="9">
         <v>231</v>
       </c>
@@ -23580,7 +23580,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A232" s="9">
         <v>232</v>
       </c>
@@ -23657,7 +23657,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="9">
         <v>233</v>
       </c>
@@ -23734,7 +23734,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A234" s="9">
         <v>234</v>
       </c>
@@ -23811,7 +23811,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A235" s="9">
         <v>235</v>
       </c>
@@ -23888,7 +23888,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A236" s="9">
         <v>236</v>
       </c>
@@ -23965,7 +23965,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A237" s="9">
         <v>237</v>
       </c>
@@ -24042,7 +24042,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A238" s="9">
         <v>238</v>
       </c>
@@ -24119,7 +24119,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="9">
         <v>239</v>
       </c>
@@ -24196,7 +24196,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A240" s="9">
         <v>240</v>
       </c>
@@ -24273,7 +24273,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A241" s="9">
         <v>241</v>
       </c>
@@ -24350,7 +24350,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A242" s="9">
         <v>242</v>
       </c>
@@ -24427,7 +24427,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A243" s="9">
         <v>243</v>
       </c>
@@ -24504,7 +24504,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A244" s="9">
         <v>244</v>
       </c>
@@ -24581,7 +24581,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A245" s="9">
         <v>245</v>
       </c>
@@ -24658,7 +24658,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="9">
         <v>246</v>
       </c>
@@ -24735,7 +24735,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A247" s="9">
         <v>247</v>
       </c>
@@ -24812,7 +24812,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A248" s="9">
         <v>248</v>
       </c>
@@ -24889,7 +24889,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A249" s="9">
         <v>249</v>
       </c>
@@ -24966,7 +24966,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A250" s="9">
         <v>250</v>
       </c>
@@ -25043,7 +25043,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A251" s="9">
         <v>251</v>
       </c>
@@ -25120,7 +25120,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A252" s="9">
         <v>252</v>
       </c>
@@ -25197,7 +25197,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A253" s="9">
         <v>253</v>
       </c>
@@ -25274,7 +25274,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A254" s="9">
         <v>254</v>
       </c>
@@ -25351,7 +25351,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A255" s="9">
         <v>255</v>
       </c>
@@ -25428,7 +25428,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A256" s="9">
         <v>256</v>
       </c>
@@ -25505,7 +25505,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A257" s="9">
         <v>257</v>
       </c>
@@ -25582,7 +25582,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A258" s="9">
         <v>258</v>
       </c>
@@ -25659,7 +25659,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A259" s="9">
         <v>259</v>
       </c>
@@ -25736,7 +25736,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A260" s="9">
         <v>260</v>
       </c>
@@ -25813,7 +25813,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A261" s="9">
         <v>261</v>
       </c>
@@ -25890,7 +25890,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="9">
         <v>262</v>
       </c>
@@ -25967,7 +25967,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A263" s="9">
         <v>263</v>
       </c>
@@ -26044,7 +26044,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A264" s="9">
         <v>264</v>
       </c>
@@ -26121,7 +26121,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A265" s="9">
         <v>265</v>
       </c>
@@ -26198,7 +26198,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A266" s="9">
         <v>266</v>
       </c>
@@ -26275,7 +26275,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A267" s="9">
         <v>267</v>
       </c>
@@ -26352,7 +26352,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A268" s="9">
         <v>268</v>
       </c>
@@ -26429,7 +26429,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A269" s="9">
         <v>269</v>
       </c>
@@ -26506,7 +26506,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A270" s="9">
         <v>270</v>
       </c>
@@ -26583,7 +26583,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A271" s="9">
         <v>271</v>
       </c>
@@ -26660,7 +26660,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A272" s="9">
         <v>272</v>
       </c>
@@ -26737,7 +26737,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A273" s="9">
         <v>273</v>
       </c>
@@ -26814,7 +26814,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A274" s="9">
         <v>274</v>
       </c>
@@ -26891,7 +26891,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A275" s="9">
         <v>275</v>
       </c>
@@ -26968,7 +26968,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A276" s="9">
         <v>276</v>
       </c>
@@ -27045,7 +27045,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A277" s="9">
         <v>277</v>
       </c>
@@ -27122,7 +27122,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A278" s="9">
         <v>278</v>
       </c>
@@ -27199,7 +27199,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A279" s="9">
         <v>279</v>
       </c>
@@ -27276,7 +27276,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A280" s="9">
         <v>280</v>
       </c>
@@ -27353,7 +27353,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A281" s="9">
         <v>281</v>
       </c>
@@ -27430,7 +27430,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A282" s="9">
         <v>282</v>
       </c>
@@ -27507,7 +27507,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A283" s="9">
         <v>283</v>
       </c>
@@ -27584,7 +27584,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A284" s="9">
         <v>284</v>
       </c>
@@ -27661,7 +27661,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A285" s="9">
         <v>285</v>
       </c>
@@ -27738,7 +27738,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A286" s="9">
         <v>286</v>
       </c>
@@ -27815,7 +27815,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A287" s="9">
         <v>287</v>
       </c>
@@ -27892,7 +27892,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A288" s="9">
         <v>288</v>
       </c>
@@ -27969,7 +27969,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A289" s="9">
         <v>289</v>
       </c>
@@ -28046,7 +28046,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A290" s="9">
         <v>290</v>
       </c>
@@ -28123,7 +28123,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="9">
         <v>291</v>
       </c>
@@ -28200,7 +28200,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A292" s="9">
         <v>292</v>
       </c>
@@ -28277,7 +28277,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A293" s="9">
         <v>293</v>
       </c>
@@ -28354,7 +28354,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A294" s="9">
         <v>294</v>
       </c>
@@ -28431,7 +28431,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A295" s="9">
         <v>295</v>
       </c>
@@ -28508,7 +28508,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A296" s="9">
         <v>296</v>
       </c>
@@ -28585,7 +28585,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A297" s="9">
         <v>297</v>
       </c>
@@ -28662,7 +28662,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A298" s="9">
         <v>298</v>
       </c>
@@ -28739,7 +28739,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A299" s="9">
         <v>299</v>
       </c>
@@ -28816,7 +28816,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A300" s="9">
         <v>300</v>
       </c>
@@ -28893,7 +28893,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A301" s="9">
         <v>301</v>
       </c>
@@ -28970,7 +28970,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A302" s="9">
         <v>302</v>
       </c>
@@ -29047,7 +29047,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A303" s="9">
         <v>303</v>
       </c>
@@ -29124,7 +29124,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A304" s="9">
         <v>304</v>
       </c>
@@ -29201,7 +29201,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:25" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A305" s="9">
         <v>305</v>
       </c>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDBAADAA-27DC-4C60-8C09-E04E7B84874C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA66E02-988E-4EA3-A20D-D4DFA67B427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -3868,7 +3868,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46165.61323101852</v>
+        <v>46165.662863194448</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>691</v>
@@ -7160,7 +7160,7 @@
   <cols>
     <col min="1" max="1" width="3.69921875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.3984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.796875" style="2" customWidth="1"/>
     <col min="4" max="5" width="8" style="2" customWidth="1"/>
     <col min="6" max="6" width="5" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="4.296875" customWidth="1"/>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFA66E02-988E-4EA3-A20D-D4DFA67B427B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ACF6D8-B71C-470C-986B-B5090EAB50B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7996" uniqueCount="844">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7996" uniqueCount="850">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2229,54 +2229,33 @@
     <t>No.Projeto</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definição do Projeto.</t>
-  </si>
-  <si>
-    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
     <t>Interdisciplinar</t>
   </si>
   <si>
-    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</t>
-  </si>
-  <si>
     <t>Requerida</t>
   </si>
   <si>
     <t>Requisito.Espacial</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Espaciais para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Mobiliário</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Mobiliários para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Equipamento</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos Equipamentos para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
   </si>
   <si>
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
-  </si>
-  <si>
     <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
   </si>
   <si>
@@ -2505,9 +2484,6 @@
     <t>NBR.Subtema</t>
   </si>
   <si>
-    <t>NBR.Serviço</t>
-  </si>
-  <si>
     <t>[ 1S.10 ]</t>
   </si>
   <si>
@@ -2623,6 +2599,48 @@
   </si>
   <si>
     <t>NBR.S.Adicional</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Definições do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Definiciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Project Definitions.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Espaciais do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos Espaciales del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Mobiliários do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Mobiliarios del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos Equipamentos do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Equipamiento del Proyecto.</t>
+  </si>
+  <si>
+    <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requisitos de Sistemas Prediais do Projeto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de Instalaciones del Proyecto.</t>
+  </si>
+  <si>
+    <t>NBR.Serviços</t>
+  </si>
+  <si>
+    <t>"Serviços para a Construção"</t>
+  </si>
+  <si>
+    <t>"Parte 3 da NBR 15.965"</t>
   </si>
 </sst>
 </file>
@@ -3118,7 +3136,119 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="36">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3868,7 +3998,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46165.662863194448</v>
+        <v>46167.411252314814</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>691</v>
@@ -3973,7 +4103,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr defaultRowHeight="10.75" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="6.55" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.69921875" style="29" bestFit="1" customWidth="1"/>
@@ -4000,7 +4130,7 @@
     <col min="27" max="27" width="79.296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="30.9" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="27.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4083,7 +4213,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48">
         <v>2</v>
       </c>
@@ -4118,7 +4248,7 @@
         <v>321</v>
       </c>
       <c r="L2" s="52" t="str">
-        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
         <v>Contêiner</v>
       </c>
       <c r="M2" s="52" t="str">
@@ -4134,10 +4264,10 @@
         <v>No Projeto</v>
       </c>
       <c r="P2" s="37" t="s">
-        <v>712</v>
+        <v>836</v>
       </c>
       <c r="Q2" s="37" t="s">
-        <v>713</v>
+        <v>837</v>
       </c>
       <c r="R2" s="53" t="s">
         <v>321</v>
@@ -4155,10 +4285,10 @@
         <v>Definida</v>
       </c>
       <c r="V2" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W2" s="55" t="str">
-        <f>CONCATENATE("Key.ABNT.",A2)</f>
+        <f t="shared" ref="W2:W6" si="3">CONCATENATE("Key.ABNT.",A2)</f>
         <v>Key.ABNT.2</v>
       </c>
       <c r="X2" s="37" t="s">
@@ -4171,10 +4301,10 @@
         <v>321</v>
       </c>
       <c r="AA2" s="37" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="48">
         <v>3</v>
       </c>
@@ -4188,10 +4318,10 @@
         <v>709</v>
       </c>
       <c r="E3" s="49" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F3" s="50" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G3" s="51" t="s">
         <v>321</v>
@@ -4225,10 +4355,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="37" t="s">
-        <v>718</v>
+        <v>839</v>
       </c>
       <c r="Q3" s="37" t="s">
-        <v>713</v>
+        <v>840</v>
       </c>
       <c r="R3" s="53" t="s">
         <v>321</v>
@@ -4246,10 +4376,10 @@
         <v>Requerida</v>
       </c>
       <c r="V3" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W3" s="55" t="str">
-        <f t="shared" ref="W3:W32" si="3">CONCATENATE("Key.ABNT.",A3)</f>
+        <f t="shared" si="3"/>
         <v>Key.ABNT.3</v>
       </c>
       <c r="X3" s="37" t="s">
@@ -4262,10 +4392,10 @@
         <v>321</v>
       </c>
       <c r="AA3" s="37" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="48">
         <v>4</v>
       </c>
@@ -4279,10 +4409,10 @@
         <v>709</v>
       </c>
       <c r="E4" s="49" t="s">
+        <v>713</v>
+      </c>
+      <c r="F4" s="50" t="s">
         <v>716</v>
-      </c>
-      <c r="F4" s="50" t="s">
-        <v>720</v>
       </c>
       <c r="G4" s="51" t="s">
         <v>321</v>
@@ -4316,10 +4446,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="37" t="s">
-        <v>721</v>
+        <v>841</v>
       </c>
       <c r="Q4" s="37" t="s">
-        <v>713</v>
+        <v>842</v>
       </c>
       <c r="R4" s="53" t="s">
         <v>321</v>
@@ -4337,7 +4467,7 @@
         <v>Requerida</v>
       </c>
       <c r="V4" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W4" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4353,10 +4483,10 @@
         <v>321</v>
       </c>
       <c r="AA4" s="37" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="48">
         <v>5</v>
       </c>
@@ -4370,10 +4500,10 @@
         <v>709</v>
       </c>
       <c r="E5" s="49" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F5" s="50" t="s">
-        <v>723</v>
+        <v>718</v>
       </c>
       <c r="G5" s="51" t="s">
         <v>321</v>
@@ -4407,10 +4537,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="37" t="s">
-        <v>724</v>
+        <v>843</v>
       </c>
       <c r="Q5" s="37" t="s">
-        <v>713</v>
+        <v>844</v>
       </c>
       <c r="R5" s="53" t="s">
         <v>321</v>
@@ -4428,7 +4558,7 @@
         <v>Requerida</v>
       </c>
       <c r="V5" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W5" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4444,10 +4574,10 @@
         <v>321</v>
       </c>
       <c r="AA5" s="37" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="48">
         <v>6</v>
       </c>
@@ -4461,10 +4591,10 @@
         <v>709</v>
       </c>
       <c r="E6" s="49" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="F6" s="50" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="G6" s="51" t="s">
         <v>321</v>
@@ -4498,10 +4628,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="37" t="s">
-        <v>727</v>
+        <v>845</v>
       </c>
       <c r="Q6" s="37" t="s">
-        <v>713</v>
+        <v>846</v>
       </c>
       <c r="R6" s="53" t="s">
         <v>321</v>
@@ -4519,7 +4649,7 @@
         <v>Requerida</v>
       </c>
       <c r="V6" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W6" s="55" t="str">
         <f t="shared" si="3"/>
@@ -4535,10 +4665,10 @@
         <v>321</v>
       </c>
       <c r="AA6" s="37" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="48">
         <v>7</v>
       </c>
@@ -4552,10 +4682,10 @@
         <v>656</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F7" s="21" t="s">
-        <v>789</v>
+        <v>782</v>
       </c>
       <c r="G7" s="31" t="s">
         <v>321</v>
@@ -4573,47 +4703,47 @@
         <v>321</v>
       </c>
       <c r="L7" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="L7:N17" si="4">CONCATENATE("", C7)</f>
         <v>Norma</v>
       </c>
       <c r="M7" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="52" t="str">
-        <f t="shared" ref="O7:O32" si="4">F7</f>
+        <f t="shared" ref="O7:O32" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="52" t="s">
-        <v>729</v>
+        <v>722</v>
       </c>
       <c r="Q7" s="52" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="R7" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S7" s="54" t="str">
-        <f t="shared" ref="S7:U22" si="5">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U22" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Norma</v>
       </c>
       <c r="T7" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U7" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W7" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="W7:W32" si="7">CONCATENATE("Key.ABNT.",A7)</f>
         <v>Key.ABNT.7</v>
       </c>
       <c r="X7" s="37" t="s">
@@ -4623,13 +4753,13 @@
         <v>321</v>
       </c>
       <c r="Z7" s="37" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="AA7" s="56" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="48">
         <v>8</v>
       </c>
@@ -4643,10 +4773,10 @@
         <v>656</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F8" s="21" t="s">
-        <v>790</v>
+        <v>783</v>
       </c>
       <c r="G8" s="31" t="s">
         <v>321</v>
@@ -4664,47 +4794,47 @@
         <v>321</v>
       </c>
       <c r="L8" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M8" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N8" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O8" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="52" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="Q8" s="52" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="R8" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S8" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T8" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U8" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W8" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.8</v>
       </c>
       <c r="X8" s="37" t="s">
@@ -4714,13 +4844,13 @@
         <v>321</v>
       </c>
       <c r="Z8" s="37" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="AA8" s="56" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="48">
         <v>9</v>
       </c>
@@ -4734,10 +4864,10 @@
         <v>656</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>791</v>
+        <v>784</v>
       </c>
       <c r="G9" s="31" t="s">
         <v>321</v>
@@ -4755,47 +4885,47 @@
         <v>321</v>
       </c>
       <c r="L9" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M9" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N9" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O9" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="52" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="Q9" s="52" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="R9" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S9" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T9" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U9" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W9" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.9</v>
       </c>
       <c r="X9" s="37" t="s">
@@ -4805,13 +4935,13 @@
         <v>321</v>
       </c>
       <c r="Z9" s="37" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="AA9" s="56" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="48">
         <v>10</v>
       </c>
@@ -4825,10 +4955,10 @@
         <v>656</v>
       </c>
       <c r="E10" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F10" s="21" t="s">
-        <v>792</v>
+        <v>785</v>
       </c>
       <c r="G10" s="31" t="s">
         <v>321</v>
@@ -4846,47 +4976,47 @@
         <v>321</v>
       </c>
       <c r="L10" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M10" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N10" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O10" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="52" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="Q10" s="52" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="R10" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S10" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T10" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U10" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W10" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.10</v>
       </c>
       <c r="X10" s="37" t="s">
@@ -4896,13 +5026,13 @@
         <v>321</v>
       </c>
       <c r="Z10" s="37" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="AA10" s="56" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="48">
         <v>11</v>
       </c>
@@ -4916,10 +5046,10 @@
         <v>656</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="G11" s="31" t="s">
         <v>321</v>
@@ -4937,47 +5067,47 @@
         <v>321</v>
       </c>
       <c r="L11" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M11" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N11" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O11" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="52" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="Q11" s="52" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="R11" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S11" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T11" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U11" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W11" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.11</v>
       </c>
       <c r="X11" s="37" t="s">
@@ -4990,10 +5120,10 @@
         <v>624</v>
       </c>
       <c r="AA11" s="56" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="48">
         <v>12</v>
       </c>
@@ -5007,10 +5137,10 @@
         <v>656</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>794</v>
+        <v>787</v>
       </c>
       <c r="G12" s="31" t="s">
         <v>321</v>
@@ -5028,47 +5158,47 @@
         <v>321</v>
       </c>
       <c r="L12" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M12" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N12" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O12" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="52" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="Q12" s="52" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="R12" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S12" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T12" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U12" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W12" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.12</v>
       </c>
       <c r="X12" s="37" t="s">
@@ -5078,13 +5208,13 @@
         <v>321</v>
       </c>
       <c r="Z12" s="37" t="s">
-        <v>750</v>
+        <v>743</v>
       </c>
       <c r="AA12" s="56" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="48">
         <v>13</v>
       </c>
@@ -5098,11 +5228,11 @@
         <v>656</v>
       </c>
       <c r="E13" s="28" t="s">
+        <v>781</v>
+      </c>
+      <c r="F13" s="21" t="s">
         <v>788</v>
       </c>
-      <c r="F13" s="21" t="s">
-        <v>795</v>
-      </c>
       <c r="G13" s="31" t="s">
         <v>321</v>
       </c>
@@ -5119,47 +5249,47 @@
         <v>321</v>
       </c>
       <c r="L13" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M13" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N13" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O13" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="52" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="Q13" s="52" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="R13" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S13" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T13" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U13" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W13" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.13</v>
       </c>
       <c r="X13" s="37" t="s">
@@ -5169,13 +5299,13 @@
         <v>321</v>
       </c>
       <c r="Z13" s="37" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="AA13" s="56" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="48">
         <v>14</v>
       </c>
@@ -5189,10 +5319,10 @@
         <v>656</v>
       </c>
       <c r="E14" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F14" s="21" t="s">
-        <v>796</v>
+        <v>789</v>
       </c>
       <c r="G14" s="31" t="s">
         <v>321</v>
@@ -5210,47 +5340,47 @@
         <v>321</v>
       </c>
       <c r="L14" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M14" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N14" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O14" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="52" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="Q14" s="52" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="R14" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S14" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T14" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U14" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W14" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.14</v>
       </c>
       <c r="X14" s="37" t="s">
@@ -5260,13 +5390,13 @@
         <v>321</v>
       </c>
       <c r="Z14" s="37" t="s">
-        <v>753</v>
+        <v>746</v>
       </c>
       <c r="AA14" s="56" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="48">
         <v>15</v>
       </c>
@@ -5280,10 +5410,10 @@
         <v>656</v>
       </c>
       <c r="E15" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>797</v>
+        <v>790</v>
       </c>
       <c r="G15" s="31" t="s">
         <v>321</v>
@@ -5301,47 +5431,47 @@
         <v>321</v>
       </c>
       <c r="L15" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M15" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N15" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O15" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="52" t="s">
-        <v>754</v>
+        <v>747</v>
       </c>
       <c r="Q15" s="52" t="s">
-        <v>755</v>
+        <v>748</v>
       </c>
       <c r="R15" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S15" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T15" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U15" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W15" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.15</v>
       </c>
       <c r="X15" s="37" t="s">
@@ -5351,13 +5481,13 @@
         <v>321</v>
       </c>
       <c r="Z15" s="37" t="s">
-        <v>756</v>
+        <v>749</v>
       </c>
       <c r="AA15" s="56" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="48">
         <v>16</v>
       </c>
@@ -5371,10 +5501,10 @@
         <v>656</v>
       </c>
       <c r="E16" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="G16" s="31" t="s">
         <v>321</v>
@@ -5392,47 +5522,47 @@
         <v>321</v>
       </c>
       <c r="L16" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M16" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N16" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O16" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="52" t="s">
-        <v>758</v>
+        <v>751</v>
       </c>
       <c r="Q16" s="52" t="s">
-        <v>759</v>
+        <v>752</v>
       </c>
       <c r="R16" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S16" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T16" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U16" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W16" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.16</v>
       </c>
       <c r="X16" s="37" t="s">
@@ -5442,13 +5572,13 @@
         <v>321</v>
       </c>
       <c r="Z16" s="37" t="s">
-        <v>760</v>
+        <v>753</v>
       </c>
       <c r="AA16" s="56" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="48">
         <v>17</v>
       </c>
@@ -5462,10 +5592,10 @@
         <v>656</v>
       </c>
       <c r="E17" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="G17" s="31" t="s">
         <v>321</v>
@@ -5483,47 +5613,47 @@
         <v>321</v>
       </c>
       <c r="L17" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>Norma</v>
       </c>
       <c r="M17" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>ABNT</v>
       </c>
       <c r="N17" s="52" t="str">
-        <f t="shared" si="0"/>
+        <f t="shared" si="4"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O17" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="52" t="s">
-        <v>762</v>
+        <v>755</v>
       </c>
       <c r="Q17" s="52" t="s">
-        <v>763</v>
+        <v>756</v>
       </c>
       <c r="R17" s="53" t="s">
         <v>321</v>
       </c>
       <c r="S17" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
       <c r="T17" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U17" s="52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W17" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.17</v>
       </c>
       <c r="X17" s="37" t="s">
@@ -5533,13 +5663,13 @@
         <v>321</v>
       </c>
       <c r="Z17" s="37" t="s">
-        <v>764</v>
+        <v>757</v>
       </c>
       <c r="AA17" s="56" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="48">
         <v>18</v>
       </c>
@@ -5553,10 +5683,10 @@
         <v>656</v>
       </c>
       <c r="E18" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F18" s="21" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>321</v>
@@ -5574,47 +5704,47 @@
         <v>321</v>
       </c>
       <c r="L18" s="52" t="str">
-        <f t="shared" ref="L18:N32" si="6">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N32" si="8">CONCATENATE("", C18)</f>
         <v>Norma</v>
       </c>
       <c r="M18" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N18" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O18" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="52" t="s">
+        <v>759</v>
+      </c>
+      <c r="Q18" s="52" t="s">
+        <v>760</v>
+      </c>
+      <c r="R18" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S18" s="54" t="str">
+        <f t="shared" si="6"/>
+        <v>Norma</v>
+      </c>
+      <c r="T18" s="54" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N18" s="52" t="str">
+      <c r="U18" s="52" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O18" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="52" t="s">
-        <v>766</v>
-      </c>
-      <c r="Q18" s="52" t="s">
-        <v>767</v>
-      </c>
-      <c r="R18" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S18" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T18" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U18" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V18" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W18" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.18</v>
       </c>
       <c r="X18" s="37" t="s">
@@ -5624,13 +5754,13 @@
         <v>321</v>
       </c>
       <c r="Z18" s="37" t="s">
-        <v>768</v>
+        <v>761</v>
       </c>
       <c r="AA18" s="56" t="s">
-        <v>769</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="48">
         <v>19</v>
       </c>
@@ -5644,10 +5774,10 @@
         <v>656</v>
       </c>
       <c r="E19" s="28" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="F19" s="21" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="G19" s="31" t="s">
         <v>321</v>
@@ -5665,47 +5795,47 @@
         <v>321</v>
       </c>
       <c r="L19" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>Norma</v>
+      </c>
+      <c r="M19" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N19" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O19" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="52" t="s">
+        <v>763</v>
+      </c>
+      <c r="Q19" s="52" t="s">
+        <v>764</v>
+      </c>
+      <c r="R19" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S19" s="54" t="str">
         <f t="shared" si="6"/>
         <v>Norma</v>
       </c>
-      <c r="M19" s="52" t="str">
+      <c r="T19" s="54" t="str">
         <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N19" s="52" t="str">
+      <c r="U19" s="52" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O19" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="52" t="s">
-        <v>770</v>
-      </c>
-      <c r="Q19" s="52" t="s">
-        <v>771</v>
-      </c>
-      <c r="R19" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S19" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>Norma</v>
-      </c>
-      <c r="T19" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U19" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V19" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W19" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.19</v>
       </c>
       <c r="X19" s="37" t="s">
@@ -5715,13 +5845,13 @@
         <v>321</v>
       </c>
       <c r="Z19" s="37" t="s">
-        <v>772</v>
+        <v>765</v>
       </c>
       <c r="AA19" s="56" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+        <v>766</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="48">
         <v>20</v>
       </c>
@@ -5729,16 +5859,16 @@
         <v>680</v>
       </c>
       <c r="C20" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D20" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="G20" s="51" t="s">
         <v>321</v>
@@ -5756,23 +5886,23 @@
         <v>321</v>
       </c>
       <c r="L20" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M20" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N20" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O20" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Transacional</v>
       </c>
       <c r="P20" s="37" t="s">
-        <v>807</v>
+        <v>799</v>
       </c>
       <c r="Q20" s="37" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -5782,22 +5912,22 @@
         <v>321</v>
       </c>
       <c r="S20" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
       <c r="T20" s="54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="U20" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="6"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="V20" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W20" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.20</v>
       </c>
       <c r="X20" s="37" t="s">
@@ -5807,14 +5937,14 @@
         <v>321</v>
       </c>
       <c r="Z20" s="54" t="s">
-        <v>805</v>
+        <v>797</v>
       </c>
       <c r="AA20" s="37" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
         <v>Transactional services</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="48">
         <v>21</v>
       </c>
@@ -5822,16 +5952,16 @@
         <v>680</v>
       </c>
       <c r="C21" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D21" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E21" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="G21" s="31" t="s">
         <v>321</v>
@@ -5849,48 +5979,48 @@
         <v>321</v>
       </c>
       <c r="L21" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M21" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N21" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="O21" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.S.Administrativo</v>
+      </c>
+      <c r="P21" s="52" t="s">
+        <v>800</v>
+      </c>
+      <c r="Q21" s="37" t="str">
+        <f t="shared" ref="Q21:Q32" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <v>Servicios administrativos</v>
+      </c>
+      <c r="R21" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S21" s="54" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M21" s="52" t="str">
+      <c r="T21" s="54" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N21" s="52" t="str">
+      <c r="U21" s="52" t="str">
         <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="O21" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.S.Administrativo</v>
-      </c>
-      <c r="P21" s="52" t="s">
-        <v>808</v>
-      </c>
-      <c r="Q21" s="37" t="str">
-        <f t="shared" ref="Q21:Q32" si="7">_xlfn.TRANSLATE(P21,"pt","es")</f>
-        <v>Servicios administrativos</v>
-      </c>
-      <c r="R21" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S21" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T21" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U21" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Serviço</v>
+        <v>NBR.Serviços</v>
       </c>
       <c r="V21" s="37" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="W21" s="55" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="7"/>
         <v>Key.ABNT.21</v>
       </c>
       <c r="X21" s="37" t="s">
@@ -5900,14 +6030,14 @@
         <v>321</v>
       </c>
       <c r="Z21" s="54" t="s">
-        <v>806</v>
+        <v>798</v>
       </c>
       <c r="AA21" s="37" t="str">
-        <f t="shared" ref="AA21:AA32" si="8">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA32" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Administrative services</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="48">
         <v>22</v>
       </c>
@@ -5915,16 +6045,16 @@
         <v>680</v>
       </c>
       <c r="C22" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D22" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E22" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="G22" s="31" t="s">
         <v>321</v>
@@ -5942,48 +6072,48 @@
         <v>321</v>
       </c>
       <c r="L22" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M22" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N22" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="O22" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.S.Comunicação</v>
+      </c>
+      <c r="P22" s="52" t="s">
+        <v>801</v>
+      </c>
+      <c r="Q22" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de comunicación</v>
+      </c>
+      <c r="R22" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S22" s="54" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M22" s="52" t="str">
+      <c r="T22" s="54" t="str">
         <f t="shared" si="6"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N22" s="52" t="str">
+      <c r="U22" s="52" t="str">
         <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="O22" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.S.Comunicação</v>
-      </c>
-      <c r="P22" s="52" t="s">
-        <v>809</v>
-      </c>
-      <c r="Q22" s="37" t="str">
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V22" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W22" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de comunicación</v>
-      </c>
-      <c r="R22" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S22" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T22" s="54" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U22" s="52" t="str">
-        <f t="shared" si="5"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V22" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W22" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.22</v>
       </c>
       <c r="X22" s="37" t="s">
@@ -5993,14 +6123,14 @@
         <v>321</v>
       </c>
       <c r="Z22" s="54" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="AA22" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Communication Services</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="48">
         <v>23</v>
       </c>
@@ -6008,75 +6138,75 @@
         <v>680</v>
       </c>
       <c r="C23" s="28" t="s">
+        <v>795</v>
+      </c>
+      <c r="D23" s="28" t="s">
+        <v>796</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>847</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>826</v>
+      </c>
+      <c r="G23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="H23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="I23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="J23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="K23" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="L23" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M23" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N23" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="O23" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.S.Conceituação</v>
+      </c>
+      <c r="P23" s="52" t="s">
         <v>802</v>
       </c>
-      <c r="D23" s="28" t="s">
-        <v>803</v>
-      </c>
-      <c r="E23" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>834</v>
-      </c>
-      <c r="G23" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="H23" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="I23" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="J23" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="K23" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L23" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q23" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de Conceptualización</v>
+      </c>
+      <c r="R23" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S23" s="54" t="str">
+        <f t="shared" ref="S23:U32" si="11">SUBSTITUTE(C23, "_", " ")</f>
         <v>NBR.Tema</v>
       </c>
-      <c r="M23" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="T23" s="54" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N23" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="O23" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.S.Conceituação</v>
-      </c>
-      <c r="P23" s="52" t="s">
-        <v>810</v>
-      </c>
-      <c r="Q23" s="37" t="str">
+      <c r="U23" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V23" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W23" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de Conceptualización</v>
-      </c>
-      <c r="R23" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S23" s="54" t="str">
-        <f t="shared" ref="S23:U32" si="9">SUBSTITUTE(C23, "_", " ")</f>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T23" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U23" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V23" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W23" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.23</v>
       </c>
       <c r="X23" s="37" t="s">
@@ -6086,14 +6216,14 @@
         <v>321</v>
       </c>
       <c r="Z23" s="54" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="AA23" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Conceptualization Services</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="48">
         <v>24</v>
       </c>
@@ -6101,75 +6231,75 @@
         <v>680</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D24" s="28" t="s">
+        <v>796</v>
+      </c>
+      <c r="E24" s="28" t="s">
+        <v>847</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>827</v>
+      </c>
+      <c r="G24" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="H24" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="I24" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="J24" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="K24" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="L24" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M24" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N24" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="O24" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.S.Informação</v>
+      </c>
+      <c r="P24" s="52" t="s">
         <v>803</v>
       </c>
-      <c r="E24" s="28" t="s">
-        <v>804</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>835</v>
-      </c>
-      <c r="G24" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="J24" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="K24" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L24" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q24" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de información</v>
+      </c>
+      <c r="R24" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S24" s="54" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M24" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="T24" s="54" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N24" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="O24" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.S.Informação</v>
-      </c>
-      <c r="P24" s="52" t="s">
-        <v>811</v>
-      </c>
-      <c r="Q24" s="37" t="str">
+      <c r="U24" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V24" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W24" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de información</v>
-      </c>
-      <c r="R24" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S24" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T24" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U24" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V24" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W24" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.24</v>
       </c>
       <c r="X24" s="37" t="s">
@@ -6179,14 +6309,14 @@
         <v>321</v>
       </c>
       <c r="Z24" s="54" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="AA24" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Information services</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="48">
         <v>25</v>
       </c>
@@ -6194,75 +6324,75 @@
         <v>680</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D25" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E25" s="28" t="s">
+        <v>847</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>828</v>
+      </c>
+      <c r="G25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="H25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="I25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="J25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="K25" s="31" t="s">
+        <v>321</v>
+      </c>
+      <c r="L25" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="M25" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="N25" s="52" t="str">
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="O25" s="52" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.S.Organização</v>
+      </c>
+      <c r="P25" s="52" t="s">
         <v>804</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>836</v>
-      </c>
-      <c r="G25" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="J25" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="K25" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="L25" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="Q25" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de organización</v>
+      </c>
+      <c r="R25" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S25" s="54" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Tema</v>
       </c>
-      <c r="M25" s="52" t="str">
-        <f t="shared" si="6"/>
+      <c r="T25" s="54" t="str">
+        <f t="shared" si="11"/>
         <v>NBR.Subtema</v>
       </c>
-      <c r="N25" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="O25" s="52" t="str">
-        <f t="shared" si="4"/>
-        <v>NBR.S.Organização</v>
-      </c>
-      <c r="P25" s="52" t="s">
-        <v>812</v>
-      </c>
-      <c r="Q25" s="37" t="str">
+      <c r="U25" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V25" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W25" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de organización</v>
-      </c>
-      <c r="R25" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S25" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T25" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U25" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V25" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W25" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.25</v>
       </c>
       <c r="X25" s="37" t="s">
@@ -6272,14 +6402,14 @@
         <v>321</v>
       </c>
       <c r="Z25" s="54" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="AA25" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Organization Services</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="48">
         <v>26</v>
       </c>
@@ -6287,16 +6417,16 @@
         <v>680</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D26" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E26" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="G26" s="31" t="s">
         <v>321</v>
@@ -6314,48 +6444,48 @@
         <v>321</v>
       </c>
       <c r="L26" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M26" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N26" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O26" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Projetual</v>
       </c>
       <c r="P26" s="52" t="s">
-        <v>813</v>
+        <v>805</v>
       </c>
       <c r="Q26" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de Desarrollo de Proyectos</v>
+      </c>
+      <c r="R26" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S26" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T26" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U26" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V26" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W26" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de Desarrollo de Proyectos</v>
-      </c>
-      <c r="R26" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S26" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T26" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U26" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V26" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W26" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.26</v>
       </c>
       <c r="X26" s="37" t="s">
@@ -6365,14 +6495,14 @@
         <v>321</v>
       </c>
       <c r="Z26" s="54" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="AA26" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Project Development Services</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="48">
         <v>27</v>
       </c>
@@ -6380,16 +6510,16 @@
         <v>680</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D27" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E27" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="G27" s="31" t="s">
         <v>321</v>
@@ -6407,48 +6537,48 @@
         <v>321</v>
       </c>
       <c r="L27" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M27" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N27" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O27" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Documental</v>
       </c>
       <c r="P27" s="52" t="s">
-        <v>814</v>
+        <v>806</v>
       </c>
       <c r="Q27" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de Documentos</v>
+      </c>
+      <c r="R27" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S27" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T27" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U27" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V27" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W27" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de Documentos</v>
-      </c>
-      <c r="R27" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S27" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T27" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U27" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V27" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W27" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.27</v>
       </c>
       <c r="X27" s="37" t="s">
@@ -6458,14 +6588,14 @@
         <v>321</v>
       </c>
       <c r="Z27" s="54" t="s">
-        <v>823</v>
+        <v>815</v>
       </c>
       <c r="AA27" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Document Services</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="48">
         <v>28</v>
       </c>
@@ -6473,16 +6603,16 @@
         <v>680</v>
       </c>
       <c r="C28" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D28" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E28" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="G28" s="31" t="s">
         <v>321</v>
@@ -6500,48 +6630,48 @@
         <v>321</v>
       </c>
       <c r="L28" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M28" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N28" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O28" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Implementação</v>
       </c>
       <c r="P28" s="52" t="s">
-        <v>815</v>
+        <v>807</v>
       </c>
       <c r="Q28" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de Implementación</v>
+      </c>
+      <c r="R28" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S28" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T28" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U28" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V28" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W28" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de Implementación</v>
-      </c>
-      <c r="R28" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S28" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T28" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U28" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V28" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W28" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.28</v>
       </c>
       <c r="X28" s="37" t="s">
@@ -6551,14 +6681,14 @@
         <v>321</v>
       </c>
       <c r="Z28" s="54" t="s">
-        <v>826</v>
+        <v>818</v>
       </c>
       <c r="AA28" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Implementation Services</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="48">
         <v>29</v>
       </c>
@@ -6566,16 +6696,16 @@
         <v>680</v>
       </c>
       <c r="C29" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D29" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E29" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="G29" s="31" t="s">
         <v>321</v>
@@ -6593,48 +6723,48 @@
         <v>321</v>
       </c>
       <c r="L29" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M29" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N29" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O29" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Operação.Predial</v>
       </c>
       <c r="P29" s="52" t="s">
-        <v>816</v>
+        <v>808</v>
       </c>
       <c r="Q29" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de Operación de Edificios</v>
+      </c>
+      <c r="R29" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S29" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T29" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U29" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V29" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W29" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de Operación de Edificios</v>
-      </c>
-      <c r="R29" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S29" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T29" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U29" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V29" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W29" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.29</v>
       </c>
       <c r="X29" s="37" t="s">
@@ -6644,14 +6774,14 @@
         <v>321</v>
       </c>
       <c r="Z29" s="54" t="s">
-        <v>827</v>
+        <v>819</v>
       </c>
       <c r="AA29" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Building Operation Services</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="48">
         <v>30</v>
       </c>
@@ -6659,16 +6789,16 @@
         <v>680</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D30" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E30" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="G30" s="31" t="s">
         <v>321</v>
@@ -6686,48 +6816,48 @@
         <v>321</v>
       </c>
       <c r="L30" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M30" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N30" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O30" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Suporte</v>
       </c>
       <c r="P30" s="52" t="s">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="Q30" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios de apoyo</v>
+      </c>
+      <c r="R30" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S30" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T30" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U30" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V30" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W30" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios de apoyo</v>
-      </c>
-      <c r="R30" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S30" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T30" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U30" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V30" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W30" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.30</v>
       </c>
       <c r="X30" s="37" t="s">
@@ -6737,14 +6867,14 @@
         <v>321</v>
       </c>
       <c r="Z30" s="54" t="s">
-        <v>828</v>
+        <v>820</v>
       </c>
       <c r="AA30" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Support Services</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="48">
         <v>31</v>
       </c>
@@ -6752,16 +6882,16 @@
         <v>680</v>
       </c>
       <c r="C31" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D31" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E31" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="G31" s="31" t="s">
         <v>321</v>
@@ -6779,48 +6909,48 @@
         <v>321</v>
       </c>
       <c r="L31" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M31" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N31" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O31" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Governo</v>
       </c>
       <c r="P31" s="52" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="Q31" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios gubernamentales</v>
+      </c>
+      <c r="R31" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S31" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T31" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U31" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V31" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W31" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios gubernamentales</v>
-      </c>
-      <c r="R31" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S31" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T31" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U31" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V31" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W31" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.31</v>
       </c>
       <c r="X31" s="37" t="s">
@@ -6830,14 +6960,14 @@
         <v>321</v>
       </c>
       <c r="Z31" s="54" t="s">
-        <v>829</v>
+        <v>821</v>
       </c>
       <c r="AA31" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Government Services</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="7.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:27" ht="6.55" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="48">
         <v>32</v>
       </c>
@@ -6845,16 +6975,16 @@
         <v>680</v>
       </c>
       <c r="C32" s="28" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="D32" s="28" t="s">
-        <v>803</v>
+        <v>796</v>
       </c>
       <c r="E32" s="28" t="s">
-        <v>804</v>
+        <v>847</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="G32" s="31" t="s">
         <v>321</v>
@@ -6872,48 +7002,48 @@
         <v>321</v>
       </c>
       <c r="L32" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Tema</v>
       </c>
       <c r="M32" s="52" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="8"/>
         <v>NBR.Subtema</v>
       </c>
       <c r="N32" s="52" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.Serviço</v>
+        <f t="shared" si="8"/>
+        <v>NBR.Serviços</v>
       </c>
       <c r="O32" s="52" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>NBR.S.Adicional</v>
       </c>
       <c r="P32" s="52" t="s">
-        <v>819</v>
+        <v>811</v>
       </c>
       <c r="Q32" s="37" t="str">
+        <f t="shared" si="9"/>
+        <v>Servicios adicionales</v>
+      </c>
+      <c r="R32" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="S32" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Tema</v>
+      </c>
+      <c r="T32" s="54" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Subtema</v>
+      </c>
+      <c r="U32" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>NBR.Serviços</v>
+      </c>
+      <c r="V32" s="37" t="s">
+        <v>712</v>
+      </c>
+      <c r="W32" s="55" t="str">
         <f t="shared" si="7"/>
-        <v>Servicios adicionales</v>
-      </c>
-      <c r="R32" s="53" t="s">
-        <v>321</v>
-      </c>
-      <c r="S32" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Tema</v>
-      </c>
-      <c r="T32" s="54" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Subtema</v>
-      </c>
-      <c r="U32" s="52" t="str">
-        <f t="shared" si="9"/>
-        <v>NBR.Serviço</v>
-      </c>
-      <c r="V32" s="37" t="s">
-        <v>714</v>
-      </c>
-      <c r="W32" s="55" t="str">
-        <f t="shared" si="3"/>
         <v>Key.ABNT.32</v>
       </c>
       <c r="X32" s="37" t="s">
@@ -6923,33 +7053,43 @@
         <v>321</v>
       </c>
       <c r="Z32" s="54" t="s">
-        <v>830</v>
+        <v>822</v>
       </c>
       <c r="AA32" s="37" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="10"/>
         <v>Additional services</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:A32">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+  <conditionalFormatting sqref="A7:A32">
+    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1 AA7:AA32">
+    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A2:A6">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="18" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA32">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA2:AA6">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7099,7 +7239,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7144,7 +7284,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7168,7 +7308,7 @@
     <col min="10" max="10" width="3.69921875" customWidth="1"/>
     <col min="11" max="11" width="7.69921875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.5" customWidth="1"/>
-    <col min="13" max="13" width="20.5" customWidth="1"/>
+    <col min="13" max="13" width="27" customWidth="1"/>
     <col min="14" max="14" width="6.296875" customWidth="1"/>
     <col min="15" max="15" width="32.5" style="34" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="3.69921875" bestFit="1" customWidth="1"/>
@@ -7281,13 +7421,13 @@
         <v>628</v>
       </c>
       <c r="K2" s="35" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="L2" s="43" t="s">
         <v>683</v>
       </c>
       <c r="M2" s="35" t="s">
-        <v>775</v>
+        <v>768</v>
       </c>
       <c r="N2" s="32" t="s">
         <v>1</v>
@@ -7334,10 +7474,10 @@
         <v>631</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>788</v>
+        <v>781</v>
       </c>
       <c r="D3" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E3" s="58" t="s">
         <v>625</v>
@@ -7358,13 +7498,13 @@
         <v>628</v>
       </c>
       <c r="K3" s="35" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="L3" s="43" t="s">
         <v>683</v>
       </c>
       <c r="M3" s="35" t="s">
-        <v>775</v>
+        <v>849</v>
       </c>
       <c r="N3" s="32" t="s">
         <v>1</v>
@@ -7411,10 +7551,10 @@
         <v>624</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>793</v>
+        <v>786</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E4" s="58" t="s">
         <v>631</v>
@@ -7435,13 +7575,13 @@
         <v>628</v>
       </c>
       <c r="K4" s="35" t="s">
-        <v>774</v>
+        <v>767</v>
       </c>
       <c r="L4" s="43" t="s">
         <v>683</v>
       </c>
       <c r="M4" s="35" t="s">
-        <v>775</v>
+        <v>848</v>
       </c>
       <c r="N4" s="32" t="s">
         <v>1</v>
@@ -7488,10 +7628,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E5" s="58" t="s">
         <v>631</v>
@@ -7518,7 +7658,7 @@
         <v>683</v>
       </c>
       <c r="M5" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N5" s="32" t="s">
         <v>1</v>
@@ -7565,10 +7705,10 @@
         <v>329</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E6" s="58" t="s">
         <v>631</v>
@@ -7595,7 +7735,7 @@
         <v>683</v>
       </c>
       <c r="M6" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N6" s="32" t="s">
         <v>1</v>
@@ -7642,10 +7782,10 @@
         <v>330</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E7" s="58" t="s">
         <v>631</v>
@@ -7672,7 +7812,7 @@
         <v>683</v>
       </c>
       <c r="M7" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N7" s="32" t="s">
         <v>1</v>
@@ -7719,10 +7859,10 @@
         <v>331</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E8" s="58" t="s">
         <v>631</v>
@@ -7749,7 +7889,7 @@
         <v>683</v>
       </c>
       <c r="M8" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N8" s="32" t="s">
         <v>1</v>
@@ -7796,10 +7936,10 @@
         <v>332</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D9" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E9" s="58" t="s">
         <v>631</v>
@@ -7826,7 +7966,7 @@
         <v>683</v>
       </c>
       <c r="M9" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N9" s="32" t="s">
         <v>1</v>
@@ -7873,10 +8013,10 @@
         <v>333</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D10" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E10" s="58" t="s">
         <v>631</v>
@@ -7903,7 +8043,7 @@
         <v>683</v>
       </c>
       <c r="M10" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N10" s="32" t="s">
         <v>1</v>
@@ -7950,10 +8090,10 @@
         <v>334</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E11" s="58" t="s">
         <v>631</v>
@@ -7980,7 +8120,7 @@
         <v>683</v>
       </c>
       <c r="M11" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N11" s="32" t="s">
         <v>1</v>
@@ -8027,10 +8167,10 @@
         <v>335</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E12" s="58" t="s">
         <v>631</v>
@@ -8057,7 +8197,7 @@
         <v>683</v>
       </c>
       <c r="M12" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N12" s="32" t="s">
         <v>1</v>
@@ -8104,10 +8244,10 @@
         <v>336</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E13" s="58" t="s">
         <v>631</v>
@@ -8134,7 +8274,7 @@
         <v>683</v>
       </c>
       <c r="M13" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N13" s="32" t="s">
         <v>1</v>
@@ -8181,10 +8321,10 @@
         <v>337</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E14" s="58" t="s">
         <v>631</v>
@@ -8211,7 +8351,7 @@
         <v>683</v>
       </c>
       <c r="M14" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N14" s="32" t="s">
         <v>1</v>
@@ -8258,10 +8398,10 @@
         <v>338</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D15" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E15" s="58" t="s">
         <v>631</v>
@@ -8288,7 +8428,7 @@
         <v>683</v>
       </c>
       <c r="M15" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N15" s="32" t="s">
         <v>1</v>
@@ -8335,10 +8475,10 @@
         <v>339</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E16" s="58" t="s">
         <v>631</v>
@@ -8365,7 +8505,7 @@
         <v>683</v>
       </c>
       <c r="M16" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N16" s="32" t="s">
         <v>1</v>
@@ -8412,10 +8552,10 @@
         <v>340</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E17" s="58" t="s">
         <v>631</v>
@@ -8442,7 +8582,7 @@
         <v>683</v>
       </c>
       <c r="M17" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N17" s="32" t="s">
         <v>1</v>
@@ -8489,10 +8629,10 @@
         <v>341</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E18" s="58" t="s">
         <v>631</v>
@@ -8519,7 +8659,7 @@
         <v>683</v>
       </c>
       <c r="M18" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N18" s="32" t="s">
         <v>1</v>
@@ -8566,10 +8706,10 @@
         <v>342</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D19" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E19" s="58" t="s">
         <v>631</v>
@@ -8596,7 +8736,7 @@
         <v>683</v>
       </c>
       <c r="M19" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N19" s="32" t="s">
         <v>1</v>
@@ -8643,10 +8783,10 @@
         <v>343</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D20" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E20" s="58" t="s">
         <v>631</v>
@@ -8673,7 +8813,7 @@
         <v>683</v>
       </c>
       <c r="M20" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N20" s="32" t="s">
         <v>1</v>
@@ -8720,10 +8860,10 @@
         <v>344</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D21" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E21" s="58" t="s">
         <v>631</v>
@@ -8750,7 +8890,7 @@
         <v>683</v>
       </c>
       <c r="M21" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N21" s="32" t="s">
         <v>1</v>
@@ -8797,10 +8937,10 @@
         <v>345</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D22" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E22" s="58" t="s">
         <v>631</v>
@@ -8827,7 +8967,7 @@
         <v>683</v>
       </c>
       <c r="M22" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N22" s="32" t="s">
         <v>1</v>
@@ -8874,10 +9014,10 @@
         <v>346</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D23" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E23" s="58" t="s">
         <v>631</v>
@@ -8904,7 +9044,7 @@
         <v>683</v>
       </c>
       <c r="M23" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N23" s="32" t="s">
         <v>1</v>
@@ -8951,10 +9091,10 @@
         <v>347</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E24" s="58" t="s">
         <v>631</v>
@@ -8981,7 +9121,7 @@
         <v>683</v>
       </c>
       <c r="M24" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N24" s="32" t="s">
         <v>1</v>
@@ -9028,10 +9168,10 @@
         <v>348</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D25" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E25" s="58" t="s">
         <v>631</v>
@@ -9058,7 +9198,7 @@
         <v>683</v>
       </c>
       <c r="M25" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N25" s="32" t="s">
         <v>1</v>
@@ -9105,10 +9245,10 @@
         <v>349</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D26" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E26" s="58" t="s">
         <v>631</v>
@@ -9135,7 +9275,7 @@
         <v>683</v>
       </c>
       <c r="M26" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N26" s="32" t="s">
         <v>1</v>
@@ -9182,10 +9322,10 @@
         <v>350</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D27" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E27" s="58" t="s">
         <v>631</v>
@@ -9212,7 +9352,7 @@
         <v>683</v>
       </c>
       <c r="M27" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N27" s="32" t="s">
         <v>1</v>
@@ -9259,10 +9399,10 @@
         <v>351</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D28" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E28" s="58" t="s">
         <v>631</v>
@@ -9289,7 +9429,7 @@
         <v>683</v>
       </c>
       <c r="M28" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N28" s="32" t="s">
         <v>1</v>
@@ -9336,10 +9476,10 @@
         <v>352</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D29" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E29" s="58" t="s">
         <v>631</v>
@@ -9366,7 +9506,7 @@
         <v>683</v>
       </c>
       <c r="M29" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N29" s="32" t="s">
         <v>1</v>
@@ -9413,10 +9553,10 @@
         <v>353</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E30" s="58" t="s">
         <v>631</v>
@@ -9443,7 +9583,7 @@
         <v>683</v>
       </c>
       <c r="M30" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N30" s="32" t="s">
         <v>1</v>
@@ -9490,10 +9630,10 @@
         <v>354</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>831</v>
+        <v>823</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E31" s="58" t="s">
         <v>631</v>
@@ -9520,7 +9660,7 @@
         <v>683</v>
       </c>
       <c r="M31" s="35" t="s">
-        <v>777</v>
+        <v>770</v>
       </c>
       <c r="N31" s="32" t="s">
         <v>1</v>
@@ -9567,10 +9707,10 @@
         <v>355</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D32" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E32" s="58" t="s">
         <v>631</v>
@@ -9597,7 +9737,7 @@
         <v>683</v>
       </c>
       <c r="M32" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N32" s="32" t="s">
         <v>1</v>
@@ -9644,10 +9784,10 @@
         <v>356</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D33" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E33" s="58" t="s">
         <v>631</v>
@@ -9674,7 +9814,7 @@
         <v>683</v>
       </c>
       <c r="M33" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N33" s="32" t="s">
         <v>1</v>
@@ -9721,10 +9861,10 @@
         <v>357</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D34" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E34" s="58" t="s">
         <v>631</v>
@@ -9751,7 +9891,7 @@
         <v>683</v>
       </c>
       <c r="M34" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N34" s="32" t="s">
         <v>1</v>
@@ -9798,10 +9938,10 @@
         <v>358</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D35" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E35" s="58" t="s">
         <v>631</v>
@@ -9828,7 +9968,7 @@
         <v>683</v>
       </c>
       <c r="M35" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N35" s="32" t="s">
         <v>1</v>
@@ -9875,10 +10015,10 @@
         <v>359</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D36" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E36" s="58" t="s">
         <v>631</v>
@@ -9905,7 +10045,7 @@
         <v>683</v>
       </c>
       <c r="M36" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N36" s="32" t="s">
         <v>1</v>
@@ -9952,10 +10092,10 @@
         <v>360</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D37" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E37" s="58" t="s">
         <v>631</v>
@@ -9982,7 +10122,7 @@
         <v>683</v>
       </c>
       <c r="M37" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N37" s="32" t="s">
         <v>1</v>
@@ -10029,10 +10169,10 @@
         <v>361</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D38" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E38" s="58" t="s">
         <v>631</v>
@@ -10059,7 +10199,7 @@
         <v>683</v>
       </c>
       <c r="M38" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N38" s="32" t="s">
         <v>1</v>
@@ -10106,10 +10246,10 @@
         <v>362</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D39" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E39" s="58" t="s">
         <v>631</v>
@@ -10136,7 +10276,7 @@
         <v>683</v>
       </c>
       <c r="M39" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N39" s="32" t="s">
         <v>1</v>
@@ -10183,10 +10323,10 @@
         <v>363</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D40" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E40" s="58" t="s">
         <v>631</v>
@@ -10213,7 +10353,7 @@
         <v>683</v>
       </c>
       <c r="M40" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N40" s="32" t="s">
         <v>1</v>
@@ -10260,10 +10400,10 @@
         <v>364</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D41" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E41" s="58" t="s">
         <v>631</v>
@@ -10290,7 +10430,7 @@
         <v>683</v>
       </c>
       <c r="M41" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N41" s="32" t="s">
         <v>1</v>
@@ -10337,10 +10477,10 @@
         <v>365</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D42" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E42" s="58" t="s">
         <v>631</v>
@@ -10367,7 +10507,7 @@
         <v>683</v>
       </c>
       <c r="M42" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N42" s="32" t="s">
         <v>1</v>
@@ -10414,10 +10554,10 @@
         <v>366</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D43" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E43" s="58" t="s">
         <v>631</v>
@@ -10444,7 +10584,7 @@
         <v>683</v>
       </c>
       <c r="M43" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N43" s="32" t="s">
         <v>1</v>
@@ -10491,10 +10631,10 @@
         <v>367</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D44" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E44" s="58" t="s">
         <v>631</v>
@@ -10521,7 +10661,7 @@
         <v>683</v>
       </c>
       <c r="M44" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N44" s="32" t="s">
         <v>1</v>
@@ -10568,10 +10708,10 @@
         <v>704</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D45" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E45" s="58" t="s">
         <v>631</v>
@@ -10598,7 +10738,7 @@
         <v>683</v>
       </c>
       <c r="M45" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N45" s="32" t="s">
         <v>1</v>
@@ -10645,10 +10785,10 @@
         <v>368</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D46" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E46" s="58" t="s">
         <v>631</v>
@@ -10675,7 +10815,7 @@
         <v>683</v>
       </c>
       <c r="M46" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N46" s="32" t="s">
         <v>1</v>
@@ -10722,10 +10862,10 @@
         <v>705</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D47" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E47" s="58" t="s">
         <v>631</v>
@@ -10752,7 +10892,7 @@
         <v>683</v>
       </c>
       <c r="M47" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N47" s="32" t="s">
         <v>1</v>
@@ -10799,10 +10939,10 @@
         <v>369</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D48" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E48" s="58" t="s">
         <v>631</v>
@@ -10829,7 +10969,7 @@
         <v>683</v>
       </c>
       <c r="M48" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N48" s="32" t="s">
         <v>1</v>
@@ -10876,10 +11016,10 @@
         <v>370</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D49" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E49" s="58" t="s">
         <v>631</v>
@@ -10906,7 +11046,7 @@
         <v>683</v>
       </c>
       <c r="M49" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N49" s="32" t="s">
         <v>1</v>
@@ -10953,10 +11093,10 @@
         <v>371</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D50" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E50" s="58" t="s">
         <v>631</v>
@@ -10983,7 +11123,7 @@
         <v>683</v>
       </c>
       <c r="M50" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N50" s="32" t="s">
         <v>1</v>
@@ -11030,10 +11170,10 @@
         <v>372</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D51" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E51" s="58" t="s">
         <v>631</v>
@@ -11060,7 +11200,7 @@
         <v>683</v>
       </c>
       <c r="M51" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N51" s="32" t="s">
         <v>1</v>
@@ -11107,10 +11247,10 @@
         <v>373</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D52" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E52" s="58" t="s">
         <v>631</v>
@@ -11137,7 +11277,7 @@
         <v>683</v>
       </c>
       <c r="M52" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N52" s="32" t="s">
         <v>1</v>
@@ -11184,10 +11324,10 @@
         <v>703</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>832</v>
+        <v>824</v>
       </c>
       <c r="D53" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E53" s="58" t="s">
         <v>631</v>
@@ -11214,7 +11354,7 @@
         <v>683</v>
       </c>
       <c r="M53" s="35" t="s">
-        <v>778</v>
+        <v>771</v>
       </c>
       <c r="N53" s="32" t="s">
         <v>1</v>
@@ -11261,10 +11401,10 @@
         <v>374</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D54" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E54" s="58" t="s">
         <v>631</v>
@@ -11291,7 +11431,7 @@
         <v>683</v>
       </c>
       <c r="M54" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N54" s="32" t="s">
         <v>1</v>
@@ -11338,10 +11478,10 @@
         <v>375</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D55" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E55" s="58" t="s">
         <v>631</v>
@@ -11368,7 +11508,7 @@
         <v>683</v>
       </c>
       <c r="M55" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N55" s="32" t="s">
         <v>1</v>
@@ -11415,10 +11555,10 @@
         <v>376</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D56" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E56" s="58" t="s">
         <v>631</v>
@@ -11445,7 +11585,7 @@
         <v>683</v>
       </c>
       <c r="M56" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N56" s="32" t="s">
         <v>1</v>
@@ -11492,10 +11632,10 @@
         <v>377</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D57" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E57" s="58" t="s">
         <v>631</v>
@@ -11522,7 +11662,7 @@
         <v>683</v>
       </c>
       <c r="M57" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N57" s="32" t="s">
         <v>1</v>
@@ -11569,10 +11709,10 @@
         <v>378</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D58" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E58" s="58" t="s">
         <v>631</v>
@@ -11599,7 +11739,7 @@
         <v>683</v>
       </c>
       <c r="M58" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N58" s="32" t="s">
         <v>1</v>
@@ -11646,10 +11786,10 @@
         <v>379</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D59" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E59" s="58" t="s">
         <v>631</v>
@@ -11676,7 +11816,7 @@
         <v>683</v>
       </c>
       <c r="M59" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N59" s="32" t="s">
         <v>1</v>
@@ -11723,10 +11863,10 @@
         <v>380</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D60" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E60" s="58" t="s">
         <v>631</v>
@@ -11753,7 +11893,7 @@
         <v>683</v>
       </c>
       <c r="M60" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N60" s="32" t="s">
         <v>1</v>
@@ -11800,10 +11940,10 @@
         <v>381</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D61" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E61" s="58" t="s">
         <v>631</v>
@@ -11830,7 +11970,7 @@
         <v>683</v>
       </c>
       <c r="M61" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N61" s="32" t="s">
         <v>1</v>
@@ -11877,10 +12017,10 @@
         <v>382</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D62" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E62" s="58" t="s">
         <v>631</v>
@@ -11907,7 +12047,7 @@
         <v>683</v>
       </c>
       <c r="M62" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N62" s="32" t="s">
         <v>1</v>
@@ -11954,10 +12094,10 @@
         <v>383</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D63" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E63" s="58" t="s">
         <v>631</v>
@@ -11984,7 +12124,7 @@
         <v>683</v>
       </c>
       <c r="M63" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N63" s="32" t="s">
         <v>1</v>
@@ -12031,10 +12171,10 @@
         <v>384</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D64" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E64" s="58" t="s">
         <v>631</v>
@@ -12061,7 +12201,7 @@
         <v>683</v>
       </c>
       <c r="M64" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N64" s="32" t="s">
         <v>1</v>
@@ -12108,10 +12248,10 @@
         <v>385</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D65" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E65" s="58" t="s">
         <v>631</v>
@@ -12138,7 +12278,7 @@
         <v>683</v>
       </c>
       <c r="M65" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N65" s="32" t="s">
         <v>1</v>
@@ -12185,10 +12325,10 @@
         <v>386</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D66" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E66" s="58" t="s">
         <v>631</v>
@@ -12215,7 +12355,7 @@
         <v>683</v>
       </c>
       <c r="M66" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N66" s="32" t="s">
         <v>1</v>
@@ -12262,10 +12402,10 @@
         <v>387</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D67" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E67" s="58" t="s">
         <v>631</v>
@@ -12292,7 +12432,7 @@
         <v>683</v>
       </c>
       <c r="M67" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N67" s="32" t="s">
         <v>1</v>
@@ -12339,10 +12479,10 @@
         <v>388</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D68" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E68" s="58" t="s">
         <v>631</v>
@@ -12369,7 +12509,7 @@
         <v>683</v>
       </c>
       <c r="M68" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N68" s="32" t="s">
         <v>1</v>
@@ -12416,10 +12556,10 @@
         <v>389</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D69" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E69" s="58" t="s">
         <v>631</v>
@@ -12446,7 +12586,7 @@
         <v>683</v>
       </c>
       <c r="M69" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N69" s="32" t="s">
         <v>1</v>
@@ -12493,10 +12633,10 @@
         <v>390</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D70" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E70" s="58" t="s">
         <v>631</v>
@@ -12523,7 +12663,7 @@
         <v>683</v>
       </c>
       <c r="M70" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N70" s="32" t="s">
         <v>1</v>
@@ -12570,10 +12710,10 @@
         <v>391</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D71" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E71" s="58" t="s">
         <v>631</v>
@@ -12600,7 +12740,7 @@
         <v>683</v>
       </c>
       <c r="M71" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N71" s="32" t="s">
         <v>1</v>
@@ -12647,10 +12787,10 @@
         <v>392</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D72" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E72" s="58" t="s">
         <v>631</v>
@@ -12677,7 +12817,7 @@
         <v>683</v>
       </c>
       <c r="M72" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N72" s="32" t="s">
         <v>1</v>
@@ -12724,10 +12864,10 @@
         <v>393</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D73" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E73" s="58" t="s">
         <v>631</v>
@@ -12754,7 +12894,7 @@
         <v>683</v>
       </c>
       <c r="M73" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N73" s="32" t="s">
         <v>1</v>
@@ -12801,10 +12941,10 @@
         <v>394</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D74" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E74" s="58" t="s">
         <v>631</v>
@@ -12831,7 +12971,7 @@
         <v>683</v>
       </c>
       <c r="M74" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N74" s="32" t="s">
         <v>1</v>
@@ -12878,10 +13018,10 @@
         <v>395</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>833</v>
+        <v>825</v>
       </c>
       <c r="D75" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E75" s="58" t="s">
         <v>631</v>
@@ -12908,7 +13048,7 @@
         <v>683</v>
       </c>
       <c r="M75" s="35" t="s">
-        <v>779</v>
+        <v>772</v>
       </c>
       <c r="N75" s="32" t="s">
         <v>1</v>
@@ -12955,10 +13095,10 @@
         <v>396</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D76" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E76" s="58" t="s">
         <v>631</v>
@@ -12985,7 +13125,7 @@
         <v>683</v>
       </c>
       <c r="M76" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N76" s="32" t="s">
         <v>1</v>
@@ -13032,10 +13172,10 @@
         <v>397</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D77" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E77" s="58" t="s">
         <v>631</v>
@@ -13062,7 +13202,7 @@
         <v>683</v>
       </c>
       <c r="M77" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N77" s="32" t="s">
         <v>1</v>
@@ -13109,10 +13249,10 @@
         <v>398</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D78" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E78" s="58" t="s">
         <v>631</v>
@@ -13139,7 +13279,7 @@
         <v>683</v>
       </c>
       <c r="M78" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N78" s="32" t="s">
         <v>1</v>
@@ -13186,10 +13326,10 @@
         <v>399</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D79" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E79" s="58" t="s">
         <v>631</v>
@@ -13216,7 +13356,7 @@
         <v>683</v>
       </c>
       <c r="M79" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N79" s="32" t="s">
         <v>1</v>
@@ -13263,10 +13403,10 @@
         <v>400</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D80" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E80" s="58" t="s">
         <v>631</v>
@@ -13293,7 +13433,7 @@
         <v>683</v>
       </c>
       <c r="M80" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N80" s="32" t="s">
         <v>1</v>
@@ -13340,10 +13480,10 @@
         <v>401</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D81" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E81" s="58" t="s">
         <v>631</v>
@@ -13370,7 +13510,7 @@
         <v>683</v>
       </c>
       <c r="M81" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N81" s="32" t="s">
         <v>1</v>
@@ -13417,10 +13557,10 @@
         <v>402</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D82" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E82" s="58" t="s">
         <v>631</v>
@@ -13447,7 +13587,7 @@
         <v>683</v>
       </c>
       <c r="M82" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N82" s="32" t="s">
         <v>1</v>
@@ -13494,10 +13634,10 @@
         <v>403</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D83" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E83" s="58" t="s">
         <v>631</v>
@@ -13524,7 +13664,7 @@
         <v>683</v>
       </c>
       <c r="M83" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N83" s="32" t="s">
         <v>1</v>
@@ -13571,10 +13711,10 @@
         <v>404</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D84" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E84" s="58" t="s">
         <v>631</v>
@@ -13601,7 +13741,7 @@
         <v>683</v>
       </c>
       <c r="M84" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N84" s="32" t="s">
         <v>1</v>
@@ -13648,10 +13788,10 @@
         <v>405</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D85" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E85" s="58" t="s">
         <v>631</v>
@@ -13678,7 +13818,7 @@
         <v>683</v>
       </c>
       <c r="M85" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N85" s="32" t="s">
         <v>1</v>
@@ -13725,10 +13865,10 @@
         <v>406</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D86" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E86" s="58" t="s">
         <v>631</v>
@@ -13755,7 +13895,7 @@
         <v>683</v>
       </c>
       <c r="M86" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N86" s="32" t="s">
         <v>1</v>
@@ -13802,10 +13942,10 @@
         <v>407</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D87" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E87" s="58" t="s">
         <v>631</v>
@@ -13832,7 +13972,7 @@
         <v>683</v>
       </c>
       <c r="M87" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N87" s="32" t="s">
         <v>1</v>
@@ -13879,10 +14019,10 @@
         <v>408</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D88" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E88" s="58" t="s">
         <v>631</v>
@@ -13909,7 +14049,7 @@
         <v>683</v>
       </c>
       <c r="M88" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N88" s="32" t="s">
         <v>1</v>
@@ -13956,10 +14096,10 @@
         <v>409</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D89" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E89" s="58" t="s">
         <v>631</v>
@@ -13986,7 +14126,7 @@
         <v>683</v>
       </c>
       <c r="M89" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N89" s="32" t="s">
         <v>1</v>
@@ -14033,10 +14173,10 @@
         <v>410</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D90" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E90" s="58" t="s">
         <v>631</v>
@@ -14063,7 +14203,7 @@
         <v>683</v>
       </c>
       <c r="M90" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N90" s="32" t="s">
         <v>1</v>
@@ -14110,10 +14250,10 @@
         <v>411</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D91" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E91" s="58" t="s">
         <v>631</v>
@@ -14140,7 +14280,7 @@
         <v>683</v>
       </c>
       <c r="M91" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N91" s="32" t="s">
         <v>1</v>
@@ -14187,10 +14327,10 @@
         <v>412</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D92" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E92" s="58" t="s">
         <v>631</v>
@@ -14217,7 +14357,7 @@
         <v>683</v>
       </c>
       <c r="M92" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N92" s="32" t="s">
         <v>1</v>
@@ -14264,10 +14404,10 @@
         <v>413</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D93" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E93" s="58" t="s">
         <v>631</v>
@@ -14294,7 +14434,7 @@
         <v>683</v>
       </c>
       <c r="M93" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N93" s="32" t="s">
         <v>1</v>
@@ -14341,10 +14481,10 @@
         <v>414</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D94" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E94" s="58" t="s">
         <v>631</v>
@@ -14371,7 +14511,7 @@
         <v>683</v>
       </c>
       <c r="M94" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N94" s="32" t="s">
         <v>1</v>
@@ -14418,10 +14558,10 @@
         <v>415</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D95" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E95" s="58" t="s">
         <v>631</v>
@@ -14448,7 +14588,7 @@
         <v>683</v>
       </c>
       <c r="M95" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N95" s="32" t="s">
         <v>1</v>
@@ -14495,10 +14635,10 @@
         <v>416</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D96" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E96" s="58" t="s">
         <v>631</v>
@@ -14525,7 +14665,7 @@
         <v>683</v>
       </c>
       <c r="M96" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N96" s="32" t="s">
         <v>1</v>
@@ -14572,10 +14712,10 @@
         <v>417</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D97" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E97" s="58" t="s">
         <v>631</v>
@@ -14602,7 +14742,7 @@
         <v>683</v>
       </c>
       <c r="M97" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N97" s="32" t="s">
         <v>1</v>
@@ -14649,10 +14789,10 @@
         <v>418</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D98" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E98" s="58" t="s">
         <v>631</v>
@@ -14679,7 +14819,7 @@
         <v>683</v>
       </c>
       <c r="M98" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N98" s="32" t="s">
         <v>1</v>
@@ -14726,10 +14866,10 @@
         <v>419</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D99" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E99" s="58" t="s">
         <v>631</v>
@@ -14756,7 +14896,7 @@
         <v>683</v>
       </c>
       <c r="M99" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N99" s="32" t="s">
         <v>1</v>
@@ -14803,10 +14943,10 @@
         <v>420</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D100" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E100" s="58" t="s">
         <v>631</v>
@@ -14833,7 +14973,7 @@
         <v>683</v>
       </c>
       <c r="M100" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N100" s="32" t="s">
         <v>1</v>
@@ -14880,10 +15020,10 @@
         <v>421</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D101" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E101" s="58" t="s">
         <v>631</v>
@@ -14910,7 +15050,7 @@
         <v>683</v>
       </c>
       <c r="M101" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N101" s="32" t="s">
         <v>1</v>
@@ -14957,10 +15097,10 @@
         <v>422</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>834</v>
+        <v>826</v>
       </c>
       <c r="D102" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E102" s="58" t="s">
         <v>631</v>
@@ -14987,7 +15127,7 @@
         <v>683</v>
       </c>
       <c r="M102" s="35" t="s">
-        <v>780</v>
+        <v>773</v>
       </c>
       <c r="N102" s="32" t="s">
         <v>1</v>
@@ -15034,10 +15174,10 @@
         <v>423</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D103" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E103" s="58" t="s">
         <v>631</v>
@@ -15064,7 +15204,7 @@
         <v>683</v>
       </c>
       <c r="M103" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N103" s="32" t="s">
         <v>1</v>
@@ -15111,10 +15251,10 @@
         <v>424</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D104" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E104" s="58" t="s">
         <v>631</v>
@@ -15141,7 +15281,7 @@
         <v>683</v>
       </c>
       <c r="M104" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N104" s="32" t="s">
         <v>1</v>
@@ -15188,10 +15328,10 @@
         <v>425</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D105" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E105" s="58" t="s">
         <v>631</v>
@@ -15218,7 +15358,7 @@
         <v>683</v>
       </c>
       <c r="M105" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N105" s="32" t="s">
         <v>1</v>
@@ -15265,10 +15405,10 @@
         <v>426</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D106" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E106" s="58" t="s">
         <v>631</v>
@@ -15295,7 +15435,7 @@
         <v>683</v>
       </c>
       <c r="M106" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N106" s="32" t="s">
         <v>1</v>
@@ -15342,10 +15482,10 @@
         <v>427</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D107" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E107" s="58" t="s">
         <v>631</v>
@@ -15372,7 +15512,7 @@
         <v>683</v>
       </c>
       <c r="M107" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N107" s="32" t="s">
         <v>1</v>
@@ -15419,10 +15559,10 @@
         <v>428</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D108" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E108" s="58" t="s">
         <v>631</v>
@@ -15449,7 +15589,7 @@
         <v>683</v>
       </c>
       <c r="M108" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N108" s="32" t="s">
         <v>1</v>
@@ -15496,10 +15636,10 @@
         <v>429</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D109" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E109" s="58" t="s">
         <v>631</v>
@@ -15526,7 +15666,7 @@
         <v>683</v>
       </c>
       <c r="M109" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N109" s="32" t="s">
         <v>1</v>
@@ -15573,10 +15713,10 @@
         <v>430</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D110" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E110" s="58" t="s">
         <v>631</v>
@@ -15603,7 +15743,7 @@
         <v>683</v>
       </c>
       <c r="M110" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N110" s="32" t="s">
         <v>1</v>
@@ -15650,10 +15790,10 @@
         <v>431</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D111" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E111" s="58" t="s">
         <v>631</v>
@@ -15680,7 +15820,7 @@
         <v>683</v>
       </c>
       <c r="M111" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N111" s="32" t="s">
         <v>1</v>
@@ -15727,10 +15867,10 @@
         <v>432</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D112" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E112" s="58" t="s">
         <v>631</v>
@@ -15757,7 +15897,7 @@
         <v>683</v>
       </c>
       <c r="M112" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N112" s="32" t="s">
         <v>1</v>
@@ -15804,10 +15944,10 @@
         <v>433</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D113" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E113" s="58" t="s">
         <v>631</v>
@@ -15834,7 +15974,7 @@
         <v>683</v>
       </c>
       <c r="M113" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N113" s="32" t="s">
         <v>1</v>
@@ -15881,10 +16021,10 @@
         <v>434</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D114" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E114" s="58" t="s">
         <v>631</v>
@@ -15911,7 +16051,7 @@
         <v>683</v>
       </c>
       <c r="M114" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N114" s="32" t="s">
         <v>1</v>
@@ -15958,10 +16098,10 @@
         <v>435</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D115" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E115" s="58" t="s">
         <v>631</v>
@@ -15988,7 +16128,7 @@
         <v>683</v>
       </c>
       <c r="M115" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N115" s="32" t="s">
         <v>1</v>
@@ -16035,10 +16175,10 @@
         <v>436</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D116" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E116" s="58" t="s">
         <v>631</v>
@@ -16065,7 +16205,7 @@
         <v>683</v>
       </c>
       <c r="M116" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N116" s="32" t="s">
         <v>1</v>
@@ -16112,10 +16252,10 @@
         <v>437</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D117" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E117" s="58" t="s">
         <v>631</v>
@@ -16142,7 +16282,7 @@
         <v>683</v>
       </c>
       <c r="M117" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N117" s="32" t="s">
         <v>1</v>
@@ -16189,10 +16329,10 @@
         <v>438</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D118" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E118" s="58" t="s">
         <v>631</v>
@@ -16219,7 +16359,7 @@
         <v>683</v>
       </c>
       <c r="M118" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N118" s="32" t="s">
         <v>1</v>
@@ -16266,10 +16406,10 @@
         <v>439</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D119" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E119" s="58" t="s">
         <v>631</v>
@@ -16296,7 +16436,7 @@
         <v>683</v>
       </c>
       <c r="M119" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N119" s="32" t="s">
         <v>1</v>
@@ -16343,10 +16483,10 @@
         <v>440</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D120" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E120" s="58" t="s">
         <v>631</v>
@@ -16373,7 +16513,7 @@
         <v>683</v>
       </c>
       <c r="M120" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N120" s="32" t="s">
         <v>1</v>
@@ -16420,10 +16560,10 @@
         <v>702</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>835</v>
+        <v>827</v>
       </c>
       <c r="D121" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E121" s="58" t="s">
         <v>631</v>
@@ -16450,7 +16590,7 @@
         <v>683</v>
       </c>
       <c r="M121" s="35" t="s">
-        <v>781</v>
+        <v>774</v>
       </c>
       <c r="N121" s="32" t="s">
         <v>1</v>
@@ -16497,10 +16637,10 @@
         <v>441</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D122" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E122" s="58" t="s">
         <v>631</v>
@@ -16574,10 +16714,10 @@
         <v>442</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D123" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E123" s="58" t="s">
         <v>631</v>
@@ -16651,10 +16791,10 @@
         <v>443</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D124" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E124" s="58" t="s">
         <v>631</v>
@@ -16728,10 +16868,10 @@
         <v>444</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D125" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E125" s="58" t="s">
         <v>631</v>
@@ -16805,10 +16945,10 @@
         <v>445</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D126" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E126" s="58" t="s">
         <v>631</v>
@@ -16882,10 +17022,10 @@
         <v>446</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D127" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E127" s="58" t="s">
         <v>631</v>
@@ -16959,10 +17099,10 @@
         <v>447</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D128" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E128" s="58" t="s">
         <v>631</v>
@@ -17036,10 +17176,10 @@
         <v>448</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D129" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E129" s="58" t="s">
         <v>631</v>
@@ -17113,10 +17253,10 @@
         <v>449</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D130" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E130" s="58" t="s">
         <v>631</v>
@@ -17190,10 +17330,10 @@
         <v>450</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D131" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E131" s="58" t="s">
         <v>631</v>
@@ -17267,10 +17407,10 @@
         <v>451</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>836</v>
+        <v>828</v>
       </c>
       <c r="D132" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E132" s="58" t="s">
         <v>631</v>
@@ -17344,10 +17484,10 @@
         <v>452</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D133" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E133" s="58" t="s">
         <v>631</v>
@@ -17421,10 +17561,10 @@
         <v>453</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D134" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E134" s="58" t="s">
         <v>631</v>
@@ -17451,7 +17591,7 @@
         <v>683</v>
       </c>
       <c r="M134" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N134" s="32" t="s">
         <v>1</v>
@@ -17498,10 +17638,10 @@
         <v>454</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D135" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E135" s="58" t="s">
         <v>631</v>
@@ -17528,7 +17668,7 @@
         <v>683</v>
       </c>
       <c r="M135" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N135" s="32" t="s">
         <v>1</v>
@@ -17575,10 +17715,10 @@
         <v>455</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D136" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E136" s="58" t="s">
         <v>631</v>
@@ -17605,7 +17745,7 @@
         <v>683</v>
       </c>
       <c r="M136" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N136" s="32" t="s">
         <v>1</v>
@@ -17652,10 +17792,10 @@
         <v>456</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D137" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E137" s="58" t="s">
         <v>631</v>
@@ -17682,7 +17822,7 @@
         <v>683</v>
       </c>
       <c r="M137" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N137" s="32" t="s">
         <v>1</v>
@@ -17729,10 +17869,10 @@
         <v>457</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D138" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E138" s="58" t="s">
         <v>631</v>
@@ -17759,7 +17899,7 @@
         <v>683</v>
       </c>
       <c r="M138" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N138" s="32" t="s">
         <v>1</v>
@@ -17806,10 +17946,10 @@
         <v>458</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D139" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E139" s="58" t="s">
         <v>631</v>
@@ -17836,7 +17976,7 @@
         <v>683</v>
       </c>
       <c r="M139" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N139" s="32" t="s">
         <v>1</v>
@@ -17883,10 +18023,10 @@
         <v>459</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D140" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E140" s="58" t="s">
         <v>631</v>
@@ -17913,7 +18053,7 @@
         <v>683</v>
       </c>
       <c r="M140" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N140" s="32" t="s">
         <v>1</v>
@@ -17960,10 +18100,10 @@
         <v>460</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D141" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E141" s="58" t="s">
         <v>631</v>
@@ -17990,7 +18130,7 @@
         <v>683</v>
       </c>
       <c r="M141" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N141" s="32" t="s">
         <v>1</v>
@@ -18037,10 +18177,10 @@
         <v>461</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D142" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E142" s="58" t="s">
         <v>631</v>
@@ -18067,7 +18207,7 @@
         <v>683</v>
       </c>
       <c r="M142" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N142" s="32" t="s">
         <v>1</v>
@@ -18114,10 +18254,10 @@
         <v>462</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D143" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E143" s="58" t="s">
         <v>631</v>
@@ -18144,7 +18284,7 @@
         <v>683</v>
       </c>
       <c r="M143" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N143" s="32" t="s">
         <v>1</v>
@@ -18191,10 +18331,10 @@
         <v>463</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D144" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E144" s="58" t="s">
         <v>631</v>
@@ -18221,7 +18361,7 @@
         <v>683</v>
       </c>
       <c r="M144" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N144" s="32" t="s">
         <v>1</v>
@@ -18268,10 +18408,10 @@
         <v>464</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>837</v>
+        <v>829</v>
       </c>
       <c r="D145" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E145" s="58" t="s">
         <v>631</v>
@@ -18298,7 +18438,7 @@
         <v>683</v>
       </c>
       <c r="M145" s="35" t="s">
-        <v>782</v>
+        <v>775</v>
       </c>
       <c r="N145" s="32" t="s">
         <v>1</v>
@@ -18345,10 +18485,10 @@
         <v>465</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D146" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E146" s="58" t="s">
         <v>631</v>
@@ -18375,7 +18515,7 @@
         <v>683</v>
       </c>
       <c r="M146" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N146" s="32" t="s">
         <v>1</v>
@@ -18422,10 +18562,10 @@
         <v>466</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D147" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E147" s="58" t="s">
         <v>631</v>
@@ -18452,7 +18592,7 @@
         <v>683</v>
       </c>
       <c r="M147" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N147" s="32" t="s">
         <v>1</v>
@@ -18499,10 +18639,10 @@
         <v>467</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D148" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E148" s="58" t="s">
         <v>631</v>
@@ -18529,7 +18669,7 @@
         <v>683</v>
       </c>
       <c r="M148" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N148" s="32" t="s">
         <v>1</v>
@@ -18576,10 +18716,10 @@
         <v>468</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D149" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E149" s="58" t="s">
         <v>631</v>
@@ -18606,7 +18746,7 @@
         <v>683</v>
       </c>
       <c r="M149" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N149" s="32" t="s">
         <v>1</v>
@@ -18653,10 +18793,10 @@
         <v>469</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D150" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E150" s="58" t="s">
         <v>631</v>
@@ -18683,7 +18823,7 @@
         <v>683</v>
       </c>
       <c r="M150" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N150" s="32" t="s">
         <v>1</v>
@@ -18730,10 +18870,10 @@
         <v>470</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D151" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E151" s="58" t="s">
         <v>631</v>
@@ -18760,7 +18900,7 @@
         <v>683</v>
       </c>
       <c r="M151" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N151" s="32" t="s">
         <v>1</v>
@@ -18807,10 +18947,10 @@
         <v>471</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D152" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E152" s="58" t="s">
         <v>631</v>
@@ -18837,7 +18977,7 @@
         <v>683</v>
       </c>
       <c r="M152" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N152" s="32" t="s">
         <v>1</v>
@@ -18884,10 +19024,10 @@
         <v>472</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D153" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E153" s="58" t="s">
         <v>631</v>
@@ -18914,7 +19054,7 @@
         <v>683</v>
       </c>
       <c r="M153" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N153" s="32" t="s">
         <v>1</v>
@@ -18961,10 +19101,10 @@
         <v>473</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D154" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E154" s="58" t="s">
         <v>631</v>
@@ -18991,7 +19131,7 @@
         <v>683</v>
       </c>
       <c r="M154" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N154" s="32" t="s">
         <v>1</v>
@@ -19038,10 +19178,10 @@
         <v>474</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D155" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E155" s="58" t="s">
         <v>631</v>
@@ -19068,7 +19208,7 @@
         <v>683</v>
       </c>
       <c r="M155" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N155" s="32" t="s">
         <v>1</v>
@@ -19115,10 +19255,10 @@
         <v>475</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D156" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E156" s="58" t="s">
         <v>631</v>
@@ -19145,7 +19285,7 @@
         <v>683</v>
       </c>
       <c r="M156" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N156" s="32" t="s">
         <v>1</v>
@@ -19192,10 +19332,10 @@
         <v>476</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D157" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E157" s="58" t="s">
         <v>631</v>
@@ -19222,7 +19362,7 @@
         <v>683</v>
       </c>
       <c r="M157" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N157" s="32" t="s">
         <v>1</v>
@@ -19269,10 +19409,10 @@
         <v>477</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D158" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E158" s="58" t="s">
         <v>631</v>
@@ -19299,7 +19439,7 @@
         <v>683</v>
       </c>
       <c r="M158" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N158" s="32" t="s">
         <v>1</v>
@@ -19346,10 +19486,10 @@
         <v>478</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D159" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E159" s="58" t="s">
         <v>631</v>
@@ -19376,7 +19516,7 @@
         <v>683</v>
       </c>
       <c r="M159" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N159" s="32" t="s">
         <v>1</v>
@@ -19423,10 +19563,10 @@
         <v>479</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D160" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E160" s="58" t="s">
         <v>631</v>
@@ -19453,7 +19593,7 @@
         <v>683</v>
       </c>
       <c r="M160" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N160" s="32" t="s">
         <v>1</v>
@@ -19500,10 +19640,10 @@
         <v>480</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D161" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E161" s="58" t="s">
         <v>631</v>
@@ -19530,7 +19670,7 @@
         <v>683</v>
       </c>
       <c r="M161" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N161" s="32" t="s">
         <v>1</v>
@@ -19577,10 +19717,10 @@
         <v>481</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D162" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E162" s="58" t="s">
         <v>631</v>
@@ -19607,7 +19747,7 @@
         <v>683</v>
       </c>
       <c r="M162" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N162" s="32" t="s">
         <v>1</v>
@@ -19654,10 +19794,10 @@
         <v>482</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D163" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E163" s="58" t="s">
         <v>631</v>
@@ -19684,7 +19824,7 @@
         <v>683</v>
       </c>
       <c r="M163" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N163" s="32" t="s">
         <v>1</v>
@@ -19731,10 +19871,10 @@
         <v>483</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D164" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E164" s="58" t="s">
         <v>631</v>
@@ -19761,7 +19901,7 @@
         <v>683</v>
       </c>
       <c r="M164" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N164" s="32" t="s">
         <v>1</v>
@@ -19808,10 +19948,10 @@
         <v>484</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D165" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E165" s="58" t="s">
         <v>631</v>
@@ -19838,7 +19978,7 @@
         <v>683</v>
       </c>
       <c r="M165" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N165" s="32" t="s">
         <v>1</v>
@@ -19885,10 +20025,10 @@
         <v>485</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D166" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E166" s="58" t="s">
         <v>631</v>
@@ -19915,7 +20055,7 @@
         <v>683</v>
       </c>
       <c r="M166" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N166" s="32" t="s">
         <v>1</v>
@@ -19962,10 +20102,10 @@
         <v>486</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D167" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E167" s="58" t="s">
         <v>631</v>
@@ -19992,7 +20132,7 @@
         <v>683</v>
       </c>
       <c r="M167" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N167" s="32" t="s">
         <v>1</v>
@@ -20039,10 +20179,10 @@
         <v>487</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D168" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E168" s="58" t="s">
         <v>631</v>
@@ -20069,7 +20209,7 @@
         <v>683</v>
       </c>
       <c r="M168" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N168" s="32" t="s">
         <v>1</v>
@@ -20116,10 +20256,10 @@
         <v>488</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D169" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E169" s="58" t="s">
         <v>631</v>
@@ -20146,7 +20286,7 @@
         <v>683</v>
       </c>
       <c r="M169" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N169" s="32" t="s">
         <v>1</v>
@@ -20193,10 +20333,10 @@
         <v>489</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D170" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E170" s="58" t="s">
         <v>631</v>
@@ -20223,7 +20363,7 @@
         <v>683</v>
       </c>
       <c r="M170" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N170" s="32" t="s">
         <v>1</v>
@@ -20270,10 +20410,10 @@
         <v>490</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D171" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E171" s="58" t="s">
         <v>631</v>
@@ -20300,7 +20440,7 @@
         <v>683</v>
       </c>
       <c r="M171" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N171" s="32" t="s">
         <v>1</v>
@@ -20347,10 +20487,10 @@
         <v>491</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D172" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E172" s="58" t="s">
         <v>631</v>
@@ -20377,7 +20517,7 @@
         <v>683</v>
       </c>
       <c r="M172" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N172" s="32" t="s">
         <v>1</v>
@@ -20424,10 +20564,10 @@
         <v>492</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D173" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E173" s="58" t="s">
         <v>631</v>
@@ -20454,7 +20594,7 @@
         <v>683</v>
       </c>
       <c r="M173" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N173" s="32" t="s">
         <v>1</v>
@@ -20501,10 +20641,10 @@
         <v>493</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D174" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E174" s="58" t="s">
         <v>631</v>
@@ -20531,7 +20671,7 @@
         <v>683</v>
       </c>
       <c r="M174" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N174" s="32" t="s">
         <v>1</v>
@@ -20578,10 +20718,10 @@
         <v>494</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D175" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E175" s="58" t="s">
         <v>631</v>
@@ -20608,7 +20748,7 @@
         <v>683</v>
       </c>
       <c r="M175" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N175" s="32" t="s">
         <v>1</v>
@@ -20655,10 +20795,10 @@
         <v>495</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D176" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E176" s="58" t="s">
         <v>631</v>
@@ -20685,7 +20825,7 @@
         <v>683</v>
       </c>
       <c r="M176" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N176" s="32" t="s">
         <v>1</v>
@@ -20732,10 +20872,10 @@
         <v>496</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D177" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E177" s="58" t="s">
         <v>631</v>
@@ -20762,7 +20902,7 @@
         <v>683</v>
       </c>
       <c r="M177" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N177" s="32" t="s">
         <v>1</v>
@@ -20809,10 +20949,10 @@
         <v>497</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>838</v>
+        <v>830</v>
       </c>
       <c r="D178" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E178" s="58" t="s">
         <v>631</v>
@@ -20839,7 +20979,7 @@
         <v>683</v>
       </c>
       <c r="M178" s="35" t="s">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="N178" s="32" t="s">
         <v>1</v>
@@ -20886,10 +21026,10 @@
         <v>498</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D179" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E179" s="58" t="s">
         <v>631</v>
@@ -20916,7 +21056,7 @@
         <v>683</v>
       </c>
       <c r="M179" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N179" s="32" t="s">
         <v>1</v>
@@ -20963,10 +21103,10 @@
         <v>499</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D180" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E180" s="58" t="s">
         <v>631</v>
@@ -20993,7 +21133,7 @@
         <v>683</v>
       </c>
       <c r="M180" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N180" s="32" t="s">
         <v>1</v>
@@ -21040,10 +21180,10 @@
         <v>500</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D181" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E181" s="58" t="s">
         <v>631</v>
@@ -21070,7 +21210,7 @@
         <v>683</v>
       </c>
       <c r="M181" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N181" s="32" t="s">
         <v>1</v>
@@ -21117,10 +21257,10 @@
         <v>501</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D182" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E182" s="58" t="s">
         <v>631</v>
@@ -21147,7 +21287,7 @@
         <v>683</v>
       </c>
       <c r="M182" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N182" s="32" t="s">
         <v>1</v>
@@ -21194,10 +21334,10 @@
         <v>502</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D183" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E183" s="58" t="s">
         <v>631</v>
@@ -21224,7 +21364,7 @@
         <v>683</v>
       </c>
       <c r="M183" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N183" s="32" t="s">
         <v>1</v>
@@ -21271,10 +21411,10 @@
         <v>503</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D184" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E184" s="58" t="s">
         <v>631</v>
@@ -21301,7 +21441,7 @@
         <v>683</v>
       </c>
       <c r="M184" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N184" s="32" t="s">
         <v>1</v>
@@ -21348,10 +21488,10 @@
         <v>504</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D185" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E185" s="58" t="s">
         <v>631</v>
@@ -21378,7 +21518,7 @@
         <v>683</v>
       </c>
       <c r="M185" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N185" s="32" t="s">
         <v>1</v>
@@ -21425,10 +21565,10 @@
         <v>505</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D186" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E186" s="58" t="s">
         <v>631</v>
@@ -21455,7 +21595,7 @@
         <v>683</v>
       </c>
       <c r="M186" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N186" s="32" t="s">
         <v>1</v>
@@ -21502,10 +21642,10 @@
         <v>506</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D187" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E187" s="58" t="s">
         <v>631</v>
@@ -21532,7 +21672,7 @@
         <v>683</v>
       </c>
       <c r="M187" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N187" s="32" t="s">
         <v>1</v>
@@ -21579,10 +21719,10 @@
         <v>507</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D188" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E188" s="58" t="s">
         <v>631</v>
@@ -21609,7 +21749,7 @@
         <v>683</v>
       </c>
       <c r="M188" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N188" s="32" t="s">
         <v>1</v>
@@ -21656,10 +21796,10 @@
         <v>508</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D189" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E189" s="58" t="s">
         <v>631</v>
@@ -21686,7 +21826,7 @@
         <v>683</v>
       </c>
       <c r="M189" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N189" s="32" t="s">
         <v>1</v>
@@ -21733,10 +21873,10 @@
         <v>509</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D190" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E190" s="58" t="s">
         <v>631</v>
@@ -21763,7 +21903,7 @@
         <v>683</v>
       </c>
       <c r="M190" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N190" s="32" t="s">
         <v>1</v>
@@ -21810,10 +21950,10 @@
         <v>510</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D191" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E191" s="58" t="s">
         <v>631</v>
@@ -21840,7 +21980,7 @@
         <v>683</v>
       </c>
       <c r="M191" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N191" s="32" t="s">
         <v>1</v>
@@ -21887,10 +22027,10 @@
         <v>511</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D192" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E192" s="58" t="s">
         <v>631</v>
@@ -21917,7 +22057,7 @@
         <v>683</v>
       </c>
       <c r="M192" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N192" s="32" t="s">
         <v>1</v>
@@ -21964,10 +22104,10 @@
         <v>512</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D193" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E193" s="58" t="s">
         <v>631</v>
@@ -21994,7 +22134,7 @@
         <v>683</v>
       </c>
       <c r="M193" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N193" s="32" t="s">
         <v>1</v>
@@ -22041,10 +22181,10 @@
         <v>513</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D194" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E194" s="58" t="s">
         <v>631</v>
@@ -22071,7 +22211,7 @@
         <v>683</v>
       </c>
       <c r="M194" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N194" s="32" t="s">
         <v>1</v>
@@ -22118,10 +22258,10 @@
         <v>514</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D195" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E195" s="58" t="s">
         <v>631</v>
@@ -22148,7 +22288,7 @@
         <v>683</v>
       </c>
       <c r="M195" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N195" s="32" t="s">
         <v>1</v>
@@ -22195,10 +22335,10 @@
         <v>515</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D196" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E196" s="58" t="s">
         <v>631</v>
@@ -22225,7 +22365,7 @@
         <v>683</v>
       </c>
       <c r="M196" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N196" s="32" t="s">
         <v>1</v>
@@ -22272,10 +22412,10 @@
         <v>516</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D197" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E197" s="58" t="s">
         <v>631</v>
@@ -22302,7 +22442,7 @@
         <v>683</v>
       </c>
       <c r="M197" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N197" s="32" t="s">
         <v>1</v>
@@ -22349,10 +22489,10 @@
         <v>517</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D198" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E198" s="58" t="s">
         <v>631</v>
@@ -22379,7 +22519,7 @@
         <v>683</v>
       </c>
       <c r="M198" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N198" s="32" t="s">
         <v>1</v>
@@ -22426,10 +22566,10 @@
         <v>518</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D199" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E199" s="58" t="s">
         <v>631</v>
@@ -22456,7 +22596,7 @@
         <v>683</v>
       </c>
       <c r="M199" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N199" s="32" t="s">
         <v>1</v>
@@ -22503,10 +22643,10 @@
         <v>519</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D200" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E200" s="58" t="s">
         <v>631</v>
@@ -22533,7 +22673,7 @@
         <v>683</v>
       </c>
       <c r="M200" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N200" s="32" t="s">
         <v>1</v>
@@ -22580,10 +22720,10 @@
         <v>520</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D201" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E201" s="58" t="s">
         <v>631</v>
@@ -22610,7 +22750,7 @@
         <v>683</v>
       </c>
       <c r="M201" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N201" s="32" t="s">
         <v>1</v>
@@ -22657,10 +22797,10 @@
         <v>521</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D202" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E202" s="58" t="s">
         <v>631</v>
@@ -22687,7 +22827,7 @@
         <v>683</v>
       </c>
       <c r="M202" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N202" s="32" t="s">
         <v>1</v>
@@ -22734,10 +22874,10 @@
         <v>522</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D203" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E203" s="58" t="s">
         <v>631</v>
@@ -22764,7 +22904,7 @@
         <v>683</v>
       </c>
       <c r="M203" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N203" s="32" t="s">
         <v>1</v>
@@ -22811,10 +22951,10 @@
         <v>523</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D204" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E204" s="58" t="s">
         <v>631</v>
@@ -22841,7 +22981,7 @@
         <v>683</v>
       </c>
       <c r="M204" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N204" s="32" t="s">
         <v>1</v>
@@ -22888,10 +23028,10 @@
         <v>524</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D205" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E205" s="58" t="s">
         <v>631</v>
@@ -22918,7 +23058,7 @@
         <v>683</v>
       </c>
       <c r="M205" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N205" s="32" t="s">
         <v>1</v>
@@ -22965,10 +23105,10 @@
         <v>525</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D206" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E206" s="58" t="s">
         <v>631</v>
@@ -22995,7 +23135,7 @@
         <v>683</v>
       </c>
       <c r="M206" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N206" s="32" t="s">
         <v>1</v>
@@ -23042,10 +23182,10 @@
         <v>526</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D207" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E207" s="58" t="s">
         <v>631</v>
@@ -23072,7 +23212,7 @@
         <v>683</v>
       </c>
       <c r="M207" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N207" s="32" t="s">
         <v>1</v>
@@ -23119,10 +23259,10 @@
         <v>527</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D208" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E208" s="58" t="s">
         <v>631</v>
@@ -23149,7 +23289,7 @@
         <v>683</v>
       </c>
       <c r="M208" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N208" s="32" t="s">
         <v>1</v>
@@ -23196,10 +23336,10 @@
         <v>528</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D209" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E209" s="58" t="s">
         <v>631</v>
@@ -23226,7 +23366,7 @@
         <v>683</v>
       </c>
       <c r="M209" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N209" s="32" t="s">
         <v>1</v>
@@ -23273,10 +23413,10 @@
         <v>529</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D210" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E210" s="58" t="s">
         <v>631</v>
@@ -23303,7 +23443,7 @@
         <v>683</v>
       </c>
       <c r="M210" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N210" s="32" t="s">
         <v>1</v>
@@ -23350,10 +23490,10 @@
         <v>530</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D211" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E211" s="58" t="s">
         <v>631</v>
@@ -23380,7 +23520,7 @@
         <v>683</v>
       </c>
       <c r="M211" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N211" s="32" t="s">
         <v>1</v>
@@ -23427,10 +23567,10 @@
         <v>531</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D212" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E212" s="58" t="s">
         <v>631</v>
@@ -23457,7 +23597,7 @@
         <v>683</v>
       </c>
       <c r="M212" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N212" s="32" t="s">
         <v>1</v>
@@ -23504,10 +23644,10 @@
         <v>532</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D213" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E213" s="58" t="s">
         <v>631</v>
@@ -23534,7 +23674,7 @@
         <v>683</v>
       </c>
       <c r="M213" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N213" s="32" t="s">
         <v>1</v>
@@ -23581,10 +23721,10 @@
         <v>533</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D214" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E214" s="58" t="s">
         <v>631</v>
@@ -23611,7 +23751,7 @@
         <v>683</v>
       </c>
       <c r="M214" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N214" s="32" t="s">
         <v>1</v>
@@ -23658,10 +23798,10 @@
         <v>534</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D215" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E215" s="58" t="s">
         <v>631</v>
@@ -23688,7 +23828,7 @@
         <v>683</v>
       </c>
       <c r="M215" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N215" s="32" t="s">
         <v>1</v>
@@ -23735,10 +23875,10 @@
         <v>535</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D216" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E216" s="58" t="s">
         <v>631</v>
@@ -23765,7 +23905,7 @@
         <v>683</v>
       </c>
       <c r="M216" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N216" s="32" t="s">
         <v>1</v>
@@ -23812,10 +23952,10 @@
         <v>536</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D217" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E217" s="58" t="s">
         <v>631</v>
@@ -23842,7 +23982,7 @@
         <v>683</v>
       </c>
       <c r="M217" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N217" s="32" t="s">
         <v>1</v>
@@ -23889,10 +24029,10 @@
         <v>537</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D218" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E218" s="58" t="s">
         <v>631</v>
@@ -23919,7 +24059,7 @@
         <v>683</v>
       </c>
       <c r="M218" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N218" s="32" t="s">
         <v>1</v>
@@ -23966,10 +24106,10 @@
         <v>538</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D219" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E219" s="58" t="s">
         <v>631</v>
@@ -23996,7 +24136,7 @@
         <v>683</v>
       </c>
       <c r="M219" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N219" s="32" t="s">
         <v>1</v>
@@ -24043,10 +24183,10 @@
         <v>539</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D220" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E220" s="58" t="s">
         <v>631</v>
@@ -24073,7 +24213,7 @@
         <v>683</v>
       </c>
       <c r="M220" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N220" s="32" t="s">
         <v>1</v>
@@ -24120,10 +24260,10 @@
         <v>540</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D221" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E221" s="58" t="s">
         <v>631</v>
@@ -24150,7 +24290,7 @@
         <v>683</v>
       </c>
       <c r="M221" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N221" s="32" t="s">
         <v>1</v>
@@ -24197,10 +24337,10 @@
         <v>541</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D222" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E222" s="58" t="s">
         <v>631</v>
@@ -24227,7 +24367,7 @@
         <v>683</v>
       </c>
       <c r="M222" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N222" s="32" t="s">
         <v>1</v>
@@ -24274,10 +24414,10 @@
         <v>542</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D223" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E223" s="58" t="s">
         <v>631</v>
@@ -24304,7 +24444,7 @@
         <v>683</v>
       </c>
       <c r="M223" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N223" s="32" t="s">
         <v>1</v>
@@ -24351,10 +24491,10 @@
         <v>543</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D224" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E224" s="58" t="s">
         <v>631</v>
@@ -24381,7 +24521,7 @@
         <v>683</v>
       </c>
       <c r="M224" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N224" s="32" t="s">
         <v>1</v>
@@ -24428,10 +24568,10 @@
         <v>544</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D225" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E225" s="58" t="s">
         <v>631</v>
@@ -24458,7 +24598,7 @@
         <v>683</v>
       </c>
       <c r="M225" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N225" s="32" t="s">
         <v>1</v>
@@ -24505,10 +24645,10 @@
         <v>545</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D226" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E226" s="58" t="s">
         <v>631</v>
@@ -24535,7 +24675,7 @@
         <v>683</v>
       </c>
       <c r="M226" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N226" s="32" t="s">
         <v>1</v>
@@ -24582,10 +24722,10 @@
         <v>546</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D227" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E227" s="58" t="s">
         <v>631</v>
@@ -24612,7 +24752,7 @@
         <v>683</v>
       </c>
       <c r="M227" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N227" s="32" t="s">
         <v>1</v>
@@ -24659,10 +24799,10 @@
         <v>547</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D228" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E228" s="58" t="s">
         <v>631</v>
@@ -24689,7 +24829,7 @@
         <v>683</v>
       </c>
       <c r="M228" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N228" s="32" t="s">
         <v>1</v>
@@ -24736,10 +24876,10 @@
         <v>548</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D229" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E229" s="58" t="s">
         <v>631</v>
@@ -24766,7 +24906,7 @@
         <v>683</v>
       </c>
       <c r="M229" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N229" s="32" t="s">
         <v>1</v>
@@ -24813,10 +24953,10 @@
         <v>549</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D230" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E230" s="58" t="s">
         <v>631</v>
@@ -24843,7 +24983,7 @@
         <v>683</v>
       </c>
       <c r="M230" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N230" s="32" t="s">
         <v>1</v>
@@ -24890,10 +25030,10 @@
         <v>550</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D231" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E231" s="58" t="s">
         <v>631</v>
@@ -24920,7 +25060,7 @@
         <v>683</v>
       </c>
       <c r="M231" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N231" s="32" t="s">
         <v>1</v>
@@ -24967,10 +25107,10 @@
         <v>551</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D232" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E232" s="58" t="s">
         <v>631</v>
@@ -24997,7 +25137,7 @@
         <v>683</v>
       </c>
       <c r="M232" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N232" s="32" t="s">
         <v>1</v>
@@ -25044,10 +25184,10 @@
         <v>552</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D233" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E233" s="58" t="s">
         <v>631</v>
@@ -25074,7 +25214,7 @@
         <v>683</v>
       </c>
       <c r="M233" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N233" s="32" t="s">
         <v>1</v>
@@ -25121,10 +25261,10 @@
         <v>553</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D234" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E234" s="58" t="s">
         <v>631</v>
@@ -25151,7 +25291,7 @@
         <v>683</v>
       </c>
       <c r="M234" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N234" s="32" t="s">
         <v>1</v>
@@ -25198,10 +25338,10 @@
         <v>554</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D235" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E235" s="58" t="s">
         <v>631</v>
@@ -25228,7 +25368,7 @@
         <v>683</v>
       </c>
       <c r="M235" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N235" s="32" t="s">
         <v>1</v>
@@ -25275,10 +25415,10 @@
         <v>555</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D236" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E236" s="58" t="s">
         <v>631</v>
@@ -25305,7 +25445,7 @@
         <v>683</v>
       </c>
       <c r="M236" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N236" s="32" t="s">
         <v>1</v>
@@ -25352,10 +25492,10 @@
         <v>556</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D237" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E237" s="58" t="s">
         <v>631</v>
@@ -25382,7 +25522,7 @@
         <v>683</v>
       </c>
       <c r="M237" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N237" s="32" t="s">
         <v>1</v>
@@ -25429,10 +25569,10 @@
         <v>706</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D238" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E238" s="58" t="s">
         <v>631</v>
@@ -25459,7 +25599,7 @@
         <v>683</v>
       </c>
       <c r="M238" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N238" s="32" t="s">
         <v>1</v>
@@ -25506,10 +25646,10 @@
         <v>557</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D239" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E239" s="58" t="s">
         <v>631</v>
@@ -25536,7 +25676,7 @@
         <v>683</v>
       </c>
       <c r="M239" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N239" s="32" t="s">
         <v>1</v>
@@ -25583,10 +25723,10 @@
         <v>558</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D240" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E240" s="58" t="s">
         <v>631</v>
@@ -25613,7 +25753,7 @@
         <v>683</v>
       </c>
       <c r="M240" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N240" s="32" t="s">
         <v>1</v>
@@ -25660,10 +25800,10 @@
         <v>559</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D241" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E241" s="58" t="s">
         <v>631</v>
@@ -25690,7 +25830,7 @@
         <v>683</v>
       </c>
       <c r="M241" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N241" s="32" t="s">
         <v>1</v>
@@ -25737,10 +25877,10 @@
         <v>560</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D242" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E242" s="58" t="s">
         <v>631</v>
@@ -25767,7 +25907,7 @@
         <v>683</v>
       </c>
       <c r="M242" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N242" s="32" t="s">
         <v>1</v>
@@ -25814,10 +25954,10 @@
         <v>561</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D243" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E243" s="58" t="s">
         <v>631</v>
@@ -25844,7 +25984,7 @@
         <v>683</v>
       </c>
       <c r="M243" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N243" s="32" t="s">
         <v>1</v>
@@ -25891,10 +26031,10 @@
         <v>562</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D244" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E244" s="58" t="s">
         <v>631</v>
@@ -25921,7 +26061,7 @@
         <v>683</v>
       </c>
       <c r="M244" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N244" s="32" t="s">
         <v>1</v>
@@ -25968,10 +26108,10 @@
         <v>563</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D245" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E245" s="58" t="s">
         <v>631</v>
@@ -25998,7 +26138,7 @@
         <v>683</v>
       </c>
       <c r="M245" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N245" s="32" t="s">
         <v>1</v>
@@ -26045,10 +26185,10 @@
         <v>564</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>839</v>
+        <v>831</v>
       </c>
       <c r="D246" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E246" s="58" t="s">
         <v>631</v>
@@ -26075,7 +26215,7 @@
         <v>683</v>
       </c>
       <c r="M246" s="35" t="s">
-        <v>784</v>
+        <v>777</v>
       </c>
       <c r="N246" s="32" t="s">
         <v>1</v>
@@ -26122,10 +26262,10 @@
         <v>565</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D247" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E247" s="58" t="s">
         <v>631</v>
@@ -26152,7 +26292,7 @@
         <v>683</v>
       </c>
       <c r="M247" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N247" s="32" t="s">
         <v>1</v>
@@ -26199,10 +26339,10 @@
         <v>566</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D248" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E248" s="58" t="s">
         <v>631</v>
@@ -26229,7 +26369,7 @@
         <v>683</v>
       </c>
       <c r="M248" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N248" s="32" t="s">
         <v>1</v>
@@ -26276,10 +26416,10 @@
         <v>567</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D249" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E249" s="58" t="s">
         <v>631</v>
@@ -26306,7 +26446,7 @@
         <v>683</v>
       </c>
       <c r="M249" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N249" s="32" t="s">
         <v>1</v>
@@ -26353,10 +26493,10 @@
         <v>568</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D250" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E250" s="58" t="s">
         <v>631</v>
@@ -26383,7 +26523,7 @@
         <v>683</v>
       </c>
       <c r="M250" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N250" s="32" t="s">
         <v>1</v>
@@ -26430,10 +26570,10 @@
         <v>569</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D251" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E251" s="58" t="s">
         <v>631</v>
@@ -26460,7 +26600,7 @@
         <v>683</v>
       </c>
       <c r="M251" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N251" s="32" t="s">
         <v>1</v>
@@ -26507,10 +26647,10 @@
         <v>570</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D252" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E252" s="58" t="s">
         <v>631</v>
@@ -26537,7 +26677,7 @@
         <v>683</v>
       </c>
       <c r="M252" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N252" s="32" t="s">
         <v>1</v>
@@ -26584,10 +26724,10 @@
         <v>571</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D253" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E253" s="58" t="s">
         <v>631</v>
@@ -26614,7 +26754,7 @@
         <v>683</v>
       </c>
       <c r="M253" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N253" s="32" t="s">
         <v>1</v>
@@ -26661,10 +26801,10 @@
         <v>572</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D254" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E254" s="58" t="s">
         <v>631</v>
@@ -26691,7 +26831,7 @@
         <v>683</v>
       </c>
       <c r="M254" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N254" s="32" t="s">
         <v>1</v>
@@ -26738,10 +26878,10 @@
         <v>573</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D255" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E255" s="58" t="s">
         <v>631</v>
@@ -26768,7 +26908,7 @@
         <v>683</v>
       </c>
       <c r="M255" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N255" s="32" t="s">
         <v>1</v>
@@ -26815,10 +26955,10 @@
         <v>574</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D256" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E256" s="58" t="s">
         <v>631</v>
@@ -26845,7 +26985,7 @@
         <v>683</v>
       </c>
       <c r="M256" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N256" s="32" t="s">
         <v>1</v>
@@ -26892,10 +27032,10 @@
         <v>575</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D257" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E257" s="58" t="s">
         <v>631</v>
@@ -26922,7 +27062,7 @@
         <v>683</v>
       </c>
       <c r="M257" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N257" s="32" t="s">
         <v>1</v>
@@ -26969,10 +27109,10 @@
         <v>576</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D258" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E258" s="58" t="s">
         <v>631</v>
@@ -26999,7 +27139,7 @@
         <v>683</v>
       </c>
       <c r="M258" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N258" s="32" t="s">
         <v>1</v>
@@ -27046,10 +27186,10 @@
         <v>577</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D259" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E259" s="58" t="s">
         <v>631</v>
@@ -27076,7 +27216,7 @@
         <v>683</v>
       </c>
       <c r="M259" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N259" s="32" t="s">
         <v>1</v>
@@ -27123,10 +27263,10 @@
         <v>578</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D260" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E260" s="58" t="s">
         <v>631</v>
@@ -27153,7 +27293,7 @@
         <v>683</v>
       </c>
       <c r="M260" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N260" s="32" t="s">
         <v>1</v>
@@ -27200,10 +27340,10 @@
         <v>579</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>840</v>
+        <v>832</v>
       </c>
       <c r="D261" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E261" s="58" t="s">
         <v>631</v>
@@ -27230,7 +27370,7 @@
         <v>683</v>
       </c>
       <c r="M261" s="35" t="s">
-        <v>785</v>
+        <v>778</v>
       </c>
       <c r="N261" s="32" t="s">
         <v>1</v>
@@ -27277,10 +27417,10 @@
         <v>580</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D262" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E262" s="58" t="s">
         <v>631</v>
@@ -27354,10 +27494,10 @@
         <v>581</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D263" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E263" s="58" t="s">
         <v>631</v>
@@ -27431,10 +27571,10 @@
         <v>582</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D264" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E264" s="58" t="s">
         <v>631</v>
@@ -27508,10 +27648,10 @@
         <v>583</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D265" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E265" s="58" t="s">
         <v>631</v>
@@ -27585,10 +27725,10 @@
         <v>584</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D266" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E266" s="58" t="s">
         <v>631</v>
@@ -27662,10 +27802,10 @@
         <v>585</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D267" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E267" s="58" t="s">
         <v>631</v>
@@ -27739,10 +27879,10 @@
         <v>586</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D268" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E268" s="58" t="s">
         <v>631</v>
@@ -27816,10 +27956,10 @@
         <v>587</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D269" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E269" s="58" t="s">
         <v>631</v>
@@ -27893,10 +28033,10 @@
         <v>588</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D270" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E270" s="58" t="s">
         <v>631</v>
@@ -27970,10 +28110,10 @@
         <v>589</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D271" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E271" s="58" t="s">
         <v>631</v>
@@ -28047,10 +28187,10 @@
         <v>590</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D272" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E272" s="58" t="s">
         <v>631</v>
@@ -28124,10 +28264,10 @@
         <v>591</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D273" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E273" s="58" t="s">
         <v>631</v>
@@ -28201,10 +28341,10 @@
         <v>592</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D274" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E274" s="58" t="s">
         <v>631</v>
@@ -28278,10 +28418,10 @@
         <v>593</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D275" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E275" s="58" t="s">
         <v>631</v>
@@ -28355,10 +28495,10 @@
         <v>594</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D276" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E276" s="58" t="s">
         <v>631</v>
@@ -28432,10 +28572,10 @@
         <v>595</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D277" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E277" s="58" t="s">
         <v>631</v>
@@ -28509,10 +28649,10 @@
         <v>596</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D278" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E278" s="58" t="s">
         <v>631</v>
@@ -28586,10 +28726,10 @@
         <v>597</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D279" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E279" s="58" t="s">
         <v>631</v>
@@ -28663,10 +28803,10 @@
         <v>598</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D280" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E280" s="58" t="s">
         <v>631</v>
@@ -28740,10 +28880,10 @@
         <v>599</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D281" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E281" s="58" t="s">
         <v>631</v>
@@ -28817,10 +28957,10 @@
         <v>600</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D282" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E282" s="58" t="s">
         <v>631</v>
@@ -28894,10 +29034,10 @@
         <v>601</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D283" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E283" s="58" t="s">
         <v>631</v>
@@ -28971,10 +29111,10 @@
         <v>602</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D284" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E284" s="58" t="s">
         <v>631</v>
@@ -29048,10 +29188,10 @@
         <v>603</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D285" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E285" s="58" t="s">
         <v>631</v>
@@ -29125,10 +29265,10 @@
         <v>604</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>841</v>
+        <v>833</v>
       </c>
       <c r="D286" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E286" s="58" t="s">
         <v>631</v>
@@ -29202,10 +29342,10 @@
         <v>605</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D287" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E287" s="58" t="s">
         <v>631</v>
@@ -29232,7 +29372,7 @@
         <v>683</v>
       </c>
       <c r="M287" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N287" s="32" t="s">
         <v>1</v>
@@ -29279,10 +29419,10 @@
         <v>606</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D288" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E288" s="58" t="s">
         <v>631</v>
@@ -29309,7 +29449,7 @@
         <v>683</v>
       </c>
       <c r="M288" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N288" s="32" t="s">
         <v>1</v>
@@ -29356,10 +29496,10 @@
         <v>607</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D289" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E289" s="58" t="s">
         <v>631</v>
@@ -29386,7 +29526,7 @@
         <v>683</v>
       </c>
       <c r="M289" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N289" s="32" t="s">
         <v>1</v>
@@ -29433,10 +29573,10 @@
         <v>608</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D290" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E290" s="58" t="s">
         <v>631</v>
@@ -29463,7 +29603,7 @@
         <v>683</v>
       </c>
       <c r="M290" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N290" s="32" t="s">
         <v>1</v>
@@ -29510,10 +29650,10 @@
         <v>609</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D291" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E291" s="58" t="s">
         <v>631</v>
@@ -29540,7 +29680,7 @@
         <v>683</v>
       </c>
       <c r="M291" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N291" s="32" t="s">
         <v>1</v>
@@ -29587,10 +29727,10 @@
         <v>610</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D292" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E292" s="58" t="s">
         <v>631</v>
@@ -29617,7 +29757,7 @@
         <v>683</v>
       </c>
       <c r="M292" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N292" s="32" t="s">
         <v>1</v>
@@ -29664,10 +29804,10 @@
         <v>611</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D293" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E293" s="58" t="s">
         <v>631</v>
@@ -29694,7 +29834,7 @@
         <v>683</v>
       </c>
       <c r="M293" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N293" s="32" t="s">
         <v>1</v>
@@ -29741,10 +29881,10 @@
         <v>612</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D294" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E294" s="58" t="s">
         <v>631</v>
@@ -29771,7 +29911,7 @@
         <v>683</v>
       </c>
       <c r="M294" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N294" s="32" t="s">
         <v>1</v>
@@ -29818,10 +29958,10 @@
         <v>613</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>842</v>
+        <v>834</v>
       </c>
       <c r="D295" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E295" s="58" t="s">
         <v>631</v>
@@ -29848,7 +29988,7 @@
         <v>683</v>
       </c>
       <c r="M295" s="35" t="s">
-        <v>786</v>
+        <v>779</v>
       </c>
       <c r="N295" s="32" t="s">
         <v>1</v>
@@ -29895,10 +30035,10 @@
         <v>614</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D296" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E296" s="58" t="s">
         <v>631</v>
@@ -29925,7 +30065,7 @@
         <v>683</v>
       </c>
       <c r="M296" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N296" s="32" t="s">
         <v>1</v>
@@ -29972,10 +30112,10 @@
         <v>615</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D297" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E297" s="58" t="s">
         <v>631</v>
@@ -30002,7 +30142,7 @@
         <v>683</v>
       </c>
       <c r="M297" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N297" s="32" t="s">
         <v>1</v>
@@ -30049,10 +30189,10 @@
         <v>616</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D298" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E298" s="58" t="s">
         <v>631</v>
@@ -30079,7 +30219,7 @@
         <v>683</v>
       </c>
       <c r="M298" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N298" s="32" t="s">
         <v>1</v>
@@ -30126,10 +30266,10 @@
         <v>617</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D299" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E299" s="58" t="s">
         <v>631</v>
@@ -30156,7 +30296,7 @@
         <v>683</v>
       </c>
       <c r="M299" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N299" s="32" t="s">
         <v>1</v>
@@ -30203,10 +30343,10 @@
         <v>618</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D300" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E300" s="58" t="s">
         <v>631</v>
@@ -30233,7 +30373,7 @@
         <v>683</v>
       </c>
       <c r="M300" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N300" s="32" t="s">
         <v>1</v>
@@ -30280,10 +30420,10 @@
         <v>619</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D301" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E301" s="58" t="s">
         <v>631</v>
@@ -30310,7 +30450,7 @@
         <v>683</v>
       </c>
       <c r="M301" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N301" s="32" t="s">
         <v>1</v>
@@ -30357,10 +30497,10 @@
         <v>620</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D302" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E302" s="58" t="s">
         <v>631</v>
@@ -30387,7 +30527,7 @@
         <v>683</v>
       </c>
       <c r="M302" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N302" s="32" t="s">
         <v>1</v>
@@ -30434,10 +30574,10 @@
         <v>621</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D303" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E303" s="58" t="s">
         <v>631</v>
@@ -30464,7 +30604,7 @@
         <v>683</v>
       </c>
       <c r="M303" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N303" s="32" t="s">
         <v>1</v>
@@ -30511,10 +30651,10 @@
         <v>622</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D304" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E304" s="58" t="s">
         <v>631</v>
@@ -30541,7 +30681,7 @@
         <v>683</v>
       </c>
       <c r="M304" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N304" s="32" t="s">
         <v>1</v>
@@ -30588,10 +30728,10 @@
         <v>623</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>843</v>
+        <v>835</v>
       </c>
       <c r="D305" s="57" t="s">
-        <v>776</v>
+        <v>769</v>
       </c>
       <c r="E305" s="58" t="s">
         <v>631</v>
@@ -30618,7 +30758,7 @@
         <v>683</v>
       </c>
       <c r="M305" s="35" t="s">
-        <v>787</v>
+        <v>780</v>
       </c>
       <c r="N305" s="32" t="s">
         <v>1</v>
@@ -30660,60 +30800,60 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr codeName="EstaPastaDeTrabalho"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77ACF6D8-B71C-470C-986B-B5090EAB50B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -3136,119 +3136,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="36">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -3998,7 +3886,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46167.411252314814</v>
+        <v>46214.346841666666</v>
       </c>
       <c r="C18" s="41" t="s">
         <v>691</v>
@@ -7061,35 +6949,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A32">
-    <cfRule type="cellIs" dxfId="35" priority="15" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="30" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="22"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA32">
-    <cfRule type="cellIs" dxfId="26" priority="13" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:A6">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+  <conditionalFormatting sqref="A2:A32">
+    <cfRule type="cellIs" dxfId="23" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:F6">
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="6"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="18" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="22"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA1:AA32">
+    <cfRule type="cellIs" dxfId="14" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7239,7 +7117,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="25" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7284,7 +7162,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30800,60 +30678,60 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="23" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="22" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="21" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="18" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="16" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="15" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="14" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729D9875-7B4A-4225-A6FA-042837DB7FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73AAD302-C87A-458D-AA06-9379C3C0DFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="841">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="840">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2596,9 +2596,6 @@
   </si>
   <si>
     <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1.</t>
-  </si>
-  <si>
-    <t>Arquitetura</t>
   </si>
   <si>
     <t>[ 5I ]</t>
@@ -3103,63 +3100,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="30">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="24">
     <dxf>
       <font>
         <b val="0"/>
@@ -3909,7 +3850,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46216.267021064814</v>
+        <v>46219.568221412039</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>690</v>
@@ -4014,7 +3955,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F6EEAB6-D26C-4450-83AD-F740CF51FA1E}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AA32"/>
-  <sheetFormatPr defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.6640625" style="27" bestFit="1" customWidth="1"/>
@@ -4041,7 +3982,7 @@
     <col min="27" max="27" width="79.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="27.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>637</v>
       </c>
@@ -4124,7 +4065,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="2" spans="1:27" s="27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:27" s="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="46">
         <v>2</v>
       </c>
@@ -4196,7 +4137,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V2" s="35" t="s">
-        <v>835</v>
+        <v>709</v>
       </c>
       <c r="W2" s="55" t="str">
         <f>CONCATENATE("Key-ABNT-",A2)</f>
@@ -4209,14 +4150,14 @@
         <v>321</v>
       </c>
       <c r="Z2" s="35" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AA2" s="35" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Project Definition.</v>
       </c>
     </row>
-    <row r="3" spans="1:27" s="27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:27" s="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="46">
         <v>3</v>
       </c>
@@ -4267,7 +4208,7 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="35" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="Q3" s="35" t="s">
         <v>834</v>
@@ -4288,7 +4229,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V3" s="35" t="s">
-        <v>835</v>
+        <v>709</v>
       </c>
       <c r="W3" s="55" t="str">
         <f t="shared" ref="W3:W32" si="4">CONCATENATE("Key-ABNT-",A3)</f>
@@ -4308,7 +4249,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
       </c>
     </row>
-    <row r="4" spans="1:27" s="27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:27" s="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="46">
         <v>4</v>
       </c>
@@ -4359,7 +4300,7 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="Q4" s="35" t="s">
         <v>834</v>
@@ -4380,7 +4321,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V4" s="35" t="s">
-        <v>835</v>
+        <v>709</v>
       </c>
       <c r="W4" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4400,7 +4341,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" s="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="46">
         <v>5</v>
       </c>
@@ -4451,7 +4392,7 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="35" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="Q5" s="35" t="s">
         <v>834</v>
@@ -4472,7 +4413,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V5" s="35" t="s">
-        <v>835</v>
+        <v>709</v>
       </c>
       <c r="W5" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4492,7 +4433,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
       </c>
     </row>
-    <row r="6" spans="1:27" s="27" customFormat="1" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" s="27" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="46">
         <v>6</v>
       </c>
@@ -4543,7 +4484,7 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="35" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="Q6" s="35" t="s">
         <v>834</v>
@@ -4564,7 +4505,7 @@
         <v>Contêineres</v>
       </c>
       <c r="V6" s="35" t="s">
-        <v>835</v>
+        <v>709</v>
       </c>
       <c r="W6" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4584,7 +4525,7 @@
         <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="46">
         <v>7</v>
       </c>
@@ -4675,7 +4616,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="46">
         <v>8</v>
       </c>
@@ -4766,7 +4707,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="46">
         <v>9</v>
       </c>
@@ -4857,7 +4798,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="46">
         <v>10</v>
       </c>
@@ -4948,7 +4889,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="46">
         <v>11</v>
       </c>
@@ -5039,7 +4980,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="46">
         <v>12</v>
       </c>
@@ -5130,7 +5071,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="46">
         <v>13</v>
       </c>
@@ -5221,7 +5162,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="46">
         <v>14</v>
       </c>
@@ -5312,7 +5253,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="46">
         <v>15</v>
       </c>
@@ -5403,7 +5344,7 @@
         <v>742</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="46">
         <v>16</v>
       </c>
@@ -5494,7 +5435,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="46">
         <v>17</v>
       </c>
@@ -5585,7 +5526,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="46">
         <v>18</v>
       </c>
@@ -5676,7 +5617,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="46">
         <v>19</v>
       </c>
@@ -5767,7 +5708,7 @@
         <v>758</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="46">
         <v>20</v>
       </c>
@@ -5860,7 +5801,7 @@
         <v>Transactional services</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="46">
         <v>21</v>
       </c>
@@ -5953,7 +5894,7 @@
         <v>Administrative services</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="46">
         <v>22</v>
       </c>
@@ -6046,7 +5987,7 @@
         <v>Communication Services</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="46">
         <v>23</v>
       </c>
@@ -6139,7 +6080,7 @@
         <v>Conceptualization Services</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="46">
         <v>24</v>
       </c>
@@ -6232,7 +6173,7 @@
         <v>Information services</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="46">
         <v>25</v>
       </c>
@@ -6325,7 +6266,7 @@
         <v>Organization Services</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="46">
         <v>26</v>
       </c>
@@ -6418,7 +6359,7 @@
         <v>Project Development Services</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="46">
         <v>27</v>
       </c>
@@ -6511,7 +6452,7 @@
         <v>Document Services</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="46">
         <v>28</v>
       </c>
@@ -6604,7 +6545,7 @@
         <v>Implementation Services</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="46">
         <v>29</v>
       </c>
@@ -6697,7 +6638,7 @@
         <v>Building Operation Services</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="46">
         <v>30</v>
       </c>
@@ -6790,7 +6731,7 @@
         <v>Support Services</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="46">
         <v>31</v>
       </c>
@@ -6883,7 +6824,7 @@
         <v>Government Services</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="6.6" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="46">
         <v>32</v>
       </c>
@@ -6977,35 +6918,25 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A7:A32">
-    <cfRule type="cellIs" dxfId="29" priority="9" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="24" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA1 AA7:AA32">
-    <cfRule type="cellIs" dxfId="20" priority="7" operator="equal">
+  <conditionalFormatting sqref="A2:B32">
+    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="5" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B6 B7:B32">
-    <cfRule type="cellIs" dxfId="1" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA2:AA6">
-    <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA32">
+    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7155,7 +7086,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7200,7 +7131,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="18" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30716,60 +30647,60 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="17" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="16" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="15" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="14" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="11" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="10" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="8" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="6" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1300785E-F444-4D51-834E-BF0D456063CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D752DB79-92D0-46CD-83AA-BA4D25B97595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="839">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="846">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2232,141 +2232,42 @@
     <t>Requisito.Sistemas</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
     <t>0M</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
     <t>0P</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
     <t>1D</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
     <t>1F</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2C</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C.</t>
-  </si>
-  <si>
     <t>2N</t>
   </si>
   <si>
     <t>2Q</t>
   </si>
   <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
     <t>3E</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
     <t>3R</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
     <t>4A</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
     <t>4U</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U.</t>
-  </si>
-  <si>
-    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
-    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>5I</t>
   </si>
   <si>
-    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I.</t>
-  </si>
-  <si>
     <t>"Normas"</t>
   </si>
   <si>
@@ -2608,6 +2509,126 @@
   </si>
   <si>
     <t>NBR.Temática</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
+  </si>
+  <si>
+    <t>Interdiciplinar</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0P. Códigos de Propriedades.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0P. Códigos de propiedad.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0P. Property Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1D. Códigos de Disciplinas.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1D. Códigos disciplinarios.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1D. Discipline Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1F. Códigos de Fases.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1F. Códigos de fase.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1F. Phase Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 1S. Códigos de Serviços.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 1S. Códigos de servicio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 1S. Service Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2C. Códigos de Produtos construtivos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2C. Códigos de Productos Constructivos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2C. Codes of Constructive Products.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2N. Códigos de Recursos Humanos.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2N. Human Resources Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 2Q. Códigos de Equipamentos.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 2Q. Códigos de equipo.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 2Q. Equipment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3E. Códigos de Elementos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3E. Códigos de elementos de edificio.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3E. Building Element Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 3R. Códigos de Recursos da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 3R. Códigos de recursos de construcción.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 3R. Building Resource Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4A. Códigos de Ambientes.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4A. Códigos de medio ambiente.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4A. Environment Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 4U. Códigos de Unidades funcionais.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 4U. Códigos de unidad funcional.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 4U. Functional Unit Codes.</t>
+  </si>
+  <si>
+    <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 5I. Códigos de Informação da construção.</t>
+  </si>
+  <si>
+    <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 5I. Códigos de información de edificación.</t>
+  </si>
+  <si>
+    <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
   </si>
 </sst>
 </file>
@@ -3097,7 +3118,33 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="27">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3847,7 +3894,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46228.453982060186</v>
+        <v>46232.781416087964</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
@@ -4067,7 +4114,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C2" s="47" t="s">
         <v>705</v>
@@ -4076,7 +4123,7 @@
         <v>707</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="F2" s="48" t="s">
         <v>706</v>
@@ -4097,7 +4144,7 @@
         <v>321</v>
       </c>
       <c r="L2" s="50" t="str">
-        <f t="shared" ref="L2:M6" si="0">CONCATENATE("", C2)</f>
+        <f t="shared" ref="L2:N17" si="0">CONCATENATE("", C2)</f>
         <v>Gestão</v>
       </c>
       <c r="M2" s="50" t="str">
@@ -4113,10 +4160,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="35" t="s">
-        <v>830</v>
+        <v>797</v>
       </c>
       <c r="Q2" s="35" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="R2" s="35" t="s">
         <v>321</v>
@@ -4147,7 +4194,7 @@
         <v>321</v>
       </c>
       <c r="Z2" s="35" t="s">
-        <v>832</v>
+        <v>799</v>
       </c>
       <c r="AA2" s="35" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -4159,7 +4206,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C3" s="47" t="s">
         <v>705</v>
@@ -4168,7 +4215,7 @@
         <v>707</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="F3" s="48" t="s">
         <v>709</v>
@@ -4205,10 +4252,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="35" t="s">
-        <v>833</v>
+        <v>800</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="R3" s="35" t="s">
         <v>321</v>
@@ -4251,7 +4298,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C4" s="47" t="s">
         <v>705</v>
@@ -4260,7 +4307,7 @@
         <v>707</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="F4" s="48" t="s">
         <v>710</v>
@@ -4297,10 +4344,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>834</v>
+        <v>801</v>
       </c>
       <c r="Q4" s="35" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>321</v>
@@ -4343,7 +4390,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C5" s="47" t="s">
         <v>705</v>
@@ -4352,7 +4399,7 @@
         <v>707</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="F5" s="48" t="s">
         <v>711</v>
@@ -4389,10 +4436,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="35" t="s">
-        <v>835</v>
+        <v>802</v>
       </c>
       <c r="Q5" s="35" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>321</v>
@@ -4435,7 +4482,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>705</v>
@@ -4444,7 +4491,7 @@
         <v>707</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>829</v>
+        <v>796</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>712</v>
@@ -4481,10 +4528,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="35" t="s">
-        <v>836</v>
+        <v>803</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>831</v>
+        <v>798</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>321</v>
@@ -4527,19 +4574,19 @@
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>773</v>
+        <v>740</v>
       </c>
       <c r="G7" s="29" t="s">
         <v>321</v>
@@ -4557,44 +4604,44 @@
         <v>321</v>
       </c>
       <c r="L7" s="50" t="str">
-        <f t="shared" ref="L7:N17" si="5">CONCATENATE("", C7)</f>
+        <f t="shared" si="0"/>
         <v>Normativo</v>
       </c>
       <c r="M7" s="50" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>ABNT</v>
       </c>
       <c r="N7" s="50" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="0"/>
         <v>NBR.Parte</v>
       </c>
       <c r="O7" s="50" t="str">
-        <f t="shared" ref="O7:O32" si="6">F7</f>
+        <f t="shared" ref="O7:O19" si="5">F7</f>
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="50" t="s">
-        <v>713</v>
+        <v>806</v>
       </c>
       <c r="Q7" s="50" t="s">
-        <v>714</v>
+        <v>807</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S7" s="51" t="str">
-        <f t="shared" ref="S7:U22" si="7">SUBSTITUTE(C7, "_", " ")</f>
+        <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T7" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
       <c r="U7" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W7" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4607,10 +4654,10 @@
         <v>321</v>
       </c>
       <c r="Z7" s="35" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="AA7" s="52" t="s">
-        <v>716</v>
+        <v>809</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4618,19 +4665,19 @@
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>774</v>
+        <v>741</v>
       </c>
       <c r="G8" s="29" t="s">
         <v>321</v>
@@ -4648,44 +4695,44 @@
         <v>321</v>
       </c>
       <c r="L8" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M8" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N8" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O8" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.0P</v>
+      </c>
+      <c r="P8" s="50" t="s">
+        <v>810</v>
+      </c>
+      <c r="Q8" s="50" t="s">
+        <v>811</v>
+      </c>
+      <c r="R8" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S8" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M8" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T8" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N8" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U8" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O8" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.0P</v>
-      </c>
-      <c r="P8" s="50" t="s">
-        <v>717</v>
-      </c>
-      <c r="Q8" s="50" t="s">
-        <v>718</v>
-      </c>
-      <c r="R8" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S8" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T8" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U8" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V8" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W8" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4698,10 +4745,10 @@
         <v>321</v>
       </c>
       <c r="Z8" s="35" t="s">
-        <v>719</v>
+        <v>714</v>
       </c>
       <c r="AA8" s="52" t="s">
-        <v>720</v>
+        <v>812</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4709,19 +4756,19 @@
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>775</v>
+        <v>742</v>
       </c>
       <c r="G9" s="29" t="s">
         <v>321</v>
@@ -4739,44 +4786,44 @@
         <v>321</v>
       </c>
       <c r="L9" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M9" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N9" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O9" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1D</v>
+      </c>
+      <c r="P9" s="50" t="s">
+        <v>813</v>
+      </c>
+      <c r="Q9" s="50" t="s">
+        <v>814</v>
+      </c>
+      <c r="R9" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S9" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M9" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T9" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N9" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U9" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O9" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1D</v>
-      </c>
-      <c r="P9" s="50" t="s">
-        <v>721</v>
-      </c>
-      <c r="Q9" s="50" t="s">
-        <v>722</v>
-      </c>
-      <c r="R9" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S9" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T9" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U9" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V9" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W9" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4789,10 +4836,10 @@
         <v>321</v>
       </c>
       <c r="Z9" s="35" t="s">
-        <v>723</v>
+        <v>715</v>
       </c>
       <c r="AA9" s="52" t="s">
-        <v>724</v>
+        <v>815</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4800,19 +4847,19 @@
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>776</v>
+        <v>743</v>
       </c>
       <c r="G10" s="29" t="s">
         <v>321</v>
@@ -4830,44 +4877,44 @@
         <v>321</v>
       </c>
       <c r="L10" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M10" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N10" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O10" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1F</v>
+      </c>
+      <c r="P10" s="50" t="s">
+        <v>816</v>
+      </c>
+      <c r="Q10" s="50" t="s">
+        <v>817</v>
+      </c>
+      <c r="R10" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S10" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M10" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T10" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N10" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U10" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O10" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1F</v>
-      </c>
-      <c r="P10" s="50" t="s">
-        <v>725</v>
-      </c>
-      <c r="Q10" s="50" t="s">
-        <v>726</v>
-      </c>
-      <c r="R10" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S10" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T10" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U10" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V10" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W10" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4880,10 +4927,10 @@
         <v>321</v>
       </c>
       <c r="Z10" s="35" t="s">
-        <v>727</v>
+        <v>716</v>
       </c>
       <c r="AA10" s="52" t="s">
-        <v>728</v>
+        <v>818</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4891,19 +4938,19 @@
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F11" s="19" t="s">
-        <v>777</v>
+        <v>744</v>
       </c>
       <c r="G11" s="29" t="s">
         <v>321</v>
@@ -4921,44 +4968,44 @@
         <v>321</v>
       </c>
       <c r="L11" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M11" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N11" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O11" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.1S</v>
+      </c>
+      <c r="P11" s="50" t="s">
+        <v>819</v>
+      </c>
+      <c r="Q11" s="50" t="s">
+        <v>820</v>
+      </c>
+      <c r="R11" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S11" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M11" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T11" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N11" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U11" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O11" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.1S</v>
-      </c>
-      <c r="P11" s="50" t="s">
-        <v>729</v>
-      </c>
-      <c r="Q11" s="50" t="s">
-        <v>730</v>
-      </c>
-      <c r="R11" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S11" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T11" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U11" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V11" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W11" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4974,7 +5021,7 @@
         <v>624</v>
       </c>
       <c r="AA11" s="52" t="s">
-        <v>731</v>
+        <v>821</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4982,19 +5029,19 @@
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>778</v>
+        <v>745</v>
       </c>
       <c r="G12" s="29" t="s">
         <v>321</v>
@@ -5012,44 +5059,44 @@
         <v>321</v>
       </c>
       <c r="L12" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M12" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N12" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O12" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2C</v>
+      </c>
+      <c r="P12" s="50" t="s">
+        <v>822</v>
+      </c>
+      <c r="Q12" s="50" t="s">
+        <v>823</v>
+      </c>
+      <c r="R12" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S12" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M12" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T12" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N12" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U12" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O12" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2C</v>
-      </c>
-      <c r="P12" s="50" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q12" s="50" t="s">
-        <v>733</v>
-      </c>
-      <c r="R12" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S12" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T12" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U12" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V12" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W12" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5062,10 +5109,10 @@
         <v>321</v>
       </c>
       <c r="Z12" s="35" t="s">
-        <v>734</v>
+        <v>717</v>
       </c>
       <c r="AA12" s="52" t="s">
-        <v>735</v>
+        <v>824</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5073,19 +5120,19 @@
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>779</v>
+        <v>746</v>
       </c>
       <c r="G13" s="29" t="s">
         <v>321</v>
@@ -5103,44 +5150,44 @@
         <v>321</v>
       </c>
       <c r="L13" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M13" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N13" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O13" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2N</v>
+      </c>
+      <c r="P13" s="50" t="s">
+        <v>825</v>
+      </c>
+      <c r="Q13" s="50" t="s">
+        <v>826</v>
+      </c>
+      <c r="R13" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S13" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M13" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T13" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N13" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U13" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O13" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2N</v>
-      </c>
-      <c r="P13" s="50" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q13" s="50" t="s">
-        <v>733</v>
-      </c>
-      <c r="R13" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S13" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T13" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U13" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V13" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W13" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5153,10 +5200,10 @@
         <v>321</v>
       </c>
       <c r="Z13" s="35" t="s">
-        <v>736</v>
+        <v>718</v>
       </c>
       <c r="AA13" s="52" t="s">
-        <v>735</v>
+        <v>827</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5164,19 +5211,19 @@
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>780</v>
+        <v>747</v>
       </c>
       <c r="G14" s="29" t="s">
         <v>321</v>
@@ -5194,44 +5241,44 @@
         <v>321</v>
       </c>
       <c r="L14" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M14" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N14" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O14" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.2Q</v>
+      </c>
+      <c r="P14" s="50" t="s">
+        <v>828</v>
+      </c>
+      <c r="Q14" s="50" t="s">
+        <v>829</v>
+      </c>
+      <c r="R14" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S14" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M14" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T14" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N14" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U14" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O14" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.2Q</v>
-      </c>
-      <c r="P14" s="50" t="s">
-        <v>732</v>
-      </c>
-      <c r="Q14" s="50" t="s">
-        <v>733</v>
-      </c>
-      <c r="R14" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S14" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T14" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U14" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V14" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W14" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5244,10 +5291,10 @@
         <v>321</v>
       </c>
       <c r="Z14" s="35" t="s">
-        <v>737</v>
+        <v>719</v>
       </c>
       <c r="AA14" s="52" t="s">
-        <v>735</v>
+        <v>830</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5255,19 +5302,19 @@
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>781</v>
+        <v>748</v>
       </c>
       <c r="G15" s="29" t="s">
         <v>321</v>
@@ -5285,44 +5332,44 @@
         <v>321</v>
       </c>
       <c r="L15" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M15" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N15" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O15" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3E</v>
+      </c>
+      <c r="P15" s="50" t="s">
+        <v>831</v>
+      </c>
+      <c r="Q15" s="50" t="s">
+        <v>832</v>
+      </c>
+      <c r="R15" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S15" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M15" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T15" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N15" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U15" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O15" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3E</v>
-      </c>
-      <c r="P15" s="50" t="s">
-        <v>738</v>
-      </c>
-      <c r="Q15" s="50" t="s">
-        <v>739</v>
-      </c>
-      <c r="R15" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S15" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T15" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U15" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V15" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W15" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5335,10 +5382,10 @@
         <v>321</v>
       </c>
       <c r="Z15" s="35" t="s">
-        <v>740</v>
+        <v>720</v>
       </c>
       <c r="AA15" s="52" t="s">
-        <v>741</v>
+        <v>833</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5346,19 +5393,19 @@
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>782</v>
+        <v>749</v>
       </c>
       <c r="G16" s="29" t="s">
         <v>321</v>
@@ -5376,44 +5423,44 @@
         <v>321</v>
       </c>
       <c r="L16" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M16" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N16" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O16" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.3R</v>
+      </c>
+      <c r="P16" s="50" t="s">
+        <v>834</v>
+      </c>
+      <c r="Q16" s="50" t="s">
+        <v>835</v>
+      </c>
+      <c r="R16" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S16" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M16" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T16" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N16" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U16" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O16" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.3R</v>
-      </c>
-      <c r="P16" s="50" t="s">
-        <v>742</v>
-      </c>
-      <c r="Q16" s="50" t="s">
-        <v>743</v>
-      </c>
-      <c r="R16" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S16" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T16" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U16" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V16" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W16" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5426,10 +5473,10 @@
         <v>321</v>
       </c>
       <c r="Z16" s="35" t="s">
-        <v>744</v>
+        <v>721</v>
       </c>
       <c r="AA16" s="52" t="s">
-        <v>745</v>
+        <v>836</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5437,19 +5484,19 @@
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>783</v>
+        <v>750</v>
       </c>
       <c r="G17" s="29" t="s">
         <v>321</v>
@@ -5467,44 +5514,44 @@
         <v>321</v>
       </c>
       <c r="L17" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>Normativo</v>
+      </c>
+      <c r="M17" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>ABNT</v>
+      </c>
+      <c r="N17" s="50" t="str">
+        <f t="shared" si="0"/>
+        <v>NBR.Parte</v>
+      </c>
+      <c r="O17" s="50" t="str">
         <f t="shared" si="5"/>
+        <v>NBR.4A</v>
+      </c>
+      <c r="P17" s="50" t="s">
+        <v>837</v>
+      </c>
+      <c r="Q17" s="50" t="s">
+        <v>838</v>
+      </c>
+      <c r="R17" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S17" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>Normativo</v>
       </c>
-      <c r="M17" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="T17" s="51" t="str">
+        <f t="shared" si="6"/>
         <v>ABNT</v>
       </c>
-      <c r="N17" s="50" t="str">
-        <f t="shared" si="5"/>
+      <c r="U17" s="50" t="str">
+        <f t="shared" si="6"/>
         <v>NBR.Parte</v>
       </c>
-      <c r="O17" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4A</v>
-      </c>
-      <c r="P17" s="50" t="s">
-        <v>746</v>
-      </c>
-      <c r="Q17" s="50" t="s">
-        <v>747</v>
-      </c>
-      <c r="R17" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S17" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T17" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>ABNT</v>
-      </c>
-      <c r="U17" s="50" t="str">
-        <f t="shared" si="7"/>
-        <v>NBR.Parte</v>
-      </c>
       <c r="V17" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W17" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5517,10 +5564,10 @@
         <v>321</v>
       </c>
       <c r="Z17" s="35" t="s">
-        <v>748</v>
+        <v>722</v>
       </c>
       <c r="AA17" s="52" t="s">
-        <v>749</v>
+        <v>839</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5528,19 +5575,19 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>784</v>
+        <v>751</v>
       </c>
       <c r="G18" s="29" t="s">
         <v>321</v>
@@ -5558,44 +5605,44 @@
         <v>321</v>
       </c>
       <c r="L18" s="50" t="str">
-        <f t="shared" ref="L18:N32" si="8">CONCATENATE("", C18)</f>
+        <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
         <v>Normativo</v>
       </c>
       <c r="M18" s="50" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N18" s="50" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O18" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.4U</v>
-      </c>
-      <c r="P18" s="50" t="s">
-        <v>750</v>
-      </c>
-      <c r="Q18" s="50" t="s">
-        <v>751</v>
-      </c>
-      <c r="R18" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S18" s="51" t="str">
-        <f t="shared" si="7"/>
-        <v>Normativo</v>
-      </c>
-      <c r="T18" s="51" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U18" s="50" t="str">
+      <c r="N18" s="50" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O18" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.4U</v>
+      </c>
+      <c r="P18" s="50" t="s">
+        <v>840</v>
+      </c>
+      <c r="Q18" s="50" t="s">
+        <v>841</v>
+      </c>
+      <c r="R18" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S18" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T18" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U18" s="50" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V18" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W18" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5608,10 +5655,10 @@
         <v>321</v>
       </c>
       <c r="Z18" s="35" t="s">
-        <v>752</v>
+        <v>723</v>
       </c>
       <c r="AA18" s="52" t="s">
-        <v>753</v>
+        <v>842</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5619,19 +5666,19 @@
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>656</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>785</v>
+        <v>752</v>
       </c>
       <c r="G19" s="29" t="s">
         <v>321</v>
@@ -5649,44 +5696,44 @@
         <v>321</v>
       </c>
       <c r="L19" s="50" t="str">
-        <f t="shared" si="8"/>
-        <v>Normativo</v>
-      </c>
-      <c r="M19" s="50" t="str">
-        <f t="shared" si="8"/>
-        <v>ABNT</v>
-      </c>
-      <c r="N19" s="50" t="str">
-        <f t="shared" si="8"/>
-        <v>NBR.Parte</v>
-      </c>
-      <c r="O19" s="50" t="str">
-        <f t="shared" si="6"/>
-        <v>NBR.5I</v>
-      </c>
-      <c r="P19" s="50" t="s">
-        <v>754</v>
-      </c>
-      <c r="Q19" s="50" t="s">
-        <v>755</v>
-      </c>
-      <c r="R19" s="35" t="s">
-        <v>321</v>
-      </c>
-      <c r="S19" s="51" t="str">
         <f t="shared" si="7"/>
         <v>Normativo</v>
       </c>
-      <c r="T19" s="51" t="str">
+      <c r="M19" s="50" t="str">
         <f t="shared" si="7"/>
         <v>ABNT</v>
       </c>
-      <c r="U19" s="50" t="str">
+      <c r="N19" s="50" t="str">
         <f t="shared" si="7"/>
         <v>NBR.Parte</v>
       </c>
+      <c r="O19" s="50" t="str">
+        <f t="shared" si="5"/>
+        <v>NBR.5I</v>
+      </c>
+      <c r="P19" s="50" t="s">
+        <v>843</v>
+      </c>
+      <c r="Q19" s="50" t="s">
+        <v>844</v>
+      </c>
+      <c r="R19" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="S19" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>Normativo</v>
+      </c>
+      <c r="T19" s="51" t="str">
+        <f t="shared" si="6"/>
+        <v>ABNT</v>
+      </c>
+      <c r="U19" s="50" t="str">
+        <f t="shared" si="6"/>
+        <v>NBR.Parte</v>
+      </c>
       <c r="V19" s="35" t="s">
-        <v>708</v>
+        <v>808</v>
       </c>
       <c r="W19" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5699,10 +5746,10 @@
         <v>321</v>
       </c>
       <c r="Z19" s="35" t="s">
-        <v>756</v>
+        <v>724</v>
       </c>
       <c r="AA19" s="52" t="s">
-        <v>757</v>
+        <v>845</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5710,19 +5757,19 @@
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="G20" s="49" t="s">
         <v>321</v>
@@ -5740,7 +5787,7 @@
         <v>321</v>
       </c>
       <c r="L20" s="50" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="L18:N32" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="50" t="str">
@@ -5752,11 +5799,11 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O20" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="O7:O32" si="9">F20</f>
         <v>NBR.S.Transacional</v>
       </c>
       <c r="P20" s="35" t="s">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="Q20" s="35" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","es")</f>
@@ -5766,15 +5813,15 @@
         <v>321</v>
       </c>
       <c r="S20" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U20" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V20" s="35" t="s">
@@ -5791,7 +5838,7 @@
         <v>321</v>
       </c>
       <c r="Z20" s="51" t="s">
-        <v>786</v>
+        <v>753</v>
       </c>
       <c r="AA20" s="35" t="str">
         <f>_xlfn.TRANSLATE(P20,"pt","en")</f>
@@ -5803,19 +5850,19 @@
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="G21" s="29" t="s">
         <v>321</v>
@@ -5845,29 +5892,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O21" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Administrativo</v>
       </c>
       <c r="P21" s="50" t="s">
-        <v>789</v>
+        <v>756</v>
       </c>
       <c r="Q21" s="35" t="str">
-        <f t="shared" ref="Q21:Q32" si="9">_xlfn.TRANSLATE(P21,"pt","es")</f>
+        <f t="shared" ref="Q21:Q32" si="11">_xlfn.TRANSLATE(P21,"pt","es")</f>
         <v>Servicios administrativos</v>
       </c>
       <c r="R21" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S21" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T21" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U21" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V21" s="35" t="s">
@@ -5884,10 +5931,10 @@
         <v>321</v>
       </c>
       <c r="Z21" s="51" t="s">
-        <v>787</v>
+        <v>754</v>
       </c>
       <c r="AA21" s="35" t="str">
-        <f t="shared" ref="AA21:AA32" si="10">_xlfn.TRANSLATE(P21,"pt","en")</f>
+        <f t="shared" ref="AA21:AA32" si="12">_xlfn.TRANSLATE(P21,"pt","en")</f>
         <v>Administrative services</v>
       </c>
     </row>
@@ -5896,19 +5943,19 @@
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="G22" s="29" t="s">
         <v>321</v>
@@ -5938,29 +5985,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O22" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Comunicação</v>
       </c>
       <c r="P22" s="50" t="s">
-        <v>790</v>
+        <v>757</v>
       </c>
       <c r="Q22" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de comunicación</v>
       </c>
       <c r="R22" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S22" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>Normativo</v>
       </c>
       <c r="T22" s="51" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U22" s="50" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V22" s="35" t="s">
@@ -5977,10 +6024,10 @@
         <v>321</v>
       </c>
       <c r="Z22" s="51" t="s">
-        <v>801</v>
+        <v>768</v>
       </c>
       <c r="AA22" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Communication Services</v>
       </c>
     </row>
@@ -5989,19 +6036,19 @@
         <v>23</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="G23" s="29" t="s">
         <v>321</v>
@@ -6031,29 +6078,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O23" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Conceituação</v>
       </c>
       <c r="P23" s="50" t="s">
-        <v>791</v>
+        <v>758</v>
       </c>
       <c r="Q23" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de Conceptualización</v>
       </c>
       <c r="R23" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S23" s="51" t="str">
-        <f t="shared" ref="S23:U32" si="11">SUBSTITUTE(C23, "_", " ")</f>
+        <f t="shared" ref="S23:U32" si="13">SUBSTITUTE(C23, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T23" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U23" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V23" s="35" t="s">
@@ -6070,10 +6117,10 @@
         <v>321</v>
       </c>
       <c r="Z23" s="51" t="s">
-        <v>802</v>
+        <v>769</v>
       </c>
       <c r="AA23" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Conceptualization Services</v>
       </c>
     </row>
@@ -6082,19 +6129,19 @@
         <v>24</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="G24" s="29" t="s">
         <v>321</v>
@@ -6124,29 +6171,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O24" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Informação</v>
       </c>
       <c r="P24" s="50" t="s">
-        <v>792</v>
+        <v>759</v>
       </c>
       <c r="Q24" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de información</v>
       </c>
       <c r="R24" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S24" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T24" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U24" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V24" s="35" t="s">
@@ -6163,10 +6210,10 @@
         <v>321</v>
       </c>
       <c r="Z24" s="51" t="s">
-        <v>805</v>
+        <v>772</v>
       </c>
       <c r="AA24" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Information services</v>
       </c>
     </row>
@@ -6175,19 +6222,19 @@
         <v>25</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="G25" s="29" t="s">
         <v>321</v>
@@ -6217,29 +6264,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O25" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Organização</v>
       </c>
       <c r="P25" s="50" t="s">
-        <v>793</v>
+        <v>760</v>
       </c>
       <c r="Q25" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de organización</v>
       </c>
       <c r="R25" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S25" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T25" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U25" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V25" s="35" t="s">
@@ -6256,10 +6303,10 @@
         <v>321</v>
       </c>
       <c r="Z25" s="51" t="s">
-        <v>806</v>
+        <v>773</v>
       </c>
       <c r="AA25" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Organization Services</v>
       </c>
     </row>
@@ -6268,19 +6315,19 @@
         <v>26</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="G26" s="29" t="s">
         <v>321</v>
@@ -6310,29 +6357,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O26" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Projetual</v>
       </c>
       <c r="P26" s="50" t="s">
-        <v>794</v>
+        <v>761</v>
       </c>
       <c r="Q26" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de Desarrollo de Proyectos</v>
       </c>
       <c r="R26" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S26" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T26" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U26" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V26" s="35" t="s">
@@ -6349,10 +6396,10 @@
         <v>321</v>
       </c>
       <c r="Z26" s="51" t="s">
-        <v>803</v>
+        <v>770</v>
       </c>
       <c r="AA26" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Project Development Services</v>
       </c>
     </row>
@@ -6361,19 +6408,19 @@
         <v>27</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="G27" s="29" t="s">
         <v>321</v>
@@ -6403,29 +6450,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O27" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Documental</v>
       </c>
       <c r="P27" s="50" t="s">
-        <v>795</v>
+        <v>762</v>
       </c>
       <c r="Q27" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de Documentos</v>
       </c>
       <c r="R27" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S27" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T27" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U27" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V27" s="35" t="s">
@@ -6442,10 +6489,10 @@
         <v>321</v>
       </c>
       <c r="Z27" s="51" t="s">
-        <v>804</v>
+        <v>771</v>
       </c>
       <c r="AA27" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Document Services</v>
       </c>
     </row>
@@ -6454,19 +6501,19 @@
         <v>28</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="G28" s="29" t="s">
         <v>321</v>
@@ -6496,29 +6543,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O28" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Implementação</v>
       </c>
       <c r="P28" s="50" t="s">
-        <v>796</v>
+        <v>763</v>
       </c>
       <c r="Q28" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de Implementación</v>
       </c>
       <c r="R28" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S28" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T28" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U28" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V28" s="35" t="s">
@@ -6535,10 +6582,10 @@
         <v>321</v>
       </c>
       <c r="Z28" s="51" t="s">
-        <v>807</v>
+        <v>774</v>
       </c>
       <c r="AA28" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Implementation Services</v>
       </c>
     </row>
@@ -6547,19 +6594,19 @@
         <v>29</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="G29" s="29" t="s">
         <v>321</v>
@@ -6589,29 +6636,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O29" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Operação.Predial</v>
       </c>
       <c r="P29" s="50" t="s">
-        <v>797</v>
+        <v>764</v>
       </c>
       <c r="Q29" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de Operación de Edificios</v>
       </c>
       <c r="R29" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S29" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T29" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U29" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V29" s="35" t="s">
@@ -6628,10 +6675,10 @@
         <v>321</v>
       </c>
       <c r="Z29" s="51" t="s">
-        <v>808</v>
+        <v>775</v>
       </c>
       <c r="AA29" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Building Operation Services</v>
       </c>
     </row>
@@ -6640,19 +6687,19 @@
         <v>30</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="G30" s="29" t="s">
         <v>321</v>
@@ -6682,29 +6729,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O30" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Suporte</v>
       </c>
       <c r="P30" s="50" t="s">
-        <v>798</v>
+        <v>765</v>
       </c>
       <c r="Q30" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios de apoyo</v>
       </c>
       <c r="R30" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S30" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T30" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U30" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V30" s="35" t="s">
@@ -6721,10 +6768,10 @@
         <v>321</v>
       </c>
       <c r="Z30" s="51" t="s">
-        <v>809</v>
+        <v>776</v>
       </c>
       <c r="AA30" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Support Services</v>
       </c>
     </row>
@@ -6733,19 +6780,19 @@
         <v>31</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="G31" s="29" t="s">
         <v>321</v>
@@ -6775,29 +6822,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O31" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Governo</v>
       </c>
       <c r="P31" s="50" t="s">
-        <v>799</v>
+        <v>766</v>
       </c>
       <c r="Q31" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios gubernamentales</v>
       </c>
       <c r="R31" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S31" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T31" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U31" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V31" s="35" t="s">
@@ -6814,10 +6861,10 @@
         <v>321</v>
       </c>
       <c r="Z31" s="51" t="s">
-        <v>810</v>
+        <v>777</v>
       </c>
       <c r="AA31" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Government Services</v>
       </c>
     </row>
@@ -6826,19 +6873,19 @@
         <v>32</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>828</v>
+        <v>795</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>838</v>
+        <v>805</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>825</v>
+        <v>792</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="G32" s="29" t="s">
         <v>321</v>
@@ -6868,29 +6915,29 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O32" s="50" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>NBR.S.Adicional</v>
       </c>
       <c r="P32" s="50" t="s">
-        <v>800</v>
+        <v>767</v>
       </c>
       <c r="Q32" s="35" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>Servicios adicionales</v>
       </c>
       <c r="R32" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S32" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>Normativo</v>
       </c>
       <c r="T32" s="51" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Temática</v>
       </c>
       <c r="U32" s="50" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="13"/>
         <v>NBR.Serviços</v>
       </c>
       <c r="V32" s="35" t="s">
@@ -6907,33 +6954,46 @@
         <v>321</v>
       </c>
       <c r="Z32" s="51" t="s">
-        <v>811</v>
+        <v>778</v>
       </c>
       <c r="AA32" s="35" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="12"/>
         <v>Additional services</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B32">
-    <cfRule type="cellIs" dxfId="23" priority="6" operator="equal">
+  <conditionalFormatting sqref="A2:B6 A20:B32">
+    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="22" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="7"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="18" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA32">
-    <cfRule type="cellIs" dxfId="14" priority="5" operator="equal">
+  <conditionalFormatting sqref="AA1:AA6 AA20:AA32">
+    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A7:B19">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AA7:AA19">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7083,7 +7143,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7128,7 +7188,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7241,7 +7301,7 @@
         <v>625</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>837</v>
+        <v>804</v>
       </c>
       <c r="D2" s="53" t="s">
         <v>321</v>
@@ -7265,13 +7325,13 @@
         <v>628</v>
       </c>
       <c r="K2" s="33" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="L2" s="41" t="s">
         <v>681</v>
       </c>
       <c r="M2" s="33" t="s">
-        <v>759</v>
+        <v>726</v>
       </c>
       <c r="N2" s="30" t="s">
         <v>1</v>
@@ -7318,10 +7378,10 @@
         <v>631</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>772</v>
+        <v>739</v>
       </c>
       <c r="D3" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E3" s="54" t="s">
         <v>625</v>
@@ -7342,13 +7402,13 @@
         <v>628</v>
       </c>
       <c r="K3" s="33" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="L3" s="41" t="s">
         <v>681</v>
       </c>
       <c r="M3" s="33" t="s">
-        <v>827</v>
+        <v>794</v>
       </c>
       <c r="N3" s="30" t="s">
         <v>1</v>
@@ -7395,10 +7455,10 @@
         <v>624</v>
       </c>
       <c r="C4" s="12" t="s">
-        <v>777</v>
+        <v>744</v>
       </c>
       <c r="D4" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E4" s="54" t="s">
         <v>631</v>
@@ -7419,13 +7479,13 @@
         <v>628</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>758</v>
+        <v>725</v>
       </c>
       <c r="L4" s="41" t="s">
         <v>681</v>
       </c>
       <c r="M4" s="33" t="s">
-        <v>826</v>
+        <v>793</v>
       </c>
       <c r="N4" s="30" t="s">
         <v>1</v>
@@ -7472,10 +7532,10 @@
         <v>328</v>
       </c>
       <c r="C5" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D5" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E5" s="54" t="s">
         <v>631</v>
@@ -7502,7 +7562,7 @@
         <v>681</v>
       </c>
       <c r="M5" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N5" s="30" t="s">
         <v>1</v>
@@ -7549,10 +7609,10 @@
         <v>329</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D6" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E6" s="54" t="s">
         <v>631</v>
@@ -7579,7 +7639,7 @@
         <v>681</v>
       </c>
       <c r="M6" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N6" s="30" t="s">
         <v>1</v>
@@ -7626,10 +7686,10 @@
         <v>330</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D7" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E7" s="54" t="s">
         <v>631</v>
@@ -7656,7 +7716,7 @@
         <v>681</v>
       </c>
       <c r="M7" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N7" s="30" t="s">
         <v>1</v>
@@ -7703,10 +7763,10 @@
         <v>331</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D8" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E8" s="54" t="s">
         <v>631</v>
@@ -7733,7 +7793,7 @@
         <v>681</v>
       </c>
       <c r="M8" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N8" s="30" t="s">
         <v>1</v>
@@ -7780,10 +7840,10 @@
         <v>332</v>
       </c>
       <c r="C9" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D9" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E9" s="54" t="s">
         <v>631</v>
@@ -7810,7 +7870,7 @@
         <v>681</v>
       </c>
       <c r="M9" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N9" s="30" t="s">
         <v>1</v>
@@ -7857,10 +7917,10 @@
         <v>333</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D10" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E10" s="54" t="s">
         <v>631</v>
@@ -7887,7 +7947,7 @@
         <v>681</v>
       </c>
       <c r="M10" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N10" s="30" t="s">
         <v>1</v>
@@ -7934,10 +7994,10 @@
         <v>334</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D11" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E11" s="54" t="s">
         <v>631</v>
@@ -7964,7 +8024,7 @@
         <v>681</v>
       </c>
       <c r="M11" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N11" s="30" t="s">
         <v>1</v>
@@ -8011,10 +8071,10 @@
         <v>335</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D12" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E12" s="54" t="s">
         <v>631</v>
@@ -8041,7 +8101,7 @@
         <v>681</v>
       </c>
       <c r="M12" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N12" s="30" t="s">
         <v>1</v>
@@ -8088,10 +8148,10 @@
         <v>336</v>
       </c>
       <c r="C13" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D13" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E13" s="54" t="s">
         <v>631</v>
@@ -8118,7 +8178,7 @@
         <v>681</v>
       </c>
       <c r="M13" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N13" s="30" t="s">
         <v>1</v>
@@ -8165,10 +8225,10 @@
         <v>337</v>
       </c>
       <c r="C14" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D14" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E14" s="54" t="s">
         <v>631</v>
@@ -8195,7 +8255,7 @@
         <v>681</v>
       </c>
       <c r="M14" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N14" s="30" t="s">
         <v>1</v>
@@ -8242,10 +8302,10 @@
         <v>338</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D15" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E15" s="54" t="s">
         <v>631</v>
@@ -8272,7 +8332,7 @@
         <v>681</v>
       </c>
       <c r="M15" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N15" s="30" t="s">
         <v>1</v>
@@ -8319,10 +8379,10 @@
         <v>339</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D16" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E16" s="54" t="s">
         <v>631</v>
@@ -8349,7 +8409,7 @@
         <v>681</v>
       </c>
       <c r="M16" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N16" s="30" t="s">
         <v>1</v>
@@ -8396,10 +8456,10 @@
         <v>340</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D17" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E17" s="54" t="s">
         <v>631</v>
@@ -8426,7 +8486,7 @@
         <v>681</v>
       </c>
       <c r="M17" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N17" s="30" t="s">
         <v>1</v>
@@ -8473,10 +8533,10 @@
         <v>341</v>
       </c>
       <c r="C18" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D18" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E18" s="54" t="s">
         <v>631</v>
@@ -8503,7 +8563,7 @@
         <v>681</v>
       </c>
       <c r="M18" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N18" s="30" t="s">
         <v>1</v>
@@ -8550,10 +8610,10 @@
         <v>342</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D19" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E19" s="54" t="s">
         <v>631</v>
@@ -8580,7 +8640,7 @@
         <v>681</v>
       </c>
       <c r="M19" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N19" s="30" t="s">
         <v>1</v>
@@ -8627,10 +8687,10 @@
         <v>343</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D20" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E20" s="54" t="s">
         <v>631</v>
@@ -8657,7 +8717,7 @@
         <v>681</v>
       </c>
       <c r="M20" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N20" s="30" t="s">
         <v>1</v>
@@ -8704,10 +8764,10 @@
         <v>344</v>
       </c>
       <c r="C21" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D21" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E21" s="54" t="s">
         <v>631</v>
@@ -8734,7 +8794,7 @@
         <v>681</v>
       </c>
       <c r="M21" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N21" s="30" t="s">
         <v>1</v>
@@ -8781,10 +8841,10 @@
         <v>345</v>
       </c>
       <c r="C22" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D22" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E22" s="54" t="s">
         <v>631</v>
@@ -8811,7 +8871,7 @@
         <v>681</v>
       </c>
       <c r="M22" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N22" s="30" t="s">
         <v>1</v>
@@ -8858,10 +8918,10 @@
         <v>346</v>
       </c>
       <c r="C23" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D23" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E23" s="54" t="s">
         <v>631</v>
@@ -8888,7 +8948,7 @@
         <v>681</v>
       </c>
       <c r="M23" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N23" s="30" t="s">
         <v>1</v>
@@ -8935,10 +8995,10 @@
         <v>347</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D24" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E24" s="54" t="s">
         <v>631</v>
@@ -8965,7 +9025,7 @@
         <v>681</v>
       </c>
       <c r="M24" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N24" s="30" t="s">
         <v>1</v>
@@ -9012,10 +9072,10 @@
         <v>348</v>
       </c>
       <c r="C25" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D25" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E25" s="54" t="s">
         <v>631</v>
@@ -9042,7 +9102,7 @@
         <v>681</v>
       </c>
       <c r="M25" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N25" s="30" t="s">
         <v>1</v>
@@ -9089,10 +9149,10 @@
         <v>349</v>
       </c>
       <c r="C26" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D26" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E26" s="54" t="s">
         <v>631</v>
@@ -9119,7 +9179,7 @@
         <v>681</v>
       </c>
       <c r="M26" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N26" s="30" t="s">
         <v>1</v>
@@ -9166,10 +9226,10 @@
         <v>350</v>
       </c>
       <c r="C27" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D27" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E27" s="54" t="s">
         <v>631</v>
@@ -9196,7 +9256,7 @@
         <v>681</v>
       </c>
       <c r="M27" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N27" s="30" t="s">
         <v>1</v>
@@ -9243,10 +9303,10 @@
         <v>351</v>
       </c>
       <c r="C28" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D28" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E28" s="54" t="s">
         <v>631</v>
@@ -9273,7 +9333,7 @@
         <v>681</v>
       </c>
       <c r="M28" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N28" s="30" t="s">
         <v>1</v>
@@ -9320,10 +9380,10 @@
         <v>352</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D29" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E29" s="54" t="s">
         <v>631</v>
@@ -9350,7 +9410,7 @@
         <v>681</v>
       </c>
       <c r="M29" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N29" s="30" t="s">
         <v>1</v>
@@ -9397,10 +9457,10 @@
         <v>353</v>
       </c>
       <c r="C30" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D30" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E30" s="54" t="s">
         <v>631</v>
@@ -9427,7 +9487,7 @@
         <v>681</v>
       </c>
       <c r="M30" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N30" s="30" t="s">
         <v>1</v>
@@ -9474,10 +9534,10 @@
         <v>354</v>
       </c>
       <c r="C31" s="12" t="s">
-        <v>812</v>
+        <v>779</v>
       </c>
       <c r="D31" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E31" s="54" t="s">
         <v>631</v>
@@ -9504,7 +9564,7 @@
         <v>681</v>
       </c>
       <c r="M31" s="33" t="s">
-        <v>761</v>
+        <v>728</v>
       </c>
       <c r="N31" s="30" t="s">
         <v>1</v>
@@ -9551,10 +9611,10 @@
         <v>355</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D32" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E32" s="54" t="s">
         <v>631</v>
@@ -9581,7 +9641,7 @@
         <v>681</v>
       </c>
       <c r="M32" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N32" s="30" t="s">
         <v>1</v>
@@ -9628,10 +9688,10 @@
         <v>356</v>
       </c>
       <c r="C33" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D33" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E33" s="54" t="s">
         <v>631</v>
@@ -9658,7 +9718,7 @@
         <v>681</v>
       </c>
       <c r="M33" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N33" s="30" t="s">
         <v>1</v>
@@ -9705,10 +9765,10 @@
         <v>357</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D34" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E34" s="54" t="s">
         <v>631</v>
@@ -9735,7 +9795,7 @@
         <v>681</v>
       </c>
       <c r="M34" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N34" s="30" t="s">
         <v>1</v>
@@ -9782,10 +9842,10 @@
         <v>358</v>
       </c>
       <c r="C35" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D35" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E35" s="54" t="s">
         <v>631</v>
@@ -9812,7 +9872,7 @@
         <v>681</v>
       </c>
       <c r="M35" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N35" s="30" t="s">
         <v>1</v>
@@ -9859,10 +9919,10 @@
         <v>359</v>
       </c>
       <c r="C36" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D36" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E36" s="54" t="s">
         <v>631</v>
@@ -9889,7 +9949,7 @@
         <v>681</v>
       </c>
       <c r="M36" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N36" s="30" t="s">
         <v>1</v>
@@ -9936,10 +9996,10 @@
         <v>360</v>
       </c>
       <c r="C37" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D37" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E37" s="54" t="s">
         <v>631</v>
@@ -9966,7 +10026,7 @@
         <v>681</v>
       </c>
       <c r="M37" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N37" s="30" t="s">
         <v>1</v>
@@ -10013,10 +10073,10 @@
         <v>361</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D38" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E38" s="54" t="s">
         <v>631</v>
@@ -10043,7 +10103,7 @@
         <v>681</v>
       </c>
       <c r="M38" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N38" s="30" t="s">
         <v>1</v>
@@ -10090,10 +10150,10 @@
         <v>362</v>
       </c>
       <c r="C39" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D39" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E39" s="54" t="s">
         <v>631</v>
@@ -10120,7 +10180,7 @@
         <v>681</v>
       </c>
       <c r="M39" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N39" s="30" t="s">
         <v>1</v>
@@ -10167,10 +10227,10 @@
         <v>363</v>
       </c>
       <c r="C40" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D40" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E40" s="54" t="s">
         <v>631</v>
@@ -10197,7 +10257,7 @@
         <v>681</v>
       </c>
       <c r="M40" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N40" s="30" t="s">
         <v>1</v>
@@ -10244,10 +10304,10 @@
         <v>364</v>
       </c>
       <c r="C41" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D41" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E41" s="54" t="s">
         <v>631</v>
@@ -10274,7 +10334,7 @@
         <v>681</v>
       </c>
       <c r="M41" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N41" s="30" t="s">
         <v>1</v>
@@ -10321,10 +10381,10 @@
         <v>365</v>
       </c>
       <c r="C42" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D42" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E42" s="54" t="s">
         <v>631</v>
@@ -10351,7 +10411,7 @@
         <v>681</v>
       </c>
       <c r="M42" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N42" s="30" t="s">
         <v>1</v>
@@ -10398,10 +10458,10 @@
         <v>366</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D43" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E43" s="54" t="s">
         <v>631</v>
@@ -10428,7 +10488,7 @@
         <v>681</v>
       </c>
       <c r="M43" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N43" s="30" t="s">
         <v>1</v>
@@ -10475,10 +10535,10 @@
         <v>367</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D44" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E44" s="54" t="s">
         <v>631</v>
@@ -10505,7 +10565,7 @@
         <v>681</v>
       </c>
       <c r="M44" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N44" s="30" t="s">
         <v>1</v>
@@ -10552,10 +10612,10 @@
         <v>702</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D45" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E45" s="54" t="s">
         <v>631</v>
@@ -10582,7 +10642,7 @@
         <v>681</v>
       </c>
       <c r="M45" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N45" s="30" t="s">
         <v>1</v>
@@ -10629,10 +10689,10 @@
         <v>368</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D46" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E46" s="54" t="s">
         <v>631</v>
@@ -10659,7 +10719,7 @@
         <v>681</v>
       </c>
       <c r="M46" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N46" s="30" t="s">
         <v>1</v>
@@ -10706,10 +10766,10 @@
         <v>703</v>
       </c>
       <c r="C47" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D47" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E47" s="54" t="s">
         <v>631</v>
@@ -10736,7 +10796,7 @@
         <v>681</v>
       </c>
       <c r="M47" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N47" s="30" t="s">
         <v>1</v>
@@ -10783,10 +10843,10 @@
         <v>369</v>
       </c>
       <c r="C48" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D48" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E48" s="54" t="s">
         <v>631</v>
@@ -10813,7 +10873,7 @@
         <v>681</v>
       </c>
       <c r="M48" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N48" s="30" t="s">
         <v>1</v>
@@ -10860,10 +10920,10 @@
         <v>370</v>
       </c>
       <c r="C49" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D49" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E49" s="54" t="s">
         <v>631</v>
@@ -10890,7 +10950,7 @@
         <v>681</v>
       </c>
       <c r="M49" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N49" s="30" t="s">
         <v>1</v>
@@ -10937,10 +10997,10 @@
         <v>371</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D50" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E50" s="54" t="s">
         <v>631</v>
@@ -10967,7 +11027,7 @@
         <v>681</v>
       </c>
       <c r="M50" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N50" s="30" t="s">
         <v>1</v>
@@ -11014,10 +11074,10 @@
         <v>372</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D51" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E51" s="54" t="s">
         <v>631</v>
@@ -11044,7 +11104,7 @@
         <v>681</v>
       </c>
       <c r="M51" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N51" s="30" t="s">
         <v>1</v>
@@ -11091,10 +11151,10 @@
         <v>373</v>
       </c>
       <c r="C52" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D52" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E52" s="54" t="s">
         <v>631</v>
@@ -11121,7 +11181,7 @@
         <v>681</v>
       </c>
       <c r="M52" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N52" s="30" t="s">
         <v>1</v>
@@ -11168,10 +11228,10 @@
         <v>701</v>
       </c>
       <c r="C53" s="12" t="s">
-        <v>813</v>
+        <v>780</v>
       </c>
       <c r="D53" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E53" s="54" t="s">
         <v>631</v>
@@ -11198,7 +11258,7 @@
         <v>681</v>
       </c>
       <c r="M53" s="33" t="s">
-        <v>762</v>
+        <v>729</v>
       </c>
       <c r="N53" s="30" t="s">
         <v>1</v>
@@ -11245,10 +11305,10 @@
         <v>374</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D54" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E54" s="54" t="s">
         <v>631</v>
@@ -11275,7 +11335,7 @@
         <v>681</v>
       </c>
       <c r="M54" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N54" s="30" t="s">
         <v>1</v>
@@ -11322,10 +11382,10 @@
         <v>375</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D55" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E55" s="54" t="s">
         <v>631</v>
@@ -11352,7 +11412,7 @@
         <v>681</v>
       </c>
       <c r="M55" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N55" s="30" t="s">
         <v>1</v>
@@ -11399,10 +11459,10 @@
         <v>376</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D56" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E56" s="54" t="s">
         <v>631</v>
@@ -11429,7 +11489,7 @@
         <v>681</v>
       </c>
       <c r="M56" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N56" s="30" t="s">
         <v>1</v>
@@ -11476,10 +11536,10 @@
         <v>377</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D57" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E57" s="54" t="s">
         <v>631</v>
@@ -11506,7 +11566,7 @@
         <v>681</v>
       </c>
       <c r="M57" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N57" s="30" t="s">
         <v>1</v>
@@ -11553,10 +11613,10 @@
         <v>378</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D58" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E58" s="54" t="s">
         <v>631</v>
@@ -11583,7 +11643,7 @@
         <v>681</v>
       </c>
       <c r="M58" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N58" s="30" t="s">
         <v>1</v>
@@ -11630,10 +11690,10 @@
         <v>379</v>
       </c>
       <c r="C59" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D59" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E59" s="54" t="s">
         <v>631</v>
@@ -11660,7 +11720,7 @@
         <v>681</v>
       </c>
       <c r="M59" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N59" s="30" t="s">
         <v>1</v>
@@ -11707,10 +11767,10 @@
         <v>380</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D60" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E60" s="54" t="s">
         <v>631</v>
@@ -11737,7 +11797,7 @@
         <v>681</v>
       </c>
       <c r="M60" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N60" s="30" t="s">
         <v>1</v>
@@ -11784,10 +11844,10 @@
         <v>381</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D61" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E61" s="54" t="s">
         <v>631</v>
@@ -11814,7 +11874,7 @@
         <v>681</v>
       </c>
       <c r="M61" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N61" s="30" t="s">
         <v>1</v>
@@ -11861,10 +11921,10 @@
         <v>382</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D62" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E62" s="54" t="s">
         <v>631</v>
@@ -11891,7 +11951,7 @@
         <v>681</v>
       </c>
       <c r="M62" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N62" s="30" t="s">
         <v>1</v>
@@ -11938,10 +11998,10 @@
         <v>383</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D63" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E63" s="54" t="s">
         <v>631</v>
@@ -11968,7 +12028,7 @@
         <v>681</v>
       </c>
       <c r="M63" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N63" s="30" t="s">
         <v>1</v>
@@ -12015,10 +12075,10 @@
         <v>384</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D64" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E64" s="54" t="s">
         <v>631</v>
@@ -12045,7 +12105,7 @@
         <v>681</v>
       </c>
       <c r="M64" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N64" s="30" t="s">
         <v>1</v>
@@ -12092,10 +12152,10 @@
         <v>385</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D65" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E65" s="54" t="s">
         <v>631</v>
@@ -12122,7 +12182,7 @@
         <v>681</v>
       </c>
       <c r="M65" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N65" s="30" t="s">
         <v>1</v>
@@ -12169,10 +12229,10 @@
         <v>386</v>
       </c>
       <c r="C66" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D66" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E66" s="54" t="s">
         <v>631</v>
@@ -12199,7 +12259,7 @@
         <v>681</v>
       </c>
       <c r="M66" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N66" s="30" t="s">
         <v>1</v>
@@ -12246,10 +12306,10 @@
         <v>387</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D67" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E67" s="54" t="s">
         <v>631</v>
@@ -12276,7 +12336,7 @@
         <v>681</v>
       </c>
       <c r="M67" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N67" s="30" t="s">
         <v>1</v>
@@ -12323,10 +12383,10 @@
         <v>388</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D68" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E68" s="54" t="s">
         <v>631</v>
@@ -12353,7 +12413,7 @@
         <v>681</v>
       </c>
       <c r="M68" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N68" s="30" t="s">
         <v>1</v>
@@ -12400,10 +12460,10 @@
         <v>389</v>
       </c>
       <c r="C69" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D69" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E69" s="54" t="s">
         <v>631</v>
@@ -12430,7 +12490,7 @@
         <v>681</v>
       </c>
       <c r="M69" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N69" s="30" t="s">
         <v>1</v>
@@ -12477,10 +12537,10 @@
         <v>390</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D70" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E70" s="54" t="s">
         <v>631</v>
@@ -12507,7 +12567,7 @@
         <v>681</v>
       </c>
       <c r="M70" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N70" s="30" t="s">
         <v>1</v>
@@ -12554,10 +12614,10 @@
         <v>391</v>
       </c>
       <c r="C71" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D71" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E71" s="54" t="s">
         <v>631</v>
@@ -12584,7 +12644,7 @@
         <v>681</v>
       </c>
       <c r="M71" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N71" s="30" t="s">
         <v>1</v>
@@ -12631,10 +12691,10 @@
         <v>392</v>
       </c>
       <c r="C72" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D72" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E72" s="54" t="s">
         <v>631</v>
@@ -12661,7 +12721,7 @@
         <v>681</v>
       </c>
       <c r="M72" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N72" s="30" t="s">
         <v>1</v>
@@ -12708,10 +12768,10 @@
         <v>393</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D73" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E73" s="54" t="s">
         <v>631</v>
@@ -12738,7 +12798,7 @@
         <v>681</v>
       </c>
       <c r="M73" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N73" s="30" t="s">
         <v>1</v>
@@ -12785,10 +12845,10 @@
         <v>394</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D74" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E74" s="54" t="s">
         <v>631</v>
@@ -12815,7 +12875,7 @@
         <v>681</v>
       </c>
       <c r="M74" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N74" s="30" t="s">
         <v>1</v>
@@ -12862,10 +12922,10 @@
         <v>395</v>
       </c>
       <c r="C75" s="12" t="s">
-        <v>814</v>
+        <v>781</v>
       </c>
       <c r="D75" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E75" s="54" t="s">
         <v>631</v>
@@ -12892,7 +12952,7 @@
         <v>681</v>
       </c>
       <c r="M75" s="33" t="s">
-        <v>763</v>
+        <v>730</v>
       </c>
       <c r="N75" s="30" t="s">
         <v>1</v>
@@ -12939,10 +12999,10 @@
         <v>396</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D76" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E76" s="54" t="s">
         <v>631</v>
@@ -12969,7 +13029,7 @@
         <v>681</v>
       </c>
       <c r="M76" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N76" s="30" t="s">
         <v>1</v>
@@ -13016,10 +13076,10 @@
         <v>397</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D77" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E77" s="54" t="s">
         <v>631</v>
@@ -13046,7 +13106,7 @@
         <v>681</v>
       </c>
       <c r="M77" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N77" s="30" t="s">
         <v>1</v>
@@ -13093,10 +13153,10 @@
         <v>398</v>
       </c>
       <c r="C78" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D78" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E78" s="54" t="s">
         <v>631</v>
@@ -13123,7 +13183,7 @@
         <v>681</v>
       </c>
       <c r="M78" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N78" s="30" t="s">
         <v>1</v>
@@ -13170,10 +13230,10 @@
         <v>399</v>
       </c>
       <c r="C79" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D79" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E79" s="54" t="s">
         <v>631</v>
@@ -13200,7 +13260,7 @@
         <v>681</v>
       </c>
       <c r="M79" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N79" s="30" t="s">
         <v>1</v>
@@ -13247,10 +13307,10 @@
         <v>400</v>
       </c>
       <c r="C80" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D80" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E80" s="54" t="s">
         <v>631</v>
@@ -13277,7 +13337,7 @@
         <v>681</v>
       </c>
       <c r="M80" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N80" s="30" t="s">
         <v>1</v>
@@ -13324,10 +13384,10 @@
         <v>401</v>
       </c>
       <c r="C81" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D81" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E81" s="54" t="s">
         <v>631</v>
@@ -13354,7 +13414,7 @@
         <v>681</v>
       </c>
       <c r="M81" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N81" s="30" t="s">
         <v>1</v>
@@ -13401,10 +13461,10 @@
         <v>402</v>
       </c>
       <c r="C82" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D82" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E82" s="54" t="s">
         <v>631</v>
@@ -13431,7 +13491,7 @@
         <v>681</v>
       </c>
       <c r="M82" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N82" s="30" t="s">
         <v>1</v>
@@ -13478,10 +13538,10 @@
         <v>403</v>
       </c>
       <c r="C83" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D83" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E83" s="54" t="s">
         <v>631</v>
@@ -13508,7 +13568,7 @@
         <v>681</v>
       </c>
       <c r="M83" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N83" s="30" t="s">
         <v>1</v>
@@ -13555,10 +13615,10 @@
         <v>404</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D84" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E84" s="54" t="s">
         <v>631</v>
@@ -13585,7 +13645,7 @@
         <v>681</v>
       </c>
       <c r="M84" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N84" s="30" t="s">
         <v>1</v>
@@ -13632,10 +13692,10 @@
         <v>405</v>
       </c>
       <c r="C85" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D85" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E85" s="54" t="s">
         <v>631</v>
@@ -13662,7 +13722,7 @@
         <v>681</v>
       </c>
       <c r="M85" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N85" s="30" t="s">
         <v>1</v>
@@ -13709,10 +13769,10 @@
         <v>406</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D86" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E86" s="54" t="s">
         <v>631</v>
@@ -13739,7 +13799,7 @@
         <v>681</v>
       </c>
       <c r="M86" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N86" s="30" t="s">
         <v>1</v>
@@ -13786,10 +13846,10 @@
         <v>407</v>
       </c>
       <c r="C87" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D87" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E87" s="54" t="s">
         <v>631</v>
@@ -13816,7 +13876,7 @@
         <v>681</v>
       </c>
       <c r="M87" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N87" s="30" t="s">
         <v>1</v>
@@ -13863,10 +13923,10 @@
         <v>408</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D88" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E88" s="54" t="s">
         <v>631</v>
@@ -13893,7 +13953,7 @@
         <v>681</v>
       </c>
       <c r="M88" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N88" s="30" t="s">
         <v>1</v>
@@ -13940,10 +14000,10 @@
         <v>409</v>
       </c>
       <c r="C89" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D89" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E89" s="54" t="s">
         <v>631</v>
@@ -13970,7 +14030,7 @@
         <v>681</v>
       </c>
       <c r="M89" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N89" s="30" t="s">
         <v>1</v>
@@ -14017,10 +14077,10 @@
         <v>410</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D90" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E90" s="54" t="s">
         <v>631</v>
@@ -14047,7 +14107,7 @@
         <v>681</v>
       </c>
       <c r="M90" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N90" s="30" t="s">
         <v>1</v>
@@ -14094,10 +14154,10 @@
         <v>411</v>
       </c>
       <c r="C91" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D91" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E91" s="54" t="s">
         <v>631</v>
@@ -14124,7 +14184,7 @@
         <v>681</v>
       </c>
       <c r="M91" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N91" s="30" t="s">
         <v>1</v>
@@ -14171,10 +14231,10 @@
         <v>412</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D92" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E92" s="54" t="s">
         <v>631</v>
@@ -14201,7 +14261,7 @@
         <v>681</v>
       </c>
       <c r="M92" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N92" s="30" t="s">
         <v>1</v>
@@ -14248,10 +14308,10 @@
         <v>413</v>
       </c>
       <c r="C93" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D93" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E93" s="54" t="s">
         <v>631</v>
@@ -14278,7 +14338,7 @@
         <v>681</v>
       </c>
       <c r="M93" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N93" s="30" t="s">
         <v>1</v>
@@ -14325,10 +14385,10 @@
         <v>414</v>
       </c>
       <c r="C94" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D94" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E94" s="54" t="s">
         <v>631</v>
@@ -14355,7 +14415,7 @@
         <v>681</v>
       </c>
       <c r="M94" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N94" s="30" t="s">
         <v>1</v>
@@ -14402,10 +14462,10 @@
         <v>415</v>
       </c>
       <c r="C95" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D95" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E95" s="54" t="s">
         <v>631</v>
@@ -14432,7 +14492,7 @@
         <v>681</v>
       </c>
       <c r="M95" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N95" s="30" t="s">
         <v>1</v>
@@ -14479,10 +14539,10 @@
         <v>416</v>
       </c>
       <c r="C96" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D96" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E96" s="54" t="s">
         <v>631</v>
@@ -14509,7 +14569,7 @@
         <v>681</v>
       </c>
       <c r="M96" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N96" s="30" t="s">
         <v>1</v>
@@ -14556,10 +14616,10 @@
         <v>417</v>
       </c>
       <c r="C97" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D97" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E97" s="54" t="s">
         <v>631</v>
@@ -14586,7 +14646,7 @@
         <v>681</v>
       </c>
       <c r="M97" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N97" s="30" t="s">
         <v>1</v>
@@ -14633,10 +14693,10 @@
         <v>418</v>
       </c>
       <c r="C98" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D98" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E98" s="54" t="s">
         <v>631</v>
@@ -14663,7 +14723,7 @@
         <v>681</v>
       </c>
       <c r="M98" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N98" s="30" t="s">
         <v>1</v>
@@ -14710,10 +14770,10 @@
         <v>419</v>
       </c>
       <c r="C99" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D99" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E99" s="54" t="s">
         <v>631</v>
@@ -14740,7 +14800,7 @@
         <v>681</v>
       </c>
       <c r="M99" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N99" s="30" t="s">
         <v>1</v>
@@ -14787,10 +14847,10 @@
         <v>420</v>
       </c>
       <c r="C100" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D100" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E100" s="54" t="s">
         <v>631</v>
@@ -14817,7 +14877,7 @@
         <v>681</v>
       </c>
       <c r="M100" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N100" s="30" t="s">
         <v>1</v>
@@ -14864,10 +14924,10 @@
         <v>421</v>
       </c>
       <c r="C101" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D101" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E101" s="54" t="s">
         <v>631</v>
@@ -14894,7 +14954,7 @@
         <v>681</v>
       </c>
       <c r="M101" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N101" s="30" t="s">
         <v>1</v>
@@ -14941,10 +15001,10 @@
         <v>422</v>
       </c>
       <c r="C102" s="12" t="s">
-        <v>815</v>
+        <v>782</v>
       </c>
       <c r="D102" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E102" s="54" t="s">
         <v>631</v>
@@ -14971,7 +15031,7 @@
         <v>681</v>
       </c>
       <c r="M102" s="33" t="s">
-        <v>764</v>
+        <v>731</v>
       </c>
       <c r="N102" s="30" t="s">
         <v>1</v>
@@ -15018,10 +15078,10 @@
         <v>423</v>
       </c>
       <c r="C103" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D103" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E103" s="54" t="s">
         <v>631</v>
@@ -15048,7 +15108,7 @@
         <v>681</v>
       </c>
       <c r="M103" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N103" s="30" t="s">
         <v>1</v>
@@ -15095,10 +15155,10 @@
         <v>424</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D104" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E104" s="54" t="s">
         <v>631</v>
@@ -15125,7 +15185,7 @@
         <v>681</v>
       </c>
       <c r="M104" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N104" s="30" t="s">
         <v>1</v>
@@ -15172,10 +15232,10 @@
         <v>425</v>
       </c>
       <c r="C105" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D105" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E105" s="54" t="s">
         <v>631</v>
@@ -15202,7 +15262,7 @@
         <v>681</v>
       </c>
       <c r="M105" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N105" s="30" t="s">
         <v>1</v>
@@ -15249,10 +15309,10 @@
         <v>426</v>
       </c>
       <c r="C106" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D106" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E106" s="54" t="s">
         <v>631</v>
@@ -15279,7 +15339,7 @@
         <v>681</v>
       </c>
       <c r="M106" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N106" s="30" t="s">
         <v>1</v>
@@ -15326,10 +15386,10 @@
         <v>427</v>
       </c>
       <c r="C107" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D107" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E107" s="54" t="s">
         <v>631</v>
@@ -15356,7 +15416,7 @@
         <v>681</v>
       </c>
       <c r="M107" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N107" s="30" t="s">
         <v>1</v>
@@ -15403,10 +15463,10 @@
         <v>428</v>
       </c>
       <c r="C108" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D108" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E108" s="54" t="s">
         <v>631</v>
@@ -15433,7 +15493,7 @@
         <v>681</v>
       </c>
       <c r="M108" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N108" s="30" t="s">
         <v>1</v>
@@ -15480,10 +15540,10 @@
         <v>429</v>
       </c>
       <c r="C109" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D109" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E109" s="54" t="s">
         <v>631</v>
@@ -15510,7 +15570,7 @@
         <v>681</v>
       </c>
       <c r="M109" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N109" s="30" t="s">
         <v>1</v>
@@ -15557,10 +15617,10 @@
         <v>430</v>
       </c>
       <c r="C110" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D110" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E110" s="54" t="s">
         <v>631</v>
@@ -15587,7 +15647,7 @@
         <v>681</v>
       </c>
       <c r="M110" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N110" s="30" t="s">
         <v>1</v>
@@ -15634,10 +15694,10 @@
         <v>431</v>
       </c>
       <c r="C111" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D111" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E111" s="54" t="s">
         <v>631</v>
@@ -15664,7 +15724,7 @@
         <v>681</v>
       </c>
       <c r="M111" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N111" s="30" t="s">
         <v>1</v>
@@ -15711,10 +15771,10 @@
         <v>432</v>
       </c>
       <c r="C112" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D112" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E112" s="54" t="s">
         <v>631</v>
@@ -15741,7 +15801,7 @@
         <v>681</v>
       </c>
       <c r="M112" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N112" s="30" t="s">
         <v>1</v>
@@ -15788,10 +15848,10 @@
         <v>433</v>
       </c>
       <c r="C113" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D113" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E113" s="54" t="s">
         <v>631</v>
@@ -15818,7 +15878,7 @@
         <v>681</v>
       </c>
       <c r="M113" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N113" s="30" t="s">
         <v>1</v>
@@ -15865,10 +15925,10 @@
         <v>434</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D114" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E114" s="54" t="s">
         <v>631</v>
@@ -15895,7 +15955,7 @@
         <v>681</v>
       </c>
       <c r="M114" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N114" s="30" t="s">
         <v>1</v>
@@ -15942,10 +16002,10 @@
         <v>435</v>
       </c>
       <c r="C115" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D115" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E115" s="54" t="s">
         <v>631</v>
@@ -15972,7 +16032,7 @@
         <v>681</v>
       </c>
       <c r="M115" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N115" s="30" t="s">
         <v>1</v>
@@ -16019,10 +16079,10 @@
         <v>436</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D116" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E116" s="54" t="s">
         <v>631</v>
@@ -16049,7 +16109,7 @@
         <v>681</v>
       </c>
       <c r="M116" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N116" s="30" t="s">
         <v>1</v>
@@ -16096,10 +16156,10 @@
         <v>437</v>
       </c>
       <c r="C117" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D117" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E117" s="54" t="s">
         <v>631</v>
@@ -16126,7 +16186,7 @@
         <v>681</v>
       </c>
       <c r="M117" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N117" s="30" t="s">
         <v>1</v>
@@ -16173,10 +16233,10 @@
         <v>438</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D118" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E118" s="54" t="s">
         <v>631</v>
@@ -16203,7 +16263,7 @@
         <v>681</v>
       </c>
       <c r="M118" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N118" s="30" t="s">
         <v>1</v>
@@ -16250,10 +16310,10 @@
         <v>439</v>
       </c>
       <c r="C119" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D119" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E119" s="54" t="s">
         <v>631</v>
@@ -16280,7 +16340,7 @@
         <v>681</v>
       </c>
       <c r="M119" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N119" s="30" t="s">
         <v>1</v>
@@ -16327,10 +16387,10 @@
         <v>440</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D120" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E120" s="54" t="s">
         <v>631</v>
@@ -16357,7 +16417,7 @@
         <v>681</v>
       </c>
       <c r="M120" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N120" s="30" t="s">
         <v>1</v>
@@ -16404,10 +16464,10 @@
         <v>700</v>
       </c>
       <c r="C121" s="12" t="s">
-        <v>816</v>
+        <v>783</v>
       </c>
       <c r="D121" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E121" s="54" t="s">
         <v>631</v>
@@ -16434,7 +16494,7 @@
         <v>681</v>
       </c>
       <c r="M121" s="33" t="s">
-        <v>765</v>
+        <v>732</v>
       </c>
       <c r="N121" s="30" t="s">
         <v>1</v>
@@ -16481,10 +16541,10 @@
         <v>441</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D122" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E122" s="54" t="s">
         <v>631</v>
@@ -16558,10 +16618,10 @@
         <v>442</v>
       </c>
       <c r="C123" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D123" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E123" s="54" t="s">
         <v>631</v>
@@ -16635,10 +16695,10 @@
         <v>443</v>
       </c>
       <c r="C124" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D124" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E124" s="54" t="s">
         <v>631</v>
@@ -16712,10 +16772,10 @@
         <v>444</v>
       </c>
       <c r="C125" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D125" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E125" s="54" t="s">
         <v>631</v>
@@ -16789,10 +16849,10 @@
         <v>445</v>
       </c>
       <c r="C126" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D126" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E126" s="54" t="s">
         <v>631</v>
@@ -16866,10 +16926,10 @@
         <v>446</v>
       </c>
       <c r="C127" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D127" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E127" s="54" t="s">
         <v>631</v>
@@ -16943,10 +17003,10 @@
         <v>447</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D128" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E128" s="54" t="s">
         <v>631</v>
@@ -17020,10 +17080,10 @@
         <v>448</v>
       </c>
       <c r="C129" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D129" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E129" s="54" t="s">
         <v>631</v>
@@ -17097,10 +17157,10 @@
         <v>449</v>
       </c>
       <c r="C130" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D130" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E130" s="54" t="s">
         <v>631</v>
@@ -17174,10 +17234,10 @@
         <v>450</v>
       </c>
       <c r="C131" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D131" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E131" s="54" t="s">
         <v>631</v>
@@ -17251,10 +17311,10 @@
         <v>451</v>
       </c>
       <c r="C132" s="12" t="s">
-        <v>817</v>
+        <v>784</v>
       </c>
       <c r="D132" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E132" s="54" t="s">
         <v>631</v>
@@ -17328,10 +17388,10 @@
         <v>452</v>
       </c>
       <c r="C133" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D133" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E133" s="54" t="s">
         <v>631</v>
@@ -17405,10 +17465,10 @@
         <v>453</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D134" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E134" s="54" t="s">
         <v>631</v>
@@ -17435,7 +17495,7 @@
         <v>681</v>
       </c>
       <c r="M134" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N134" s="30" t="s">
         <v>1</v>
@@ -17482,10 +17542,10 @@
         <v>454</v>
       </c>
       <c r="C135" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D135" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E135" s="54" t="s">
         <v>631</v>
@@ -17512,7 +17572,7 @@
         <v>681</v>
       </c>
       <c r="M135" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N135" s="30" t="s">
         <v>1</v>
@@ -17559,10 +17619,10 @@
         <v>455</v>
       </c>
       <c r="C136" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D136" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E136" s="54" t="s">
         <v>631</v>
@@ -17589,7 +17649,7 @@
         <v>681</v>
       </c>
       <c r="M136" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N136" s="30" t="s">
         <v>1</v>
@@ -17636,10 +17696,10 @@
         <v>456</v>
       </c>
       <c r="C137" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D137" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E137" s="54" t="s">
         <v>631</v>
@@ -17666,7 +17726,7 @@
         <v>681</v>
       </c>
       <c r="M137" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N137" s="30" t="s">
         <v>1</v>
@@ -17713,10 +17773,10 @@
         <v>457</v>
       </c>
       <c r="C138" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D138" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E138" s="54" t="s">
         <v>631</v>
@@ -17743,7 +17803,7 @@
         <v>681</v>
       </c>
       <c r="M138" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N138" s="30" t="s">
         <v>1</v>
@@ -17790,10 +17850,10 @@
         <v>458</v>
       </c>
       <c r="C139" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D139" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E139" s="54" t="s">
         <v>631</v>
@@ -17820,7 +17880,7 @@
         <v>681</v>
       </c>
       <c r="M139" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N139" s="30" t="s">
         <v>1</v>
@@ -17867,10 +17927,10 @@
         <v>459</v>
       </c>
       <c r="C140" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D140" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E140" s="54" t="s">
         <v>631</v>
@@ -17897,7 +17957,7 @@
         <v>681</v>
       </c>
       <c r="M140" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N140" s="30" t="s">
         <v>1</v>
@@ -17944,10 +18004,10 @@
         <v>460</v>
       </c>
       <c r="C141" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D141" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E141" s="54" t="s">
         <v>631</v>
@@ -17974,7 +18034,7 @@
         <v>681</v>
       </c>
       <c r="M141" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N141" s="30" t="s">
         <v>1</v>
@@ -18021,10 +18081,10 @@
         <v>461</v>
       </c>
       <c r="C142" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D142" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E142" s="54" t="s">
         <v>631</v>
@@ -18051,7 +18111,7 @@
         <v>681</v>
       </c>
       <c r="M142" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N142" s="30" t="s">
         <v>1</v>
@@ -18098,10 +18158,10 @@
         <v>462</v>
       </c>
       <c r="C143" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D143" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E143" s="54" t="s">
         <v>631</v>
@@ -18128,7 +18188,7 @@
         <v>681</v>
       </c>
       <c r="M143" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N143" s="30" t="s">
         <v>1</v>
@@ -18175,10 +18235,10 @@
         <v>463</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D144" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E144" s="54" t="s">
         <v>631</v>
@@ -18205,7 +18265,7 @@
         <v>681</v>
       </c>
       <c r="M144" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N144" s="30" t="s">
         <v>1</v>
@@ -18252,10 +18312,10 @@
         <v>464</v>
       </c>
       <c r="C145" s="12" t="s">
-        <v>818</v>
+        <v>785</v>
       </c>
       <c r="D145" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E145" s="54" t="s">
         <v>631</v>
@@ -18282,7 +18342,7 @@
         <v>681</v>
       </c>
       <c r="M145" s="33" t="s">
-        <v>766</v>
+        <v>733</v>
       </c>
       <c r="N145" s="30" t="s">
         <v>1</v>
@@ -18329,10 +18389,10 @@
         <v>465</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D146" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E146" s="54" t="s">
         <v>631</v>
@@ -18359,7 +18419,7 @@
         <v>681</v>
       </c>
       <c r="M146" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N146" s="30" t="s">
         <v>1</v>
@@ -18406,10 +18466,10 @@
         <v>466</v>
       </c>
       <c r="C147" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D147" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E147" s="54" t="s">
         <v>631</v>
@@ -18436,7 +18496,7 @@
         <v>681</v>
       </c>
       <c r="M147" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N147" s="30" t="s">
         <v>1</v>
@@ -18483,10 +18543,10 @@
         <v>467</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D148" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E148" s="54" t="s">
         <v>631</v>
@@ -18513,7 +18573,7 @@
         <v>681</v>
       </c>
       <c r="M148" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N148" s="30" t="s">
         <v>1</v>
@@ -18560,10 +18620,10 @@
         <v>468</v>
       </c>
       <c r="C149" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D149" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E149" s="54" t="s">
         <v>631</v>
@@ -18590,7 +18650,7 @@
         <v>681</v>
       </c>
       <c r="M149" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N149" s="30" t="s">
         <v>1</v>
@@ -18637,10 +18697,10 @@
         <v>469</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D150" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E150" s="54" t="s">
         <v>631</v>
@@ -18667,7 +18727,7 @@
         <v>681</v>
       </c>
       <c r="M150" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N150" s="30" t="s">
         <v>1</v>
@@ -18714,10 +18774,10 @@
         <v>470</v>
       </c>
       <c r="C151" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D151" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E151" s="54" t="s">
         <v>631</v>
@@ -18744,7 +18804,7 @@
         <v>681</v>
       </c>
       <c r="M151" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N151" s="30" t="s">
         <v>1</v>
@@ -18791,10 +18851,10 @@
         <v>471</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D152" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E152" s="54" t="s">
         <v>631</v>
@@ -18821,7 +18881,7 @@
         <v>681</v>
       </c>
       <c r="M152" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N152" s="30" t="s">
         <v>1</v>
@@ -18868,10 +18928,10 @@
         <v>472</v>
       </c>
       <c r="C153" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D153" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E153" s="54" t="s">
         <v>631</v>
@@ -18898,7 +18958,7 @@
         <v>681</v>
       </c>
       <c r="M153" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N153" s="30" t="s">
         <v>1</v>
@@ -18945,10 +19005,10 @@
         <v>473</v>
       </c>
       <c r="C154" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D154" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E154" s="54" t="s">
         <v>631</v>
@@ -18975,7 +19035,7 @@
         <v>681</v>
       </c>
       <c r="M154" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N154" s="30" t="s">
         <v>1</v>
@@ -19022,10 +19082,10 @@
         <v>474</v>
       </c>
       <c r="C155" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D155" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E155" s="54" t="s">
         <v>631</v>
@@ -19052,7 +19112,7 @@
         <v>681</v>
       </c>
       <c r="M155" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N155" s="30" t="s">
         <v>1</v>
@@ -19099,10 +19159,10 @@
         <v>475</v>
       </c>
       <c r="C156" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D156" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E156" s="54" t="s">
         <v>631</v>
@@ -19129,7 +19189,7 @@
         <v>681</v>
       </c>
       <c r="M156" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N156" s="30" t="s">
         <v>1</v>
@@ -19176,10 +19236,10 @@
         <v>476</v>
       </c>
       <c r="C157" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D157" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E157" s="54" t="s">
         <v>631</v>
@@ -19206,7 +19266,7 @@
         <v>681</v>
       </c>
       <c r="M157" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N157" s="30" t="s">
         <v>1</v>
@@ -19253,10 +19313,10 @@
         <v>477</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D158" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E158" s="54" t="s">
         <v>631</v>
@@ -19283,7 +19343,7 @@
         <v>681</v>
       </c>
       <c r="M158" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N158" s="30" t="s">
         <v>1</v>
@@ -19330,10 +19390,10 @@
         <v>478</v>
       </c>
       <c r="C159" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D159" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E159" s="54" t="s">
         <v>631</v>
@@ -19360,7 +19420,7 @@
         <v>681</v>
       </c>
       <c r="M159" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N159" s="30" t="s">
         <v>1</v>
@@ -19407,10 +19467,10 @@
         <v>479</v>
       </c>
       <c r="C160" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D160" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E160" s="54" t="s">
         <v>631</v>
@@ -19437,7 +19497,7 @@
         <v>681</v>
       </c>
       <c r="M160" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N160" s="30" t="s">
         <v>1</v>
@@ -19484,10 +19544,10 @@
         <v>480</v>
       </c>
       <c r="C161" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D161" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E161" s="54" t="s">
         <v>631</v>
@@ -19514,7 +19574,7 @@
         <v>681</v>
       </c>
       <c r="M161" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N161" s="30" t="s">
         <v>1</v>
@@ -19561,10 +19621,10 @@
         <v>481</v>
       </c>
       <c r="C162" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D162" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E162" s="54" t="s">
         <v>631</v>
@@ -19591,7 +19651,7 @@
         <v>681</v>
       </c>
       <c r="M162" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N162" s="30" t="s">
         <v>1</v>
@@ -19638,10 +19698,10 @@
         <v>482</v>
       </c>
       <c r="C163" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D163" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E163" s="54" t="s">
         <v>631</v>
@@ -19668,7 +19728,7 @@
         <v>681</v>
       </c>
       <c r="M163" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N163" s="30" t="s">
         <v>1</v>
@@ -19715,10 +19775,10 @@
         <v>483</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D164" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E164" s="54" t="s">
         <v>631</v>
@@ -19745,7 +19805,7 @@
         <v>681</v>
       </c>
       <c r="M164" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N164" s="30" t="s">
         <v>1</v>
@@ -19792,10 +19852,10 @@
         <v>484</v>
       </c>
       <c r="C165" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D165" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E165" s="54" t="s">
         <v>631</v>
@@ -19822,7 +19882,7 @@
         <v>681</v>
       </c>
       <c r="M165" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N165" s="30" t="s">
         <v>1</v>
@@ -19869,10 +19929,10 @@
         <v>485</v>
       </c>
       <c r="C166" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D166" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E166" s="54" t="s">
         <v>631</v>
@@ -19899,7 +19959,7 @@
         <v>681</v>
       </c>
       <c r="M166" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N166" s="30" t="s">
         <v>1</v>
@@ -19946,10 +20006,10 @@
         <v>486</v>
       </c>
       <c r="C167" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D167" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E167" s="54" t="s">
         <v>631</v>
@@ -19976,7 +20036,7 @@
         <v>681</v>
       </c>
       <c r="M167" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N167" s="30" t="s">
         <v>1</v>
@@ -20023,10 +20083,10 @@
         <v>487</v>
       </c>
       <c r="C168" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D168" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E168" s="54" t="s">
         <v>631</v>
@@ -20053,7 +20113,7 @@
         <v>681</v>
       </c>
       <c r="M168" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N168" s="30" t="s">
         <v>1</v>
@@ -20100,10 +20160,10 @@
         <v>488</v>
       </c>
       <c r="C169" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D169" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E169" s="54" t="s">
         <v>631</v>
@@ -20130,7 +20190,7 @@
         <v>681</v>
       </c>
       <c r="M169" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N169" s="30" t="s">
         <v>1</v>
@@ -20177,10 +20237,10 @@
         <v>489</v>
       </c>
       <c r="C170" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D170" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E170" s="54" t="s">
         <v>631</v>
@@ -20207,7 +20267,7 @@
         <v>681</v>
       </c>
       <c r="M170" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N170" s="30" t="s">
         <v>1</v>
@@ -20254,10 +20314,10 @@
         <v>490</v>
       </c>
       <c r="C171" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D171" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E171" s="54" t="s">
         <v>631</v>
@@ -20284,7 +20344,7 @@
         <v>681</v>
       </c>
       <c r="M171" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N171" s="30" t="s">
         <v>1</v>
@@ -20331,10 +20391,10 @@
         <v>491</v>
       </c>
       <c r="C172" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D172" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E172" s="54" t="s">
         <v>631</v>
@@ -20361,7 +20421,7 @@
         <v>681</v>
       </c>
       <c r="M172" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N172" s="30" t="s">
         <v>1</v>
@@ -20408,10 +20468,10 @@
         <v>492</v>
       </c>
       <c r="C173" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D173" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E173" s="54" t="s">
         <v>631</v>
@@ -20438,7 +20498,7 @@
         <v>681</v>
       </c>
       <c r="M173" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N173" s="30" t="s">
         <v>1</v>
@@ -20485,10 +20545,10 @@
         <v>493</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D174" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E174" s="54" t="s">
         <v>631</v>
@@ -20515,7 +20575,7 @@
         <v>681</v>
       </c>
       <c r="M174" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N174" s="30" t="s">
         <v>1</v>
@@ -20562,10 +20622,10 @@
         <v>494</v>
       </c>
       <c r="C175" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D175" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E175" s="54" t="s">
         <v>631</v>
@@ -20592,7 +20652,7 @@
         <v>681</v>
       </c>
       <c r="M175" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N175" s="30" t="s">
         <v>1</v>
@@ -20639,10 +20699,10 @@
         <v>495</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D176" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E176" s="54" t="s">
         <v>631</v>
@@ -20669,7 +20729,7 @@
         <v>681</v>
       </c>
       <c r="M176" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N176" s="30" t="s">
         <v>1</v>
@@ -20716,10 +20776,10 @@
         <v>496</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D177" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E177" s="54" t="s">
         <v>631</v>
@@ -20746,7 +20806,7 @@
         <v>681</v>
       </c>
       <c r="M177" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N177" s="30" t="s">
         <v>1</v>
@@ -20793,10 +20853,10 @@
         <v>497</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>819</v>
+        <v>786</v>
       </c>
       <c r="D178" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E178" s="54" t="s">
         <v>631</v>
@@ -20823,7 +20883,7 @@
         <v>681</v>
       </c>
       <c r="M178" s="33" t="s">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="N178" s="30" t="s">
         <v>1</v>
@@ -20870,10 +20930,10 @@
         <v>498</v>
       </c>
       <c r="C179" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D179" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E179" s="54" t="s">
         <v>631</v>
@@ -20900,7 +20960,7 @@
         <v>681</v>
       </c>
       <c r="M179" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N179" s="30" t="s">
         <v>1</v>
@@ -20947,10 +21007,10 @@
         <v>499</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D180" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E180" s="54" t="s">
         <v>631</v>
@@ -20977,7 +21037,7 @@
         <v>681</v>
       </c>
       <c r="M180" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N180" s="30" t="s">
         <v>1</v>
@@ -21024,10 +21084,10 @@
         <v>500</v>
       </c>
       <c r="C181" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D181" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E181" s="54" t="s">
         <v>631</v>
@@ -21054,7 +21114,7 @@
         <v>681</v>
       </c>
       <c r="M181" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N181" s="30" t="s">
         <v>1</v>
@@ -21101,10 +21161,10 @@
         <v>501</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D182" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E182" s="54" t="s">
         <v>631</v>
@@ -21131,7 +21191,7 @@
         <v>681</v>
       </c>
       <c r="M182" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N182" s="30" t="s">
         <v>1</v>
@@ -21178,10 +21238,10 @@
         <v>502</v>
       </c>
       <c r="C183" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D183" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E183" s="54" t="s">
         <v>631</v>
@@ -21208,7 +21268,7 @@
         <v>681</v>
       </c>
       <c r="M183" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N183" s="30" t="s">
         <v>1</v>
@@ -21255,10 +21315,10 @@
         <v>503</v>
       </c>
       <c r="C184" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D184" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E184" s="54" t="s">
         <v>631</v>
@@ -21285,7 +21345,7 @@
         <v>681</v>
       </c>
       <c r="M184" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N184" s="30" t="s">
         <v>1</v>
@@ -21332,10 +21392,10 @@
         <v>504</v>
       </c>
       <c r="C185" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D185" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E185" s="54" t="s">
         <v>631</v>
@@ -21362,7 +21422,7 @@
         <v>681</v>
       </c>
       <c r="M185" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N185" s="30" t="s">
         <v>1</v>
@@ -21409,10 +21469,10 @@
         <v>505</v>
       </c>
       <c r="C186" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D186" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E186" s="54" t="s">
         <v>631</v>
@@ -21439,7 +21499,7 @@
         <v>681</v>
       </c>
       <c r="M186" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N186" s="30" t="s">
         <v>1</v>
@@ -21486,10 +21546,10 @@
         <v>506</v>
       </c>
       <c r="C187" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D187" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E187" s="54" t="s">
         <v>631</v>
@@ -21516,7 +21576,7 @@
         <v>681</v>
       </c>
       <c r="M187" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N187" s="30" t="s">
         <v>1</v>
@@ -21563,10 +21623,10 @@
         <v>507</v>
       </c>
       <c r="C188" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D188" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E188" s="54" t="s">
         <v>631</v>
@@ -21593,7 +21653,7 @@
         <v>681</v>
       </c>
       <c r="M188" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N188" s="30" t="s">
         <v>1</v>
@@ -21640,10 +21700,10 @@
         <v>508</v>
       </c>
       <c r="C189" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D189" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E189" s="54" t="s">
         <v>631</v>
@@ -21670,7 +21730,7 @@
         <v>681</v>
       </c>
       <c r="M189" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N189" s="30" t="s">
         <v>1</v>
@@ -21717,10 +21777,10 @@
         <v>509</v>
       </c>
       <c r="C190" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D190" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E190" s="54" t="s">
         <v>631</v>
@@ -21747,7 +21807,7 @@
         <v>681</v>
       </c>
       <c r="M190" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N190" s="30" t="s">
         <v>1</v>
@@ -21794,10 +21854,10 @@
         <v>510</v>
       </c>
       <c r="C191" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D191" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E191" s="54" t="s">
         <v>631</v>
@@ -21824,7 +21884,7 @@
         <v>681</v>
       </c>
       <c r="M191" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N191" s="30" t="s">
         <v>1</v>
@@ -21871,10 +21931,10 @@
         <v>511</v>
       </c>
       <c r="C192" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D192" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E192" s="54" t="s">
         <v>631</v>
@@ -21901,7 +21961,7 @@
         <v>681</v>
       </c>
       <c r="M192" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N192" s="30" t="s">
         <v>1</v>
@@ -21948,10 +22008,10 @@
         <v>512</v>
       </c>
       <c r="C193" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D193" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E193" s="54" t="s">
         <v>631</v>
@@ -21978,7 +22038,7 @@
         <v>681</v>
       </c>
       <c r="M193" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N193" s="30" t="s">
         <v>1</v>
@@ -22025,10 +22085,10 @@
         <v>513</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D194" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E194" s="54" t="s">
         <v>631</v>
@@ -22055,7 +22115,7 @@
         <v>681</v>
       </c>
       <c r="M194" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N194" s="30" t="s">
         <v>1</v>
@@ -22102,10 +22162,10 @@
         <v>514</v>
       </c>
       <c r="C195" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D195" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E195" s="54" t="s">
         <v>631</v>
@@ -22132,7 +22192,7 @@
         <v>681</v>
       </c>
       <c r="M195" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N195" s="30" t="s">
         <v>1</v>
@@ -22179,10 +22239,10 @@
         <v>515</v>
       </c>
       <c r="C196" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D196" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E196" s="54" t="s">
         <v>631</v>
@@ -22209,7 +22269,7 @@
         <v>681</v>
       </c>
       <c r="M196" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N196" s="30" t="s">
         <v>1</v>
@@ -22256,10 +22316,10 @@
         <v>516</v>
       </c>
       <c r="C197" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D197" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E197" s="54" t="s">
         <v>631</v>
@@ -22286,7 +22346,7 @@
         <v>681</v>
       </c>
       <c r="M197" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N197" s="30" t="s">
         <v>1</v>
@@ -22333,10 +22393,10 @@
         <v>517</v>
       </c>
       <c r="C198" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D198" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E198" s="54" t="s">
         <v>631</v>
@@ -22363,7 +22423,7 @@
         <v>681</v>
       </c>
       <c r="M198" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N198" s="30" t="s">
         <v>1</v>
@@ -22410,10 +22470,10 @@
         <v>518</v>
       </c>
       <c r="C199" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D199" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E199" s="54" t="s">
         <v>631</v>
@@ -22440,7 +22500,7 @@
         <v>681</v>
       </c>
       <c r="M199" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N199" s="30" t="s">
         <v>1</v>
@@ -22487,10 +22547,10 @@
         <v>519</v>
       </c>
       <c r="C200" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D200" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E200" s="54" t="s">
         <v>631</v>
@@ -22517,7 +22577,7 @@
         <v>681</v>
       </c>
       <c r="M200" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N200" s="30" t="s">
         <v>1</v>
@@ -22564,10 +22624,10 @@
         <v>520</v>
       </c>
       <c r="C201" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D201" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E201" s="54" t="s">
         <v>631</v>
@@ -22594,7 +22654,7 @@
         <v>681</v>
       </c>
       <c r="M201" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N201" s="30" t="s">
         <v>1</v>
@@ -22641,10 +22701,10 @@
         <v>521</v>
       </c>
       <c r="C202" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D202" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E202" s="54" t="s">
         <v>631</v>
@@ -22671,7 +22731,7 @@
         <v>681</v>
       </c>
       <c r="M202" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N202" s="30" t="s">
         <v>1</v>
@@ -22718,10 +22778,10 @@
         <v>522</v>
       </c>
       <c r="C203" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D203" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E203" s="54" t="s">
         <v>631</v>
@@ -22748,7 +22808,7 @@
         <v>681</v>
       </c>
       <c r="M203" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N203" s="30" t="s">
         <v>1</v>
@@ -22795,10 +22855,10 @@
         <v>523</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D204" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E204" s="54" t="s">
         <v>631</v>
@@ -22825,7 +22885,7 @@
         <v>681</v>
       </c>
       <c r="M204" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N204" s="30" t="s">
         <v>1</v>
@@ -22872,10 +22932,10 @@
         <v>524</v>
       </c>
       <c r="C205" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D205" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E205" s="54" t="s">
         <v>631</v>
@@ -22902,7 +22962,7 @@
         <v>681</v>
       </c>
       <c r="M205" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N205" s="30" t="s">
         <v>1</v>
@@ -22949,10 +23009,10 @@
         <v>525</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D206" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E206" s="54" t="s">
         <v>631</v>
@@ -22979,7 +23039,7 @@
         <v>681</v>
       </c>
       <c r="M206" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N206" s="30" t="s">
         <v>1</v>
@@ -23026,10 +23086,10 @@
         <v>526</v>
       </c>
       <c r="C207" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D207" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E207" s="54" t="s">
         <v>631</v>
@@ -23056,7 +23116,7 @@
         <v>681</v>
       </c>
       <c r="M207" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N207" s="30" t="s">
         <v>1</v>
@@ -23103,10 +23163,10 @@
         <v>527</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D208" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E208" s="54" t="s">
         <v>631</v>
@@ -23133,7 +23193,7 @@
         <v>681</v>
       </c>
       <c r="M208" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N208" s="30" t="s">
         <v>1</v>
@@ -23180,10 +23240,10 @@
         <v>528</v>
       </c>
       <c r="C209" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D209" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E209" s="54" t="s">
         <v>631</v>
@@ -23210,7 +23270,7 @@
         <v>681</v>
       </c>
       <c r="M209" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N209" s="30" t="s">
         <v>1</v>
@@ -23257,10 +23317,10 @@
         <v>529</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D210" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E210" s="54" t="s">
         <v>631</v>
@@ -23287,7 +23347,7 @@
         <v>681</v>
       </c>
       <c r="M210" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N210" s="30" t="s">
         <v>1</v>
@@ -23334,10 +23394,10 @@
         <v>530</v>
       </c>
       <c r="C211" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D211" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E211" s="54" t="s">
         <v>631</v>
@@ -23364,7 +23424,7 @@
         <v>681</v>
       </c>
       <c r="M211" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N211" s="30" t="s">
         <v>1</v>
@@ -23411,10 +23471,10 @@
         <v>531</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D212" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E212" s="54" t="s">
         <v>631</v>
@@ -23441,7 +23501,7 @@
         <v>681</v>
       </c>
       <c r="M212" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N212" s="30" t="s">
         <v>1</v>
@@ -23488,10 +23548,10 @@
         <v>532</v>
       </c>
       <c r="C213" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D213" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E213" s="54" t="s">
         <v>631</v>
@@ -23518,7 +23578,7 @@
         <v>681</v>
       </c>
       <c r="M213" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N213" s="30" t="s">
         <v>1</v>
@@ -23565,10 +23625,10 @@
         <v>533</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D214" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E214" s="54" t="s">
         <v>631</v>
@@ -23595,7 +23655,7 @@
         <v>681</v>
       </c>
       <c r="M214" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N214" s="30" t="s">
         <v>1</v>
@@ -23642,10 +23702,10 @@
         <v>534</v>
       </c>
       <c r="C215" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D215" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E215" s="54" t="s">
         <v>631</v>
@@ -23672,7 +23732,7 @@
         <v>681</v>
       </c>
       <c r="M215" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N215" s="30" t="s">
         <v>1</v>
@@ -23719,10 +23779,10 @@
         <v>535</v>
       </c>
       <c r="C216" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D216" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E216" s="54" t="s">
         <v>631</v>
@@ -23749,7 +23809,7 @@
         <v>681</v>
       </c>
       <c r="M216" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N216" s="30" t="s">
         <v>1</v>
@@ -23796,10 +23856,10 @@
         <v>536</v>
       </c>
       <c r="C217" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D217" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E217" s="54" t="s">
         <v>631</v>
@@ -23826,7 +23886,7 @@
         <v>681</v>
       </c>
       <c r="M217" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N217" s="30" t="s">
         <v>1</v>
@@ -23873,10 +23933,10 @@
         <v>537</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D218" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E218" s="54" t="s">
         <v>631</v>
@@ -23903,7 +23963,7 @@
         <v>681</v>
       </c>
       <c r="M218" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N218" s="30" t="s">
         <v>1</v>
@@ -23950,10 +24010,10 @@
         <v>538</v>
       </c>
       <c r="C219" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D219" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E219" s="54" t="s">
         <v>631</v>
@@ -23980,7 +24040,7 @@
         <v>681</v>
       </c>
       <c r="M219" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N219" s="30" t="s">
         <v>1</v>
@@ -24027,10 +24087,10 @@
         <v>539</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D220" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E220" s="54" t="s">
         <v>631</v>
@@ -24057,7 +24117,7 @@
         <v>681</v>
       </c>
       <c r="M220" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N220" s="30" t="s">
         <v>1</v>
@@ -24104,10 +24164,10 @@
         <v>540</v>
       </c>
       <c r="C221" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D221" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E221" s="54" t="s">
         <v>631</v>
@@ -24134,7 +24194,7 @@
         <v>681</v>
       </c>
       <c r="M221" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N221" s="30" t="s">
         <v>1</v>
@@ -24181,10 +24241,10 @@
         <v>541</v>
       </c>
       <c r="C222" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D222" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E222" s="54" t="s">
         <v>631</v>
@@ -24211,7 +24271,7 @@
         <v>681</v>
       </c>
       <c r="M222" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N222" s="30" t="s">
         <v>1</v>
@@ -24258,10 +24318,10 @@
         <v>542</v>
       </c>
       <c r="C223" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D223" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E223" s="54" t="s">
         <v>631</v>
@@ -24288,7 +24348,7 @@
         <v>681</v>
       </c>
       <c r="M223" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N223" s="30" t="s">
         <v>1</v>
@@ -24335,10 +24395,10 @@
         <v>543</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D224" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E224" s="54" t="s">
         <v>631</v>
@@ -24365,7 +24425,7 @@
         <v>681</v>
       </c>
       <c r="M224" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N224" s="30" t="s">
         <v>1</v>
@@ -24412,10 +24472,10 @@
         <v>544</v>
       </c>
       <c r="C225" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D225" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E225" s="54" t="s">
         <v>631</v>
@@ -24442,7 +24502,7 @@
         <v>681</v>
       </c>
       <c r="M225" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N225" s="30" t="s">
         <v>1</v>
@@ -24489,10 +24549,10 @@
         <v>545</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D226" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E226" s="54" t="s">
         <v>631</v>
@@ -24519,7 +24579,7 @@
         <v>681</v>
       </c>
       <c r="M226" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N226" s="30" t="s">
         <v>1</v>
@@ -24566,10 +24626,10 @@
         <v>546</v>
       </c>
       <c r="C227" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D227" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E227" s="54" t="s">
         <v>631</v>
@@ -24596,7 +24656,7 @@
         <v>681</v>
       </c>
       <c r="M227" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N227" s="30" t="s">
         <v>1</v>
@@ -24643,10 +24703,10 @@
         <v>547</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D228" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E228" s="54" t="s">
         <v>631</v>
@@ -24673,7 +24733,7 @@
         <v>681</v>
       </c>
       <c r="M228" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N228" s="30" t="s">
         <v>1</v>
@@ -24720,10 +24780,10 @@
         <v>548</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D229" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E229" s="54" t="s">
         <v>631</v>
@@ -24750,7 +24810,7 @@
         <v>681</v>
       </c>
       <c r="M229" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N229" s="30" t="s">
         <v>1</v>
@@ -24797,10 +24857,10 @@
         <v>549</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D230" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E230" s="54" t="s">
         <v>631</v>
@@ -24827,7 +24887,7 @@
         <v>681</v>
       </c>
       <c r="M230" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N230" s="30" t="s">
         <v>1</v>
@@ -24874,10 +24934,10 @@
         <v>550</v>
       </c>
       <c r="C231" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D231" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E231" s="54" t="s">
         <v>631</v>
@@ -24904,7 +24964,7 @@
         <v>681</v>
       </c>
       <c r="M231" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N231" s="30" t="s">
         <v>1</v>
@@ -24951,10 +25011,10 @@
         <v>551</v>
       </c>
       <c r="C232" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D232" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E232" s="54" t="s">
         <v>631</v>
@@ -24981,7 +25041,7 @@
         <v>681</v>
       </c>
       <c r="M232" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N232" s="30" t="s">
         <v>1</v>
@@ -25028,10 +25088,10 @@
         <v>552</v>
       </c>
       <c r="C233" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D233" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E233" s="54" t="s">
         <v>631</v>
@@ -25058,7 +25118,7 @@
         <v>681</v>
       </c>
       <c r="M233" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N233" s="30" t="s">
         <v>1</v>
@@ -25105,10 +25165,10 @@
         <v>553</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D234" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E234" s="54" t="s">
         <v>631</v>
@@ -25135,7 +25195,7 @@
         <v>681</v>
       </c>
       <c r="M234" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N234" s="30" t="s">
         <v>1</v>
@@ -25182,10 +25242,10 @@
         <v>554</v>
       </c>
       <c r="C235" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D235" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E235" s="54" t="s">
         <v>631</v>
@@ -25212,7 +25272,7 @@
         <v>681</v>
       </c>
       <c r="M235" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N235" s="30" t="s">
         <v>1</v>
@@ -25259,10 +25319,10 @@
         <v>555</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D236" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E236" s="54" t="s">
         <v>631</v>
@@ -25289,7 +25349,7 @@
         <v>681</v>
       </c>
       <c r="M236" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N236" s="30" t="s">
         <v>1</v>
@@ -25336,10 +25396,10 @@
         <v>556</v>
       </c>
       <c r="C237" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D237" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E237" s="54" t="s">
         <v>631</v>
@@ -25366,7 +25426,7 @@
         <v>681</v>
       </c>
       <c r="M237" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N237" s="30" t="s">
         <v>1</v>
@@ -25413,10 +25473,10 @@
         <v>704</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D238" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E238" s="54" t="s">
         <v>631</v>
@@ -25443,7 +25503,7 @@
         <v>681</v>
       </c>
       <c r="M238" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N238" s="30" t="s">
         <v>1</v>
@@ -25490,10 +25550,10 @@
         <v>557</v>
       </c>
       <c r="C239" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D239" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E239" s="54" t="s">
         <v>631</v>
@@ -25520,7 +25580,7 @@
         <v>681</v>
       </c>
       <c r="M239" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N239" s="30" t="s">
         <v>1</v>
@@ -25567,10 +25627,10 @@
         <v>558</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D240" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E240" s="54" t="s">
         <v>631</v>
@@ -25597,7 +25657,7 @@
         <v>681</v>
       </c>
       <c r="M240" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N240" s="30" t="s">
         <v>1</v>
@@ -25644,10 +25704,10 @@
         <v>559</v>
       </c>
       <c r="C241" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D241" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E241" s="54" t="s">
         <v>631</v>
@@ -25674,7 +25734,7 @@
         <v>681</v>
       </c>
       <c r="M241" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N241" s="30" t="s">
         <v>1</v>
@@ -25721,10 +25781,10 @@
         <v>560</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D242" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E242" s="54" t="s">
         <v>631</v>
@@ -25751,7 +25811,7 @@
         <v>681</v>
       </c>
       <c r="M242" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N242" s="30" t="s">
         <v>1</v>
@@ -25798,10 +25858,10 @@
         <v>561</v>
       </c>
       <c r="C243" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D243" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E243" s="54" t="s">
         <v>631</v>
@@ -25828,7 +25888,7 @@
         <v>681</v>
       </c>
       <c r="M243" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N243" s="30" t="s">
         <v>1</v>
@@ -25875,10 +25935,10 @@
         <v>562</v>
       </c>
       <c r="C244" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D244" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E244" s="54" t="s">
         <v>631</v>
@@ -25905,7 +25965,7 @@
         <v>681</v>
       </c>
       <c r="M244" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N244" s="30" t="s">
         <v>1</v>
@@ -25952,10 +26012,10 @@
         <v>563</v>
       </c>
       <c r="C245" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D245" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E245" s="54" t="s">
         <v>631</v>
@@ -25982,7 +26042,7 @@
         <v>681</v>
       </c>
       <c r="M245" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N245" s="30" t="s">
         <v>1</v>
@@ -26029,10 +26089,10 @@
         <v>564</v>
       </c>
       <c r="C246" s="12" t="s">
-        <v>820</v>
+        <v>787</v>
       </c>
       <c r="D246" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E246" s="54" t="s">
         <v>631</v>
@@ -26059,7 +26119,7 @@
         <v>681</v>
       </c>
       <c r="M246" s="33" t="s">
-        <v>768</v>
+        <v>735</v>
       </c>
       <c r="N246" s="30" t="s">
         <v>1</v>
@@ -26106,10 +26166,10 @@
         <v>565</v>
       </c>
       <c r="C247" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D247" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E247" s="54" t="s">
         <v>631</v>
@@ -26136,7 +26196,7 @@
         <v>681</v>
       </c>
       <c r="M247" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N247" s="30" t="s">
         <v>1</v>
@@ -26183,10 +26243,10 @@
         <v>566</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D248" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E248" s="54" t="s">
         <v>631</v>
@@ -26213,7 +26273,7 @@
         <v>681</v>
       </c>
       <c r="M248" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N248" s="30" t="s">
         <v>1</v>
@@ -26260,10 +26320,10 @@
         <v>567</v>
       </c>
       <c r="C249" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D249" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E249" s="54" t="s">
         <v>631</v>
@@ -26290,7 +26350,7 @@
         <v>681</v>
       </c>
       <c r="M249" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N249" s="30" t="s">
         <v>1</v>
@@ -26337,10 +26397,10 @@
         <v>568</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D250" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E250" s="54" t="s">
         <v>631</v>
@@ -26367,7 +26427,7 @@
         <v>681</v>
       </c>
       <c r="M250" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N250" s="30" t="s">
         <v>1</v>
@@ -26414,10 +26474,10 @@
         <v>569</v>
       </c>
       <c r="C251" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D251" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E251" s="54" t="s">
         <v>631</v>
@@ -26444,7 +26504,7 @@
         <v>681</v>
       </c>
       <c r="M251" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N251" s="30" t="s">
         <v>1</v>
@@ -26491,10 +26551,10 @@
         <v>570</v>
       </c>
       <c r="C252" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D252" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E252" s="54" t="s">
         <v>631</v>
@@ -26521,7 +26581,7 @@
         <v>681</v>
       </c>
       <c r="M252" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N252" s="30" t="s">
         <v>1</v>
@@ -26568,10 +26628,10 @@
         <v>571</v>
       </c>
       <c r="C253" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D253" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E253" s="54" t="s">
         <v>631</v>
@@ -26598,7 +26658,7 @@
         <v>681</v>
       </c>
       <c r="M253" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N253" s="30" t="s">
         <v>1</v>
@@ -26645,10 +26705,10 @@
         <v>572</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D254" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E254" s="54" t="s">
         <v>631</v>
@@ -26675,7 +26735,7 @@
         <v>681</v>
       </c>
       <c r="M254" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N254" s="30" t="s">
         <v>1</v>
@@ -26722,10 +26782,10 @@
         <v>573</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D255" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E255" s="54" t="s">
         <v>631</v>
@@ -26752,7 +26812,7 @@
         <v>681</v>
       </c>
       <c r="M255" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N255" s="30" t="s">
         <v>1</v>
@@ -26799,10 +26859,10 @@
         <v>574</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D256" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E256" s="54" t="s">
         <v>631</v>
@@ -26829,7 +26889,7 @@
         <v>681</v>
       </c>
       <c r="M256" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N256" s="30" t="s">
         <v>1</v>
@@ -26876,10 +26936,10 @@
         <v>575</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D257" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E257" s="54" t="s">
         <v>631</v>
@@ -26906,7 +26966,7 @@
         <v>681</v>
       </c>
       <c r="M257" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N257" s="30" t="s">
         <v>1</v>
@@ -26953,10 +27013,10 @@
         <v>576</v>
       </c>
       <c r="C258" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D258" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E258" s="54" t="s">
         <v>631</v>
@@ -26983,7 +27043,7 @@
         <v>681</v>
       </c>
       <c r="M258" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N258" s="30" t="s">
         <v>1</v>
@@ -27030,10 +27090,10 @@
         <v>577</v>
       </c>
       <c r="C259" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D259" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E259" s="54" t="s">
         <v>631</v>
@@ -27060,7 +27120,7 @@
         <v>681</v>
       </c>
       <c r="M259" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N259" s="30" t="s">
         <v>1</v>
@@ -27107,10 +27167,10 @@
         <v>578</v>
       </c>
       <c r="C260" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D260" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E260" s="54" t="s">
         <v>631</v>
@@ -27137,7 +27197,7 @@
         <v>681</v>
       </c>
       <c r="M260" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N260" s="30" t="s">
         <v>1</v>
@@ -27184,10 +27244,10 @@
         <v>579</v>
       </c>
       <c r="C261" s="12" t="s">
-        <v>821</v>
+        <v>788</v>
       </c>
       <c r="D261" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E261" s="54" t="s">
         <v>631</v>
@@ -27214,7 +27274,7 @@
         <v>681</v>
       </c>
       <c r="M261" s="33" t="s">
-        <v>769</v>
+        <v>736</v>
       </c>
       <c r="N261" s="30" t="s">
         <v>1</v>
@@ -27261,10 +27321,10 @@
         <v>580</v>
       </c>
       <c r="C262" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D262" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E262" s="54" t="s">
         <v>631</v>
@@ -27338,10 +27398,10 @@
         <v>581</v>
       </c>
       <c r="C263" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D263" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E263" s="54" t="s">
         <v>631</v>
@@ -27415,10 +27475,10 @@
         <v>582</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D264" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E264" s="54" t="s">
         <v>631</v>
@@ -27492,10 +27552,10 @@
         <v>583</v>
       </c>
       <c r="C265" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D265" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E265" s="54" t="s">
         <v>631</v>
@@ -27569,10 +27629,10 @@
         <v>584</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D266" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E266" s="54" t="s">
         <v>631</v>
@@ -27646,10 +27706,10 @@
         <v>585</v>
       </c>
       <c r="C267" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D267" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E267" s="54" t="s">
         <v>631</v>
@@ -27723,10 +27783,10 @@
         <v>586</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D268" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E268" s="54" t="s">
         <v>631</v>
@@ -27800,10 +27860,10 @@
         <v>587</v>
       </c>
       <c r="C269" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D269" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E269" s="54" t="s">
         <v>631</v>
@@ -27877,10 +27937,10 @@
         <v>588</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D270" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E270" s="54" t="s">
         <v>631</v>
@@ -27954,10 +28014,10 @@
         <v>589</v>
       </c>
       <c r="C271" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D271" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E271" s="54" t="s">
         <v>631</v>
@@ -28031,10 +28091,10 @@
         <v>590</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D272" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E272" s="54" t="s">
         <v>631</v>
@@ -28108,10 +28168,10 @@
         <v>591</v>
       </c>
       <c r="C273" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D273" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E273" s="54" t="s">
         <v>631</v>
@@ -28185,10 +28245,10 @@
         <v>592</v>
       </c>
       <c r="C274" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D274" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E274" s="54" t="s">
         <v>631</v>
@@ -28262,10 +28322,10 @@
         <v>593</v>
       </c>
       <c r="C275" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D275" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E275" s="54" t="s">
         <v>631</v>
@@ -28339,10 +28399,10 @@
         <v>594</v>
       </c>
       <c r="C276" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D276" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E276" s="54" t="s">
         <v>631</v>
@@ -28416,10 +28476,10 @@
         <v>595</v>
       </c>
       <c r="C277" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D277" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E277" s="54" t="s">
         <v>631</v>
@@ -28493,10 +28553,10 @@
         <v>596</v>
       </c>
       <c r="C278" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D278" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E278" s="54" t="s">
         <v>631</v>
@@ -28570,10 +28630,10 @@
         <v>597</v>
       </c>
       <c r="C279" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D279" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E279" s="54" t="s">
         <v>631</v>
@@ -28647,10 +28707,10 @@
         <v>598</v>
       </c>
       <c r="C280" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D280" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E280" s="54" t="s">
         <v>631</v>
@@ -28724,10 +28784,10 @@
         <v>599</v>
       </c>
       <c r="C281" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D281" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E281" s="54" t="s">
         <v>631</v>
@@ -28801,10 +28861,10 @@
         <v>600</v>
       </c>
       <c r="C282" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D282" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E282" s="54" t="s">
         <v>631</v>
@@ -28878,10 +28938,10 @@
         <v>601</v>
       </c>
       <c r="C283" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D283" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E283" s="54" t="s">
         <v>631</v>
@@ -28955,10 +29015,10 @@
         <v>602</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D284" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E284" s="54" t="s">
         <v>631</v>
@@ -29032,10 +29092,10 @@
         <v>603</v>
       </c>
       <c r="C285" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D285" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E285" s="54" t="s">
         <v>631</v>
@@ -29109,10 +29169,10 @@
         <v>604</v>
       </c>
       <c r="C286" s="12" t="s">
-        <v>822</v>
+        <v>789</v>
       </c>
       <c r="D286" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E286" s="54" t="s">
         <v>631</v>
@@ -29186,10 +29246,10 @@
         <v>605</v>
       </c>
       <c r="C287" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D287" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E287" s="54" t="s">
         <v>631</v>
@@ -29216,7 +29276,7 @@
         <v>681</v>
       </c>
       <c r="M287" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N287" s="30" t="s">
         <v>1</v>
@@ -29263,10 +29323,10 @@
         <v>606</v>
       </c>
       <c r="C288" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D288" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E288" s="54" t="s">
         <v>631</v>
@@ -29293,7 +29353,7 @@
         <v>681</v>
       </c>
       <c r="M288" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N288" s="30" t="s">
         <v>1</v>
@@ -29340,10 +29400,10 @@
         <v>607</v>
       </c>
       <c r="C289" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D289" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E289" s="54" t="s">
         <v>631</v>
@@ -29370,7 +29430,7 @@
         <v>681</v>
       </c>
       <c r="M289" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N289" s="30" t="s">
         <v>1</v>
@@ -29417,10 +29477,10 @@
         <v>608</v>
       </c>
       <c r="C290" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D290" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E290" s="54" t="s">
         <v>631</v>
@@ -29447,7 +29507,7 @@
         <v>681</v>
       </c>
       <c r="M290" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N290" s="30" t="s">
         <v>1</v>
@@ -29494,10 +29554,10 @@
         <v>609</v>
       </c>
       <c r="C291" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D291" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E291" s="54" t="s">
         <v>631</v>
@@ -29524,7 +29584,7 @@
         <v>681</v>
       </c>
       <c r="M291" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N291" s="30" t="s">
         <v>1</v>
@@ -29571,10 +29631,10 @@
         <v>610</v>
       </c>
       <c r="C292" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D292" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E292" s="54" t="s">
         <v>631</v>
@@ -29601,7 +29661,7 @@
         <v>681</v>
       </c>
       <c r="M292" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N292" s="30" t="s">
         <v>1</v>
@@ -29648,10 +29708,10 @@
         <v>611</v>
       </c>
       <c r="C293" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D293" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E293" s="54" t="s">
         <v>631</v>
@@ -29678,7 +29738,7 @@
         <v>681</v>
       </c>
       <c r="M293" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N293" s="30" t="s">
         <v>1</v>
@@ -29725,10 +29785,10 @@
         <v>612</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D294" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E294" s="54" t="s">
         <v>631</v>
@@ -29755,7 +29815,7 @@
         <v>681</v>
       </c>
       <c r="M294" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N294" s="30" t="s">
         <v>1</v>
@@ -29802,10 +29862,10 @@
         <v>613</v>
       </c>
       <c r="C295" s="12" t="s">
-        <v>823</v>
+        <v>790</v>
       </c>
       <c r="D295" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E295" s="54" t="s">
         <v>631</v>
@@ -29832,7 +29892,7 @@
         <v>681</v>
       </c>
       <c r="M295" s="33" t="s">
-        <v>770</v>
+        <v>737</v>
       </c>
       <c r="N295" s="30" t="s">
         <v>1</v>
@@ -29879,10 +29939,10 @@
         <v>614</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D296" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E296" s="54" t="s">
         <v>631</v>
@@ -29909,7 +29969,7 @@
         <v>681</v>
       </c>
       <c r="M296" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N296" s="30" t="s">
         <v>1</v>
@@ -29956,10 +30016,10 @@
         <v>615</v>
       </c>
       <c r="C297" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D297" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E297" s="54" t="s">
         <v>631</v>
@@ -29986,7 +30046,7 @@
         <v>681</v>
       </c>
       <c r="M297" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N297" s="30" t="s">
         <v>1</v>
@@ -30033,10 +30093,10 @@
         <v>616</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D298" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E298" s="54" t="s">
         <v>631</v>
@@ -30063,7 +30123,7 @@
         <v>681</v>
       </c>
       <c r="M298" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N298" s="30" t="s">
         <v>1</v>
@@ -30110,10 +30170,10 @@
         <v>617</v>
       </c>
       <c r="C299" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D299" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E299" s="54" t="s">
         <v>631</v>
@@ -30140,7 +30200,7 @@
         <v>681</v>
       </c>
       <c r="M299" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N299" s="30" t="s">
         <v>1</v>
@@ -30187,10 +30247,10 @@
         <v>618</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D300" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E300" s="54" t="s">
         <v>631</v>
@@ -30217,7 +30277,7 @@
         <v>681</v>
       </c>
       <c r="M300" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N300" s="30" t="s">
         <v>1</v>
@@ -30264,10 +30324,10 @@
         <v>619</v>
       </c>
       <c r="C301" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D301" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E301" s="54" t="s">
         <v>631</v>
@@ -30294,7 +30354,7 @@
         <v>681</v>
       </c>
       <c r="M301" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N301" s="30" t="s">
         <v>1</v>
@@ -30341,10 +30401,10 @@
         <v>620</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D302" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E302" s="54" t="s">
         <v>631</v>
@@ -30371,7 +30431,7 @@
         <v>681</v>
       </c>
       <c r="M302" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N302" s="30" t="s">
         <v>1</v>
@@ -30418,10 +30478,10 @@
         <v>621</v>
       </c>
       <c r="C303" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D303" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E303" s="54" t="s">
         <v>631</v>
@@ -30448,7 +30508,7 @@
         <v>681</v>
       </c>
       <c r="M303" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N303" s="30" t="s">
         <v>1</v>
@@ -30495,10 +30555,10 @@
         <v>622</v>
       </c>
       <c r="C304" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D304" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E304" s="54" t="s">
         <v>631</v>
@@ -30525,7 +30585,7 @@
         <v>681</v>
       </c>
       <c r="M304" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N304" s="30" t="s">
         <v>1</v>
@@ -30572,10 +30632,10 @@
         <v>623</v>
       </c>
       <c r="C305" s="12" t="s">
-        <v>824</v>
+        <v>791</v>
       </c>
       <c r="D305" s="53" t="s">
-        <v>760</v>
+        <v>727</v>
       </c>
       <c r="E305" s="54" t="s">
         <v>631</v>
@@ -30602,7 +30662,7 @@
         <v>681</v>
       </c>
       <c r="M305" s="33" t="s">
-        <v>771</v>
+        <v>738</v>
       </c>
       <c r="N305" s="30" t="s">
         <v>1</v>
@@ -30644,60 +30704,60 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D752DB79-92D0-46CD-83AA-BA4D25B97595}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7DC0F-E610-4753-AAB9-2022B23E5F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="1" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7991" uniqueCount="846">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8030" uniqueCount="872">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2629,13 +2629,91 @@
   </si>
   <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 5I. Building Information Codes.</t>
+  </si>
+  <si>
+    <t>Fonte1</t>
+  </si>
+  <si>
+    <t>https://brasil.un.org/pt-br/sdgs</t>
+  </si>
+  <si>
+    <t>Fonte2</t>
+  </si>
+  <si>
+    <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
+  </si>
+  <si>
+    <t>Fonte3</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
+  </si>
+  <si>
+    <t>FonteVegetação1</t>
+  </si>
+  <si>
+    <t>https://museunacional.ufrj.br/hortobotanico</t>
+  </si>
+  <si>
+    <t>FonteVegetação2</t>
+  </si>
+  <si>
+    <t>https://www.embrapa.br/florestas/publicacoes</t>
+  </si>
+  <si>
+    <t>FonteVegetação3</t>
+  </si>
+  <si>
+    <t>https://www.arvoresgigantes.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação4</t>
+  </si>
+  <si>
+    <t>https://www.scielo.br/j/abb</t>
+  </si>
+  <si>
+    <t>FonteVegetação5</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/inpa/pt-br/Pesquisa/colecoes/botanica</t>
+  </si>
+  <si>
+    <t>FonteVegetação6</t>
+  </si>
+  <si>
+    <t>https://botanicasaopaulo.org</t>
+  </si>
+  <si>
+    <t>FonteVegetação7</t>
+  </si>
+  <si>
+    <t>https://pesquisa.in.gov.br/imprensa</t>
+  </si>
+  <si>
+    <t>FonteVegetação8</t>
+  </si>
+  <si>
+    <t>https://mapas.florestal.gov.br</t>
+  </si>
+  <si>
+    <t>FonteTSB</t>
+  </si>
+  <si>
+    <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
+  </si>
+  <si>
+    <t>FonteSINAPI</t>
+  </si>
+  <si>
+    <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="8"/>
       <color theme="1"/>
@@ -2723,8 +2801,34 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="6"/>
+      <color theme="10"/>
+      <name val="Arial Nova Cond Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="27">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2881,6 +2985,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -2943,11 +3053,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3113,38 +3224,30 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="17" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
+    <cellStyle name="Hiperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{75D7255F-4B16-4C61-A12B-6DBA4ACA1970}"/>
   </cellStyles>
-  <dxfs count="27">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="25">
     <dxf>
       <font>
         <b val="0"/>
@@ -3266,6 +3369,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3691,7 +3804,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33CFA2BD-3953-447B-BF8D-35BA528839AD}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C39"/>
   <sheetFormatPr defaultRowHeight="9" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.69921875" bestFit="1" customWidth="1"/>
@@ -3894,7 +4007,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46232.781416087964</v>
+        <v>46233.479224189818</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
@@ -3990,7 +4103,157 @@
         <v>691</v>
       </c>
     </row>
+    <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="36" t="s">
+        <v>846</v>
+      </c>
+      <c r="B27" s="57" t="s">
+        <v>847</v>
+      </c>
+      <c r="C27" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="36" t="s">
+        <v>848</v>
+      </c>
+      <c r="B28" s="58" t="s">
+        <v>849</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="36" t="s">
+        <v>850</v>
+      </c>
+      <c r="B29" s="58" t="s">
+        <v>851</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="36" t="s">
+        <v>852</v>
+      </c>
+      <c r="B30" s="6" t="s">
+        <v>853</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="36" t="s">
+        <v>854</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>855</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="36" t="s">
+        <v>856</v>
+      </c>
+      <c r="B32" s="6" t="s">
+        <v>857</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="36" t="s">
+        <v>858</v>
+      </c>
+      <c r="B33" s="60" t="s">
+        <v>859</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="36" t="s">
+        <v>860</v>
+      </c>
+      <c r="B34" s="60" t="s">
+        <v>861</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="36" t="s">
+        <v>862</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>863</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="36" t="s">
+        <v>864</v>
+      </c>
+      <c r="B36" s="60" t="s">
+        <v>865</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="36" t="s">
+        <v>866</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>867</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="B38" s="61" t="s">
+        <v>869</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="63" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="36" t="s">
+        <v>870</v>
+      </c>
+      <c r="B39" s="62" t="s">
+        <v>871</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>689</v>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{9BF71058-C383-44BC-A74B-ECE963D64DA6}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{5A982D2F-07F6-452C-A1A5-6F1E4BE3C3B7}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{7178BAF0-2889-4AE8-A340-43020EF117B5}"/>
+    <hyperlink ref="B38" r:id="rId4" xr:uid="{81A486FE-DA42-427E-98D3-B95ADB1E2290}"/>
+    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{0DF7099B-0B78-4FE6-B5A6-DEA2F02693C0}"/>
+  </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
@@ -5787,7 +6050,7 @@
         <v>321</v>
       </c>
       <c r="L20" s="50" t="str">
-        <f t="shared" ref="L18:N32" si="8">CONCATENATE("", C20)</f>
+        <f t="shared" ref="L20:N32" si="8">CONCATENATE("", C20)</f>
         <v>Normativo</v>
       </c>
       <c r="M20" s="50" t="str">
@@ -5799,7 +6062,7 @@
         <v>NBR.Serviços</v>
       </c>
       <c r="O20" s="50" t="str">
-        <f t="shared" ref="O7:O32" si="9">F20</f>
+        <f t="shared" ref="O20:O32" si="9">F20</f>
         <v>NBR.S.Transacional</v>
       </c>
       <c r="P20" s="35" t="s">
@@ -5813,7 +6076,7 @@
         <v>321</v>
       </c>
       <c r="S20" s="51" t="str">
-        <f t="shared" ref="S7:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
+        <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
         <v>Normativo</v>
       </c>
       <c r="T20" s="51" t="str">
@@ -6962,38 +7225,28 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A2:B6 A20:B32">
-    <cfRule type="cellIs" dxfId="26" priority="9" operator="equal">
+  <conditionalFormatting sqref="A2:B32">
+    <cfRule type="cellIs" dxfId="24" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F6">
-    <cfRule type="duplicateValues" dxfId="25" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="7"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7:F19">
+    <cfRule type="duplicateValues" dxfId="19" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="21" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="31"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA6 AA20:AA32">
-    <cfRule type="cellIs" dxfId="17" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A7:B19">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7:F19">
-    <cfRule type="duplicateValues" dxfId="1" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AA7:AA19">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+  <conditionalFormatting sqref="AA1:AA32">
+    <cfRule type="cellIs" dxfId="14" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7143,7 +7396,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:U2">
-    <cfRule type="cellIs" dxfId="16" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -7188,7 +7441,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A2">
-    <cfRule type="cellIs" dxfId="15" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -30704,60 +30957,60 @@
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
   <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="14" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="cellIs" dxfId="13" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H1">
-    <cfRule type="cellIs" dxfId="12" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="cellIs" dxfId="11" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L1">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="N1">
-    <cfRule type="cellIs" dxfId="9" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P1">
-    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1">
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="6" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:Y1048576">
-    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V1">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X1">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/ABNT/Ontologia_15965_1S.xlsx
+++ b/Versão5/ABNT/Ontologia_15965_1S.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\ABNT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEA7DC0F-E610-4753-AAB9-2022B23E5F0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B279E5-017B-4E77-8BD4-73858CDF1FA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" activeTab="4" xr2:uid="{82C81399-C775-48F3-A336-58DE5F35A6D9}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="9" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8030" uniqueCount="872">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8030" uniqueCount="871">
   <si>
     <t>Indivíduo</t>
   </si>
@@ -2478,9 +2478,6 @@
     <t>"Parte 3 da NBR 15.965"</t>
   </si>
   <si>
-    <t>Conceito</t>
-  </si>
-  <si>
     <t>Contêineres</t>
   </si>
   <si>
@@ -2505,21 +2502,12 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Normativo</t>
-  </si>
-  <si>
-    <t>NBR.Temática</t>
-  </si>
-  <si>
     <t>Código ABNT do sistema de classificação da construção do Brasil. NBR 15.965 - 0M. Códigos de Materiais.</t>
   </si>
   <si>
     <t>Código ABNT del sistema de clasificación de la construcción en Brasil. NBR 15.965 - 0M. Códigos de materiales.</t>
   </si>
   <si>
-    <t>Interdiciplinar</t>
-  </si>
-  <si>
     <t>ABNT code of the construction classification system in Brazil. NBR 15.965 - 0M. Material Codes.</t>
   </si>
   <si>
@@ -2707,6 +2695,15 @@
   </si>
   <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
+  </si>
+  <si>
+    <t>Conceitos</t>
+  </si>
+  <si>
+    <t>Normativos</t>
+  </si>
+  <si>
+    <t>NBR.Temáticas</t>
   </si>
 </sst>
 </file>
@@ -4007,7 +4004,7 @@
       </c>
       <c r="B18" s="5">
         <f ca="1">NOW()</f>
-        <v>46233.479224189818</v>
+        <v>46243.560060648146</v>
       </c>
       <c r="C18" s="39" t="s">
         <v>689</v>
@@ -4105,10 +4102,10 @@
     </row>
     <row r="27" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="36" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B27" s="57" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C27" s="39" t="s">
         <v>689</v>
@@ -4116,10 +4113,10 @@
     </row>
     <row r="28" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="36" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="B28" s="58" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C28" s="39" t="s">
         <v>689</v>
@@ -4127,10 +4124,10 @@
     </row>
     <row r="29" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="36" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B29" s="58" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C29" s="39" t="s">
         <v>689</v>
@@ -4138,10 +4135,10 @@
     </row>
     <row r="30" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="36" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>853</v>
+        <v>849</v>
       </c>
       <c r="C30" s="39" t="s">
         <v>689</v>
@@ -4149,10 +4146,10 @@
     </row>
     <row r="31" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="36" t="s">
-        <v>854</v>
+        <v>850</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="C31" s="39" t="s">
         <v>689</v>
@@ -4160,10 +4157,10 @@
     </row>
     <row r="32" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="36" t="s">
-        <v>856</v>
+        <v>852</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="C32" s="39" t="s">
         <v>689</v>
@@ -4171,10 +4168,10 @@
     </row>
     <row r="33" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="36" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="B33" s="60" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="C33" s="39" t="s">
         <v>689</v>
@@ -4182,10 +4179,10 @@
     </row>
     <row r="34" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="36" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="B34" s="60" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="C34" s="39" t="s">
         <v>689</v>
@@ -4193,10 +4190,10 @@
     </row>
     <row r="35" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="36" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="C35" s="39" t="s">
         <v>689</v>
@@ -4204,10 +4201,10 @@
     </row>
     <row r="36" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="36" t="s">
-        <v>864</v>
+        <v>860</v>
       </c>
       <c r="B36" s="60" t="s">
-        <v>865</v>
+        <v>861</v>
       </c>
       <c r="C36" s="39" t="s">
         <v>689</v>
@@ -4215,10 +4212,10 @@
     </row>
     <row r="37" spans="1:3" s="59" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="36" t="s">
-        <v>866</v>
+        <v>862</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C37" s="39" t="s">
         <v>689</v>
@@ -4226,10 +4223,10 @@
     </row>
     <row r="38" spans="1:3" ht="10" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="4" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="B38" s="61" t="s">
-        <v>869</v>
+        <v>865</v>
       </c>
       <c r="C38" s="39" t="s">
         <v>689</v>
@@ -4237,10 +4234,10 @@
     </row>
     <row r="39" spans="1:3" s="63" customFormat="1" ht="9.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="36" t="s">
-        <v>870</v>
+        <v>866</v>
       </c>
       <c r="B39" s="62" t="s">
-        <v>871</v>
+        <v>867</v>
       </c>
       <c r="C39" s="39" t="s">
         <v>689</v>
@@ -4264,8 +4261,8 @@
   <dimension ref="A1:AA32"/>
   <sheetFormatPr defaultRowHeight="6.75" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.69921875" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.8984375" customWidth="1"/>
+    <col min="2" max="2" width="6.59765625" style="27" customWidth="1"/>
     <col min="3" max="3" width="7" style="27" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.19921875" style="27" customWidth="1"/>
     <col min="5" max="5" width="9.69921875" style="27" customWidth="1"/>
@@ -4377,7 +4374,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C2" s="47" t="s">
         <v>705</v>
@@ -4386,7 +4383,7 @@
         <v>707</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F2" s="48" t="s">
         <v>706</v>
@@ -4423,10 +4420,10 @@
         <v>Contêiner</v>
       </c>
       <c r="P2" s="35" t="s">
+        <v>796</v>
+      </c>
+      <c r="Q2" s="35" t="s">
         <v>797</v>
-      </c>
-      <c r="Q2" s="35" t="s">
-        <v>798</v>
       </c>
       <c r="R2" s="35" t="s">
         <v>321</v>
@@ -4457,7 +4454,7 @@
         <v>321</v>
       </c>
       <c r="Z2" s="35" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AA2" s="35" t="str">
         <f t="shared" ref="AA2:AA6" si="3">_xlfn.TRANSLATE(P2,"pt","en")</f>
@@ -4469,7 +4466,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C3" s="47" t="s">
         <v>705</v>
@@ -4478,7 +4475,7 @@
         <v>707</v>
       </c>
       <c r="E3" s="48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F3" s="48" t="s">
         <v>709</v>
@@ -4515,10 +4512,10 @@
         <v>Requisito Espacial</v>
       </c>
       <c r="P3" s="35" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="Q3" s="35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R3" s="35" t="s">
         <v>321</v>
@@ -4561,7 +4558,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C4" s="47" t="s">
         <v>705</v>
@@ -4570,7 +4567,7 @@
         <v>707</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F4" s="48" t="s">
         <v>710</v>
@@ -4607,10 +4604,10 @@
         <v>Requisito Mobiliário</v>
       </c>
       <c r="P4" s="35" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="Q4" s="35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R4" s="35" t="s">
         <v>321</v>
@@ -4653,7 +4650,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C5" s="47" t="s">
         <v>705</v>
@@ -4662,7 +4659,7 @@
         <v>707</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F5" s="48" t="s">
         <v>711</v>
@@ -4699,10 +4696,10 @@
         <v>Requisito Equipamento</v>
       </c>
       <c r="P5" s="35" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q5" s="35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R5" s="35" t="s">
         <v>321</v>
@@ -4745,7 +4742,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>705</v>
@@ -4754,7 +4751,7 @@
         <v>707</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>712</v>
@@ -4791,10 +4788,10 @@
         <v>Requisito Sistemas</v>
       </c>
       <c r="P6" s="35" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="Q6" s="35" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="R6" s="35" t="s">
         <v>321</v>
@@ -4837,10 +4834,10 @@
         <v>7</v>
       </c>
       <c r="B7" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D7" s="26" t="s">
         <v>656</v>
@@ -4868,7 +4865,7 @@
       </c>
       <c r="L7" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M7" s="50" t="str">
         <f t="shared" si="0"/>
@@ -4883,17 +4880,17 @@
         <v>NBR.0M</v>
       </c>
       <c r="P7" s="50" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="Q7" s="50" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="R7" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S7" s="51" t="str">
         <f t="shared" ref="S7:U19" si="6">SUBSTITUTE(C7, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T7" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4904,7 +4901,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V7" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W7" s="55" t="str">
         <f t="shared" si="4"/>
@@ -4920,7 +4917,7 @@
         <v>713</v>
       </c>
       <c r="AA7" s="52" t="s">
-        <v>809</v>
+        <v>805</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -4928,10 +4925,10 @@
         <v>8</v>
       </c>
       <c r="B8" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D8" s="26" t="s">
         <v>656</v>
@@ -4959,7 +4956,7 @@
       </c>
       <c r="L8" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M8" s="50" t="str">
         <f t="shared" si="0"/>
@@ -4974,17 +4971,17 @@
         <v>NBR.0P</v>
       </c>
       <c r="P8" s="50" t="s">
-        <v>810</v>
+        <v>806</v>
       </c>
       <c r="Q8" s="50" t="s">
-        <v>811</v>
+        <v>807</v>
       </c>
       <c r="R8" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S8" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T8" s="51" t="str">
         <f t="shared" si="6"/>
@@ -4995,7 +4992,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V8" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W8" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5011,7 +5008,7 @@
         <v>714</v>
       </c>
       <c r="AA8" s="52" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5019,10 +5016,10 @@
         <v>9</v>
       </c>
       <c r="B9" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D9" s="26" t="s">
         <v>656</v>
@@ -5050,7 +5047,7 @@
       </c>
       <c r="L9" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M9" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5065,17 +5062,17 @@
         <v>NBR.1D</v>
       </c>
       <c r="P9" s="50" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="Q9" s="50" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="R9" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S9" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T9" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5086,7 +5083,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V9" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W9" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5102,7 +5099,7 @@
         <v>715</v>
       </c>
       <c r="AA9" s="52" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5110,10 +5107,10 @@
         <v>10</v>
       </c>
       <c r="B10" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>656</v>
@@ -5141,7 +5138,7 @@
       </c>
       <c r="L10" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M10" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5156,17 +5153,17 @@
         <v>NBR.1F</v>
       </c>
       <c r="P10" s="50" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="Q10" s="50" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="R10" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S10" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T10" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5177,7 +5174,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V10" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W10" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5193,7 +5190,7 @@
         <v>716</v>
       </c>
       <c r="AA10" s="52" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
     </row>
     <row r="11" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5201,10 +5198,10 @@
         <v>11</v>
       </c>
       <c r="B11" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D11" s="26" t="s">
         <v>656</v>
@@ -5232,7 +5229,7 @@
       </c>
       <c r="L11" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M11" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5247,17 +5244,17 @@
         <v>NBR.1S</v>
       </c>
       <c r="P11" s="50" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="Q11" s="50" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="R11" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S11" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T11" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5268,7 +5265,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V11" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W11" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5284,7 +5281,7 @@
         <v>624</v>
       </c>
       <c r="AA11" s="52" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5292,10 +5289,10 @@
         <v>12</v>
       </c>
       <c r="B12" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D12" s="26" t="s">
         <v>656</v>
@@ -5323,7 +5320,7 @@
       </c>
       <c r="L12" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M12" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5338,17 +5335,17 @@
         <v>NBR.2C</v>
       </c>
       <c r="P12" s="50" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="Q12" s="50" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="R12" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S12" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T12" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5359,7 +5356,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V12" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W12" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5375,7 +5372,7 @@
         <v>717</v>
       </c>
       <c r="AA12" s="52" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5383,10 +5380,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D13" s="26" t="s">
         <v>656</v>
@@ -5414,7 +5411,7 @@
       </c>
       <c r="L13" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M13" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5429,17 +5426,17 @@
         <v>NBR.2N</v>
       </c>
       <c r="P13" s="50" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="Q13" s="50" t="s">
-        <v>826</v>
+        <v>822</v>
       </c>
       <c r="R13" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S13" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T13" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5450,7 +5447,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V13" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W13" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5466,7 +5463,7 @@
         <v>718</v>
       </c>
       <c r="AA13" s="52" t="s">
-        <v>827</v>
+        <v>823</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5474,10 +5471,10 @@
         <v>14</v>
       </c>
       <c r="B14" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>656</v>
@@ -5505,7 +5502,7 @@
       </c>
       <c r="L14" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M14" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5520,17 +5517,17 @@
         <v>NBR.2Q</v>
       </c>
       <c r="P14" s="50" t="s">
-        <v>828</v>
+        <v>824</v>
       </c>
       <c r="Q14" s="50" t="s">
-        <v>829</v>
+        <v>825</v>
       </c>
       <c r="R14" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S14" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T14" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5541,7 +5538,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V14" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W14" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5557,7 +5554,7 @@
         <v>719</v>
       </c>
       <c r="AA14" s="52" t="s">
-        <v>830</v>
+        <v>826</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5565,10 +5562,10 @@
         <v>15</v>
       </c>
       <c r="B15" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D15" s="26" t="s">
         <v>656</v>
@@ -5596,7 +5593,7 @@
       </c>
       <c r="L15" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M15" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5611,17 +5608,17 @@
         <v>NBR.3E</v>
       </c>
       <c r="P15" s="50" t="s">
-        <v>831</v>
+        <v>827</v>
       </c>
       <c r="Q15" s="50" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="R15" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S15" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T15" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5632,7 +5629,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V15" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W15" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5648,7 +5645,7 @@
         <v>720</v>
       </c>
       <c r="AA15" s="52" t="s">
-        <v>833</v>
+        <v>829</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5656,10 +5653,10 @@
         <v>16</v>
       </c>
       <c r="B16" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D16" s="26" t="s">
         <v>656</v>
@@ -5687,7 +5684,7 @@
       </c>
       <c r="L16" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M16" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5702,17 +5699,17 @@
         <v>NBR.3R</v>
       </c>
       <c r="P16" s="50" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="Q16" s="50" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="R16" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S16" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T16" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5723,7 +5720,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V16" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W16" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5739,7 +5736,7 @@
         <v>721</v>
       </c>
       <c r="AA16" s="52" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
     </row>
     <row r="17" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5747,10 +5744,10 @@
         <v>17</v>
       </c>
       <c r="B17" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D17" s="26" t="s">
         <v>656</v>
@@ -5778,7 +5775,7 @@
       </c>
       <c r="L17" s="50" t="str">
         <f t="shared" si="0"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M17" s="50" t="str">
         <f t="shared" si="0"/>
@@ -5793,17 +5790,17 @@
         <v>NBR.4A</v>
       </c>
       <c r="P17" s="50" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="Q17" s="50" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="R17" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S17" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T17" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5814,7 +5811,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V17" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W17" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5830,7 +5827,7 @@
         <v>722</v>
       </c>
       <c r="AA17" s="52" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
     </row>
     <row r="18" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5838,10 +5835,10 @@
         <v>18</v>
       </c>
       <c r="B18" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D18" s="26" t="s">
         <v>656</v>
@@ -5869,7 +5866,7 @@
       </c>
       <c r="L18" s="50" t="str">
         <f t="shared" ref="L18:N19" si="7">CONCATENATE("", C18)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M18" s="50" t="str">
         <f t="shared" si="7"/>
@@ -5884,17 +5881,17 @@
         <v>NBR.4U</v>
       </c>
       <c r="P18" s="50" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="Q18" s="50" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="R18" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S18" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T18" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5905,7 +5902,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V18" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W18" s="55" t="str">
         <f t="shared" si="4"/>
@@ -5921,7 +5918,7 @@
         <v>723</v>
       </c>
       <c r="AA18" s="52" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
     </row>
     <row r="19" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -5929,10 +5926,10 @@
         <v>19</v>
       </c>
       <c r="B19" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D19" s="26" t="s">
         <v>656</v>
@@ -5960,7 +5957,7 @@
       </c>
       <c r="L19" s="50" t="str">
         <f t="shared" si="7"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M19" s="50" t="str">
         <f t="shared" si="7"/>
@@ -5975,17 +5972,17 @@
         <v>NBR.5I</v>
       </c>
       <c r="P19" s="50" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="Q19" s="50" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="R19" s="35" t="s">
         <v>321</v>
       </c>
       <c r="S19" s="51" t="str">
         <f t="shared" si="6"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T19" s="51" t="str">
         <f t="shared" si="6"/>
@@ -5996,7 +5993,7 @@
         <v>NBR.Parte</v>
       </c>
       <c r="V19" s="35" t="s">
-        <v>808</v>
+        <v>708</v>
       </c>
       <c r="W19" s="55" t="str">
         <f t="shared" si="4"/>
@@ -6012,7 +6009,7 @@
         <v>724</v>
       </c>
       <c r="AA19" s="52" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
     </row>
     <row r="20" spans="1:27" ht="6.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -6020,13 +6017,13 @@
         <v>20</v>
       </c>
       <c r="B20" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E20" s="26" t="s">
         <v>792</v>
@@ -6051,11 +6048,11 @@
       </c>
       <c r="L20" s="50" t="str">
         <f t="shared" ref="L20:N32" si="8">CONCATENATE("", C20)</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M20" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N20" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6077,11 +6074,11 @@
       </c>
       <c r="S20" s="51" t="str">
         <f t="shared" ref="S20:U22" si="10">SUBSTITUTE(C20, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T20" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U20" s="50" t="str">
         <f t="shared" si="10"/>
@@ -6113,13 +6110,13 @@
         <v>21</v>
       </c>
       <c r="B21" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E21" s="26" t="s">
         <v>792</v>
@@ -6144,11 +6141,11 @@
       </c>
       <c r="L21" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M21" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N21" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6170,11 +6167,11 @@
       </c>
       <c r="S21" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T21" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U21" s="50" t="str">
         <f t="shared" si="10"/>
@@ -6206,13 +6203,13 @@
         <v>22</v>
       </c>
       <c r="B22" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>792</v>
@@ -6237,11 +6234,11 @@
       </c>
       <c r="L22" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M22" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N22" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6263,11 +6260,11 @@
       </c>
       <c r="S22" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T22" s="51" t="str">
         <f t="shared" si="10"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U22" s="50" t="str">
         <f t="shared" si="10"/>
@@ -6299,13 +6296,13 @@
         <v>23</v>
       </c>
       <c r="B23" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>792</v>
@@ -6330,11 +6327,11 @@
       </c>
       <c r="L23" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M23" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N23" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6356,11 +6353,11 @@
       </c>
       <c r="S23" s="51" t="str">
         <f t="shared" ref="S23:U32" si="13">SUBSTITUTE(C23, "_", " ")</f>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T23" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U23" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6392,13 +6389,13 @@
         <v>24</v>
       </c>
       <c r="B24" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>792</v>
@@ -6423,11 +6420,11 @@
       </c>
       <c r="L24" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M24" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N24" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6449,11 +6446,11 @@
       </c>
       <c r="S24" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T24" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U24" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6485,13 +6482,13 @@
         <v>25</v>
       </c>
       <c r="B25" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>792</v>
@@ -6516,11 +6513,11 @@
       </c>
       <c r="L25" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M25" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N25" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6542,11 +6539,11 @@
       </c>
       <c r="S25" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T25" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U25" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6578,13 +6575,13 @@
         <v>26</v>
       </c>
       <c r="B26" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E26" s="26" t="s">
         <v>792</v>
@@ -6609,11 +6606,11 @@
       </c>
       <c r="L26" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M26" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N26" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6635,11 +6632,11 @@
       </c>
       <c r="S26" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T26" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U26" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6671,13 +6668,13 @@
         <v>27</v>
       </c>
       <c r="B27" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D27" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E27" s="26" t="s">
         <v>792</v>
@@ -6702,11 +6699,11 @@
       </c>
       <c r="L27" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M27" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N27" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6728,11 +6725,11 @@
       </c>
       <c r="S27" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T27" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U27" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6764,13 +6761,13 @@
         <v>28</v>
       </c>
       <c r="B28" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D28" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E28" s="26" t="s">
         <v>792</v>
@@ -6795,11 +6792,11 @@
       </c>
       <c r="L28" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M28" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N28" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6821,11 +6818,11 @@
       </c>
       <c r="S28" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T28" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U28" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6857,13 +6854,13 @@
         <v>29</v>
       </c>
       <c r="B29" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D29" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E29" s="26" t="s">
         <v>792</v>
@@ -6888,11 +6885,11 @@
       </c>
       <c r="L29" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M29" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N29" s="50" t="str">
         <f t="shared" si="8"/>
@@ -6914,11 +6911,11 @@
       </c>
       <c r="S29" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T29" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U29" s="50" t="str">
         <f t="shared" si="13"/>
@@ -6950,13 +6947,13 @@
         <v>30</v>
       </c>
       <c r="B30" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D30" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>792</v>
@@ -6981,11 +6978,11 @@
       </c>
       <c r="L30" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M30" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N30" s="50" t="str">
         <f t="shared" si="8"/>
@@ -7007,11 +7004,11 @@
       </c>
       <c r="S30" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T30" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U30" s="50" t="str">
         <f t="shared" si="13"/>
@@ -7043,13 +7040,13 @@
         <v>31</v>
       </c>
       <c r="B31" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D31" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>792</v>
@@ -7074,11 +7071,11 @@
       </c>
       <c r="L31" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M31" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N31" s="50" t="str">
         <f t="shared" si="8"/>
@@ -7100,11 +7097,11 @@
       </c>
       <c r="S31" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T31" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U31" s="50" t="str">
         <f t="shared" si="13"/>
@@ -7136,13 +7133,13 @@
         <v>32</v>
       </c>
       <c r="B32" s="47" t="s">
-        <v>795</v>
+        <v>868</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D32" s="26" t="s">
-        <v>805</v>
+        <v>870</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>792</v>
@@ -7167,11 +7164,11 @@
       </c>
       <c r="L32" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="M32" s="50" t="str">
         <f t="shared" si="8"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="N32" s="50" t="str">
         <f t="shared" si="8"/>
@@ -7193,11 +7190,11 @@
       </c>
       <c r="S32" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>Normativo</v>
+        <v>Normativos</v>
       </c>
       <c r="T32" s="51" t="str">
         <f t="shared" si="13"/>
-        <v>NBR.Temática</v>
+        <v>NBR.Temáticas</v>
       </c>
       <c r="U32" s="50" t="str">
         <f t="shared" si="13"/>
@@ -7554,7 +7551,7 @@
         <v>625</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>804</v>
+        <v>869</v>
       </c>
       <c r="D2" s="53" t="s">
         <v>321</v>
